--- a/data/prod_parameters/HorseHerd.xlsx
+++ b/data/prod_parameters/HorseHerd.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="default" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -18,10 +18,96 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="22">
+  <si>
+    <t>f_breed</t>
+  </si>
+  <si>
+    <t>f_prod_system</t>
+  </si>
+  <si>
+    <t>f_animal</t>
+  </si>
+  <si>
+    <t>ponies and Icelandic horses</t>
+  </si>
+  <si>
+    <t>broodmares</t>
+  </si>
+  <si>
+    <t>young horses</t>
+  </si>
+  <si>
+    <t>cold blooded horses</t>
+  </si>
+  <si>
+    <t>riding horses</t>
+  </si>
+  <si>
+    <t>trotters and racehorses</t>
+  </si>
+  <si>
+    <t>low-performing horses</t>
+  </si>
+  <si>
+    <t>medium-performing horses</t>
+  </si>
+  <si>
+    <t>parameter</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>unit</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>source</t>
+  </si>
+  <si>
+    <t>share_of_horses</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>slaughter_weight</t>
+  </si>
+  <si>
+    <t>kg CW</t>
+  </si>
+  <si>
+    <t>live_weight</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -49,8 +135,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -331,9 +421,176 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="2">
+        <v>60.549226441631497</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="2">
+        <v>27.5045007032349</v>
+      </c>
+      <c r="F4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="2">
+        <v>3.7389592123769302</v>
+      </c>
+      <c r="F5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="2">
+        <v>8.2073136427566808</v>
+      </c>
+      <c r="F6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="2">
+        <v>394.61241132208016</v>
+      </c>
+      <c r="F9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="2">
+        <v>585.45178524024413</v>
+      </c>
+      <c r="F10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="2">
+        <v>567.18533165122039</v>
+      </c>
+      <c r="F11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="2">
+        <v>496.52359083562101</v>
+      </c>
+      <c r="F12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/prod_parameters/HorseHerd.xlsx
+++ b/data/prod_parameters/HorseHerd.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="default" sheetId="1" r:id="rId1"/>
+    <sheet name="ME req young horses" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="57">
   <si>
     <t>f_breed</t>
   </si>
@@ -85,13 +86,122 @@
   </si>
   <si>
     <t>kg</t>
+  </si>
+  <si>
+    <t>Live and slaughter weight</t>
+  </si>
+  <si>
+    <t>Feed requirements</t>
+  </si>
+  <si>
+    <t>energy_adjustment_factor</t>
+  </si>
+  <si>
+    <t>gestation_energy_factor</t>
+  </si>
+  <si>
+    <t>lactation_energy_factor</t>
+  </si>
+  <si>
+    <t>Tabell 9</t>
+  </si>
+  <si>
+    <t>3 months lactation</t>
+  </si>
+  <si>
+    <t>foals_per_year</t>
+  </si>
+  <si>
+    <t>Seems to be common with one foal per year but some room for a missed year</t>
+  </si>
+  <si>
+    <t>MJ ME per day/kg LW^0.75</t>
+  </si>
+  <si>
+    <t>Tabell 5b. Grundenergibehov (underhåll+tillväxt)* (MJ/dag) för unghästar med hög tillväxttakt (L=lättfödd, N=normalfödd, S= svårfödd). Vid hög tillväxttakt blir den dagliga tillväxten 40 % högre än vid låg från 7 mån</t>
+  </si>
+  <si>
+    <t>Uppskattad vuxenvikt</t>
+  </si>
+  <si>
+    <t>3-6 mån</t>
+  </si>
+  <si>
+    <t>7-12 mån</t>
+  </si>
+  <si>
+    <t>13-18 mån</t>
+  </si>
+  <si>
+    <t>19-36 mån</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>LW^0.75</t>
+  </si>
+  <si>
+    <t>Adult live weight</t>
+  </si>
+  <si>
+    <t>maintenance_energy_factor</t>
+  </si>
+  <si>
+    <t>Feed rations</t>
+  </si>
+  <si>
+    <t>share_in_ration</t>
+  </si>
+  <si>
+    <t>Fallback</t>
+  </si>
+  <si>
+    <t>f_feed</t>
+  </si>
+  <si>
+    <t>% of DM</t>
+  </si>
+  <si>
+    <t>hay</t>
+  </si>
+  <si>
+    <t>grazing</t>
+  </si>
+  <si>
+    <t>Tabell 5a. Grundenergibehov (underhåll+tillväxt)* (MJ/dag) för unghästar med låg tillväxttakt (L=lättfödd, N=normalfödd, S= svårfödd)</t>
+  </si>
+  <si>
+    <t>MEAN</t>
+  </si>
+  <si>
+    <t>SD</t>
+  </si>
+  <si>
+    <t>calculated from Tabell 5b</t>
+  </si>
+  <si>
+    <t>Tabell 13. 11 mont gestation. Assume linear growth from month 1 (+0%) to 8 (+15%)</t>
+  </si>
+  <si>
+    <t>No activity adjustment</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -114,16 +224,78 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -131,16 +303,118 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" indent="2" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" indent="2" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" indent="2" shrinkToFit="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -156,6 +430,2451 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.16600526191073828"/>
+          <c:y val="5.4320987654320987E-2"/>
+          <c:w val="0.71268022894524086"/>
+          <c:h val="0.83173636628754744"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'ME req young horses'!$S$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>L</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'ME req young horses'!$O$21:$O$28</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>31.622776601683803</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>53.182958969449857</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>72.084342424042617</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>89.442719099991592</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>105.73712634405643</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>121.23093028059735</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>136.0891589269774</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>150.42412372345569</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'ME req young horses'!$S$21:$S$28</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0.5454928963790453</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.55468895623024339</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.55490552670504234</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.5562219094030727</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.55325884126685776</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.55266424042877405</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.55662038473355446</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.55343516677583804</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D9A6-4EE6-98ED-B52090D957FC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'ME req young horses'!$T$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>N</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'ME req young horses'!$O$21:$O$28</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>31.622776601683803</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>53.182958969449857</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>72.084342424042617</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>89.442719099991592</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>105.73712634405643</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>121.23093028059735</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>136.0891589269774</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>150.42412372345569</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'ME req young horses'!$T$21:$T$28</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0.57711567298072908</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.58289347942839131</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.58265080304029448</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.58417275912181998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.58163108953695297</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.57947258044957284</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.58601288029704246</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.58002664626056299</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-D9A6-4EE6-98ED-B52090D957FC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'ME req young horses'!$U$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>S</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'ME req young horses'!$O$21:$O$28</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>31.622776601683803</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>53.182958969449857</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>72.084342424042617</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>89.442719099991592</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>105.73712634405643</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>121.23093028059735</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>136.0891589269774</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>150.42412372345569</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'ME req young horses'!$U$21:$U$28</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0.60873844958241285</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.61109800262653935</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.61039607937554663</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.61212360884056738</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.6100033378070483</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.60834310047197149</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.61356834488781253</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.60994206068087853</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-D9A6-4EE6-98ED-B52090D957FC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="815639632"/>
+        <c:axId val="815649200"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="815639632"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="815649200"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="815649200"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="815639632"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:legendEntry>
+        <c:idx val="3"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="4"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="5"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.88173121816893341"/>
+          <c:y val="5.343248760571595E-2"/>
+          <c:w val="8.4253046374238888E-2"/>
+          <c:h val="0.25771401745075245"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.16600526191073828"/>
+          <c:y val="5.4320987654320987E-2"/>
+          <c:w val="0.71268022894524086"/>
+          <c:h val="0.83173636628754744"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'ME req young horses'!$S$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>L</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'ME req young horses'!$O$6:$O$13</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>31.622776601683803</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>53.182958969449857</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>72.084342424042617</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>89.442719099991592</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>105.73712634405643</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>121.23093028059735</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>136.0891589269774</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>150.42412372345569</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'ME req young horses'!$S$6:$S$13</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0.60873844958241285</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.60639724876018131</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.60692791983364014</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.60653343889681788</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.6100033378070483</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.60628092047037152</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.60622022099694051</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.60661812574528795</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1353-4230-BB93-7C29A99186A4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'ME req young horses'!$T$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>N</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'ME req young horses'!$O$6:$O$13</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>31.622776601683803</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>53.182958969449857</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>72.084342424042617</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>89.442719099991592</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>105.73712634405643</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>121.23093028059735</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>136.0891589269774</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>150.42412372345569</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'ME req young horses'!$T$6:$T$13</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0.64036122618409663</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.63930252582468727</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.63467319616889217</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.63727937358744002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.63837558607714351</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.63721362049437014</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.6356127165604285</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.63819550763339883</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1353-4230-BB93-7C29A99186A4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'ME req young horses'!$U$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>S</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'ME req young horses'!$O$6:$O$13</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>31.622776601683803</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>53.182958969449857</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>72.084342424042617</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>89.442719099991592</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>105.73712634405643</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>121.23093028059735</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>136.0891589269774</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>150.42412372345569</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'ME req young horses'!$U$6:$U$13</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0.67198400278578041</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.66280629515647727</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.66935479158795741</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.67082039324993692</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.67384089641476264</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.66814632051836864</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.66684224309663453</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.66644895458591913</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-1353-4230-BB93-7C29A99186A4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="815639632"/>
+        <c:axId val="815649200"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="815639632"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="815649200"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="815649200"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="815639632"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:legendEntry>
+        <c:idx val="3"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="4"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="5"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.88173121816893341"/>
+          <c:y val="5.343248760571595E-2"/>
+          <c:w val="8.4253046374238888E-2"/>
+          <c:h val="0.25771401745075245"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>266701</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>266701</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -421,16 +3140,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.5703125" customWidth="1"/>
+    <col min="5" max="5" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" customWidth="1"/>
+    <col min="8" max="8" width="38.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -441,156 +3163,1902 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="2">
+      <c r="F3" s="2">
         <v>60.549226441631497</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="2">
+      <c r="F4" s="2">
         <v>27.5045007032349</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>4</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="2">
+      <c r="F5" s="2">
         <v>3.7389592123769302</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
         <v>5</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="2">
+      <c r="F6" s="2">
         <v>8.2073136427566808</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="10">
+        <v>0.9</v>
+      </c>
+      <c r="H7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="2">
+      <c r="F9" s="2">
         <v>394.61241132208016</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>6</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="2">
+      <c r="F10" s="2">
         <v>585.45178524024413</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>7</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="2">
+      <c r="F11" s="2">
         <v>567.18533165122039</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>8</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="2">
+      <c r="F12" s="2">
         <v>496.52359083562101</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>21</v>
+      </c>
+      <c r="H12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E13" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="G15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="G16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17" s="8">
+        <f>0.5*1.05</f>
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="G17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="8">
+        <f>0.5*1.1</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" t="s">
+        <v>5</v>
+      </c>
+      <c r="E19" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" s="8">
+        <v>0.60721495776158751</v>
+      </c>
+      <c r="G19" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20" s="8">
+        <v>0.60721495776158751</v>
+      </c>
+      <c r="G20" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" s="8">
+        <v>0.63762671906630719</v>
+      </c>
+      <c r="G21" t="s">
+        <v>31</v>
+      </c>
+      <c r="H21" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" t="s">
+        <v>43</v>
+      </c>
+      <c r="F22" s="8">
+        <v>0.66878048717447958</v>
+      </c>
+      <c r="G22" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E23" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="9">
+        <f>( (0.15/2)*8 + 0.15 + 0.25 + 0.3 ) / 12</f>
+        <v>0.10833333333333334</v>
+      </c>
+      <c r="H23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E24" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" s="9">
+        <f xml:space="preserve"> (1*3 + 0.7*1)/12</f>
+        <v>0.30833333333333335</v>
+      </c>
+      <c r="H24" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C25" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" t="s">
+        <v>24</v>
+      </c>
+      <c r="F25">
+        <v>0.25</v>
+      </c>
+      <c r="H25" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" t="s">
+        <v>24</v>
+      </c>
+      <c r="F26" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="H26" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C27" t="s">
+        <v>4</v>
+      </c>
+      <c r="E27" t="s">
+        <v>24</v>
+      </c>
+      <c r="F27" s="9">
+        <v>0</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
+        <v>5</v>
+      </c>
+      <c r="E28" t="s">
+        <v>24</v>
+      </c>
+      <c r="F28" s="28">
+        <v>0</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E31" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="F31" s="29">
+        <v>0</v>
+      </c>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D32" t="s">
+        <v>49</v>
+      </c>
+      <c r="E32" t="s">
+        <v>45</v>
+      </c>
+      <c r="F32" s="2">
+        <v>80</v>
+      </c>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+    </row>
+    <row r="33" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D33" t="s">
+        <v>50</v>
+      </c>
+      <c r="E33" t="s">
+        <v>45</v>
+      </c>
+      <c r="F33">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B3:U30"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="3" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="30"/>
+      <c r="M3" s="30"/>
+      <c r="N3" s="30"/>
+      <c r="O3" s="30"/>
+    </row>
+    <row r="4" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="11"/>
+      <c r="D4" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="11"/>
+      <c r="F4" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="33"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="33"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="M4" s="33"/>
+      <c r="N4" s="33"/>
+      <c r="O4" s="13"/>
+    </row>
+    <row r="5" spans="2:21" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B5" s="32"/>
+      <c r="C5" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="N5" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="O5" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="P5" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q5" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="R5" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="S5" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="T5" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="U5" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="17">
+        <v>100</v>
+      </c>
+      <c r="C6" s="18">
+        <v>17</v>
+      </c>
+      <c r="D6" s="19">
+        <v>18</v>
+      </c>
+      <c r="E6" s="18">
+        <v>19</v>
+      </c>
+      <c r="F6" s="19">
+        <v>20</v>
+      </c>
+      <c r="G6" s="19">
+        <v>21</v>
+      </c>
+      <c r="H6" s="18">
+        <v>22</v>
+      </c>
+      <c r="I6" s="19">
+        <v>21</v>
+      </c>
+      <c r="J6" s="19">
+        <v>22</v>
+      </c>
+      <c r="K6" s="19">
+        <v>23</v>
+      </c>
+      <c r="L6" s="19">
+        <v>19</v>
+      </c>
+      <c r="M6" s="19">
+        <v>20</v>
+      </c>
+      <c r="N6" s="19">
+        <v>21</v>
+      </c>
+      <c r="O6" s="2">
+        <f>B6^0.75</f>
+        <v>31.622776601683803</v>
+      </c>
+      <c r="P6" s="2">
+        <f>AVERAGE(C6,F6,I6,L6)</f>
+        <v>19.25</v>
+      </c>
+      <c r="Q6" s="2">
+        <f t="shared" ref="Q6:R6" si="0">AVERAGE(D6,G6,J6,M6)</f>
+        <v>20.25</v>
+      </c>
+      <c r="R6" s="2">
+        <f t="shared" si="0"/>
+        <v>21.25</v>
+      </c>
+      <c r="S6" s="8">
+        <f>P6/$O6</f>
+        <v>0.60873844958241285</v>
+      </c>
+      <c r="T6" s="8">
+        <f t="shared" ref="T6:U13" si="1">Q6/$O6</f>
+        <v>0.64036122618409663</v>
+      </c>
+      <c r="U6" s="8">
+        <f t="shared" si="1"/>
+        <v>0.67198400278578041</v>
+      </c>
+    </row>
+    <row r="7" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="20">
+        <v>200</v>
+      </c>
+      <c r="C7" s="21">
+        <v>29</v>
+      </c>
+      <c r="D7" s="22">
+        <v>30</v>
+      </c>
+      <c r="E7" s="21">
+        <v>32</v>
+      </c>
+      <c r="F7" s="22">
+        <v>33</v>
+      </c>
+      <c r="G7" s="22">
+        <v>35</v>
+      </c>
+      <c r="H7" s="21">
+        <v>36</v>
+      </c>
+      <c r="I7" s="22">
+        <v>34</v>
+      </c>
+      <c r="J7" s="22">
+        <v>36</v>
+      </c>
+      <c r="K7" s="22">
+        <v>37</v>
+      </c>
+      <c r="L7" s="22">
+        <v>33</v>
+      </c>
+      <c r="M7" s="22">
+        <v>35</v>
+      </c>
+      <c r="N7" s="22">
+        <v>36</v>
+      </c>
+      <c r="O7" s="2">
+        <f t="shared" ref="O7:O13" si="2">B7^0.75</f>
+        <v>53.182958969449857</v>
+      </c>
+      <c r="P7" s="2">
+        <f t="shared" ref="P7:P13" si="3">AVERAGE(C7,F7,I7,L7)</f>
+        <v>32.25</v>
+      </c>
+      <c r="Q7" s="2">
+        <f t="shared" ref="Q7:Q13" si="4">AVERAGE(D7,G7,J7,M7)</f>
+        <v>34</v>
+      </c>
+      <c r="R7" s="2">
+        <f t="shared" ref="R7:R13" si="5">AVERAGE(E7,H7,K7,N7)</f>
+        <v>35.25</v>
+      </c>
+      <c r="S7" s="8">
+        <f t="shared" ref="S7:S13" si="6">P7/$O7</f>
+        <v>0.60639724876018131</v>
+      </c>
+      <c r="T7" s="8">
+        <f t="shared" si="1"/>
+        <v>0.63930252582468727</v>
+      </c>
+      <c r="U7" s="8">
+        <f t="shared" si="1"/>
+        <v>0.66280629515647727</v>
+      </c>
+    </row>
+    <row r="8" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="20">
+        <v>300</v>
+      </c>
+      <c r="C8" s="21">
+        <v>39</v>
+      </c>
+      <c r="D8" s="22">
+        <v>41</v>
+      </c>
+      <c r="E8" s="21">
+        <v>43</v>
+      </c>
+      <c r="F8" s="22">
+        <v>45</v>
+      </c>
+      <c r="G8" s="22">
+        <v>47</v>
+      </c>
+      <c r="H8" s="21">
+        <v>50</v>
+      </c>
+      <c r="I8" s="22">
+        <v>47</v>
+      </c>
+      <c r="J8" s="22">
+        <v>49</v>
+      </c>
+      <c r="K8" s="22">
+        <v>52</v>
+      </c>
+      <c r="L8" s="22">
+        <v>44</v>
+      </c>
+      <c r="M8" s="22">
+        <v>46</v>
+      </c>
+      <c r="N8" s="22">
+        <v>48</v>
+      </c>
+      <c r="O8" s="2">
+        <f t="shared" si="2"/>
+        <v>72.084342424042617</v>
+      </c>
+      <c r="P8" s="2">
+        <f t="shared" si="3"/>
+        <v>43.75</v>
+      </c>
+      <c r="Q8" s="2">
+        <f t="shared" si="4"/>
+        <v>45.75</v>
+      </c>
+      <c r="R8" s="2">
+        <f t="shared" si="5"/>
+        <v>48.25</v>
+      </c>
+      <c r="S8" s="8">
+        <f t="shared" si="6"/>
+        <v>0.60692791983364014</v>
+      </c>
+      <c r="T8" s="8">
+        <f t="shared" si="1"/>
+        <v>0.63467319616889217</v>
+      </c>
+      <c r="U8" s="8">
+        <f t="shared" si="1"/>
+        <v>0.66935479158795741</v>
+      </c>
+    </row>
+    <row r="9" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="20">
+        <v>400</v>
+      </c>
+      <c r="C9" s="21">
+        <v>49</v>
+      </c>
+      <c r="D9" s="22">
+        <v>51</v>
+      </c>
+      <c r="E9" s="21">
+        <v>54</v>
+      </c>
+      <c r="F9" s="22">
+        <v>55</v>
+      </c>
+      <c r="G9" s="22">
+        <v>58</v>
+      </c>
+      <c r="H9" s="21">
+        <v>61</v>
+      </c>
+      <c r="I9" s="22">
+        <v>58</v>
+      </c>
+      <c r="J9" s="22">
+        <v>61</v>
+      </c>
+      <c r="K9" s="22">
+        <v>64</v>
+      </c>
+      <c r="L9" s="22">
+        <v>55</v>
+      </c>
+      <c r="M9" s="22">
+        <v>58</v>
+      </c>
+      <c r="N9" s="22">
+        <v>61</v>
+      </c>
+      <c r="O9" s="2">
+        <f t="shared" si="2"/>
+        <v>89.442719099991592</v>
+      </c>
+      <c r="P9" s="2">
+        <f t="shared" si="3"/>
+        <v>54.25</v>
+      </c>
+      <c r="Q9" s="2">
+        <f t="shared" si="4"/>
+        <v>57</v>
+      </c>
+      <c r="R9" s="2">
+        <f t="shared" si="5"/>
+        <v>60</v>
+      </c>
+      <c r="S9" s="8">
+        <f t="shared" si="6"/>
+        <v>0.60653343889681788</v>
+      </c>
+      <c r="T9" s="8">
+        <f t="shared" si="1"/>
+        <v>0.63727937358744002</v>
+      </c>
+      <c r="U9" s="8">
+        <f t="shared" si="1"/>
+        <v>0.67082039324993692</v>
+      </c>
+    </row>
+    <row r="10" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="20">
+        <v>500</v>
+      </c>
+      <c r="C10" s="21">
+        <v>58</v>
+      </c>
+      <c r="D10" s="22">
+        <v>61</v>
+      </c>
+      <c r="E10" s="21">
+        <v>64</v>
+      </c>
+      <c r="F10" s="22">
+        <v>66</v>
+      </c>
+      <c r="G10" s="22">
+        <v>69</v>
+      </c>
+      <c r="H10" s="21">
+        <v>73</v>
+      </c>
+      <c r="I10" s="22">
+        <v>69</v>
+      </c>
+      <c r="J10" s="22">
+        <v>72</v>
+      </c>
+      <c r="K10" s="22">
+        <v>76</v>
+      </c>
+      <c r="L10" s="22">
+        <v>65</v>
+      </c>
+      <c r="M10" s="22">
+        <v>68</v>
+      </c>
+      <c r="N10" s="22">
+        <v>72</v>
+      </c>
+      <c r="O10" s="2">
+        <f t="shared" si="2"/>
+        <v>105.73712634405643</v>
+      </c>
+      <c r="P10" s="2">
+        <f t="shared" si="3"/>
+        <v>64.5</v>
+      </c>
+      <c r="Q10" s="2">
+        <f t="shared" si="4"/>
+        <v>67.5</v>
+      </c>
+      <c r="R10" s="2">
+        <f t="shared" si="5"/>
+        <v>71.25</v>
+      </c>
+      <c r="S10" s="8">
+        <f t="shared" si="6"/>
+        <v>0.6100033378070483</v>
+      </c>
+      <c r="T10" s="8">
+        <f t="shared" si="1"/>
+        <v>0.63837558607714351</v>
+      </c>
+      <c r="U10" s="8">
+        <f t="shared" si="1"/>
+        <v>0.67384089641476264</v>
+      </c>
+    </row>
+    <row r="11" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="20">
+        <v>600</v>
+      </c>
+      <c r="C11" s="21">
+        <v>66</v>
+      </c>
+      <c r="D11" s="22">
+        <v>69</v>
+      </c>
+      <c r="E11" s="21">
+        <v>73</v>
+      </c>
+      <c r="F11" s="22">
+        <v>75</v>
+      </c>
+      <c r="G11" s="22">
+        <v>79</v>
+      </c>
+      <c r="H11" s="21">
+        <v>83</v>
+      </c>
+      <c r="I11" s="22">
+        <v>79</v>
+      </c>
+      <c r="J11" s="22">
+        <v>83</v>
+      </c>
+      <c r="K11" s="22">
+        <v>87</v>
+      </c>
+      <c r="L11" s="22">
+        <v>74</v>
+      </c>
+      <c r="M11" s="22">
+        <v>78</v>
+      </c>
+      <c r="N11" s="22">
+        <v>81</v>
+      </c>
+      <c r="O11" s="2">
+        <f t="shared" si="2"/>
+        <v>121.23093028059735</v>
+      </c>
+      <c r="P11" s="2">
+        <f t="shared" si="3"/>
+        <v>73.5</v>
+      </c>
+      <c r="Q11" s="2">
+        <f t="shared" si="4"/>
+        <v>77.25</v>
+      </c>
+      <c r="R11" s="2">
+        <f t="shared" si="5"/>
+        <v>81</v>
+      </c>
+      <c r="S11" s="8">
+        <f t="shared" si="6"/>
+        <v>0.60628092047037152</v>
+      </c>
+      <c r="T11" s="8">
+        <f t="shared" si="1"/>
+        <v>0.63721362049437014</v>
+      </c>
+      <c r="U11" s="8">
+        <f t="shared" si="1"/>
+        <v>0.66814632051836864</v>
+      </c>
+    </row>
+    <row r="12" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="20">
+        <v>700</v>
+      </c>
+      <c r="C12" s="21">
+        <v>75</v>
+      </c>
+      <c r="D12" s="22">
+        <v>79</v>
+      </c>
+      <c r="E12" s="21">
+        <v>83</v>
+      </c>
+      <c r="F12" s="22">
+        <v>84</v>
+      </c>
+      <c r="G12" s="22">
+        <v>88</v>
+      </c>
+      <c r="H12" s="21">
+        <v>92</v>
+      </c>
+      <c r="I12" s="22">
+        <v>88</v>
+      </c>
+      <c r="J12" s="22">
+        <v>92</v>
+      </c>
+      <c r="K12" s="22">
+        <v>97</v>
+      </c>
+      <c r="L12" s="22">
+        <v>83</v>
+      </c>
+      <c r="M12" s="22">
+        <v>87</v>
+      </c>
+      <c r="N12" s="22">
+        <v>91</v>
+      </c>
+      <c r="O12" s="2">
+        <f t="shared" si="2"/>
+        <v>136.0891589269774</v>
+      </c>
+      <c r="P12" s="2">
+        <f t="shared" si="3"/>
+        <v>82.5</v>
+      </c>
+      <c r="Q12" s="2">
+        <f t="shared" si="4"/>
+        <v>86.5</v>
+      </c>
+      <c r="R12" s="2">
+        <f t="shared" si="5"/>
+        <v>90.75</v>
+      </c>
+      <c r="S12" s="8">
+        <f t="shared" si="6"/>
+        <v>0.60622022099694051</v>
+      </c>
+      <c r="T12" s="8">
+        <f t="shared" si="1"/>
+        <v>0.6356127165604285</v>
+      </c>
+      <c r="U12" s="8">
+        <f t="shared" si="1"/>
+        <v>0.66684224309663453</v>
+      </c>
+    </row>
+    <row r="13" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="23">
+        <v>800</v>
+      </c>
+      <c r="C13" s="24">
+        <v>82</v>
+      </c>
+      <c r="D13" s="25">
+        <v>86</v>
+      </c>
+      <c r="E13" s="24">
+        <v>90</v>
+      </c>
+      <c r="F13" s="25">
+        <v>93</v>
+      </c>
+      <c r="G13" s="25">
+        <v>98</v>
+      </c>
+      <c r="H13" s="24">
+        <v>102</v>
+      </c>
+      <c r="I13" s="25">
+        <v>98</v>
+      </c>
+      <c r="J13" s="25">
+        <v>103</v>
+      </c>
+      <c r="K13" s="25">
+        <v>108</v>
+      </c>
+      <c r="L13" s="25">
+        <v>92</v>
+      </c>
+      <c r="M13" s="25">
+        <v>97</v>
+      </c>
+      <c r="N13" s="25">
+        <v>101</v>
+      </c>
+      <c r="O13" s="2">
+        <f t="shared" si="2"/>
+        <v>150.42412372345569</v>
+      </c>
+      <c r="P13" s="2">
+        <f t="shared" si="3"/>
+        <v>91.25</v>
+      </c>
+      <c r="Q13" s="2">
+        <f t="shared" si="4"/>
+        <v>96</v>
+      </c>
+      <c r="R13" s="2">
+        <f t="shared" si="5"/>
+        <v>100.25</v>
+      </c>
+      <c r="S13" s="8">
+        <f t="shared" si="6"/>
+        <v>0.60661812574528795</v>
+      </c>
+      <c r="T13" s="8">
+        <f t="shared" si="1"/>
+        <v>0.63819550763339883</v>
+      </c>
+      <c r="U13" s="8">
+        <f t="shared" si="1"/>
+        <v>0.66644895458591913</v>
+      </c>
+    </row>
+    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="P14" s="9"/>
+      <c r="Q14" s="9"/>
+      <c r="R14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="S14" s="27">
+        <f>AVERAGE(S6:S13)</f>
+        <v>0.60721495776158751</v>
+      </c>
+      <c r="T14" s="27">
+        <f t="shared" ref="T14:U14" si="7">AVERAGE(T6:T13)</f>
+        <v>0.63762671906630719</v>
+      </c>
+      <c r="U14" s="27">
+        <f t="shared" si="7"/>
+        <v>0.66878048717447958</v>
+      </c>
+    </row>
+    <row r="15" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="R15" t="s">
+        <v>53</v>
+      </c>
+      <c r="S15" s="8">
+        <f>_xlfn.STDEV.P(S6:S13)</f>
+        <v>1.3004678340959768E-3</v>
+      </c>
+      <c r="T15" s="8">
+        <f t="shared" ref="T15:U15" si="8">_xlfn.STDEV.P(T6:T13)</f>
+        <v>1.7407247992471731E-3</v>
+      </c>
+      <c r="U15" s="8">
+        <f t="shared" si="8"/>
+        <v>3.2719884672688794E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B17" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="34"/>
+      <c r="J17" s="34"/>
+      <c r="K17" s="34"/>
+      <c r="L17" s="34"/>
+      <c r="M17" s="34"/>
+      <c r="N17" s="34"/>
+      <c r="O17" s="34"/>
+    </row>
+    <row r="18" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="34"/>
+      <c r="I18" s="34"/>
+      <c r="J18" s="34"/>
+      <c r="K18" s="34"/>
+      <c r="L18" s="34"/>
+      <c r="M18" s="34"/>
+      <c r="N18" s="34"/>
+      <c r="O18" s="34"/>
+    </row>
+    <row r="19" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="11"/>
+      <c r="D19" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="11"/>
+      <c r="F19" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="G19" s="33"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="J19" s="33"/>
+      <c r="K19" s="33"/>
+      <c r="L19" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="M19" s="33"/>
+      <c r="N19" s="33"/>
+      <c r="O19" s="13"/>
+    </row>
+    <row r="20" spans="2:21" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B20" s="32"/>
+      <c r="C20" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="H20" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="I20" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="J20" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="K20" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="L20" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="M20" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="N20" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="O20" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="P20" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q20" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="R20" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="S20" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="T20" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="U20" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="17">
+        <v>100</v>
+      </c>
+      <c r="C21" s="18">
+        <v>17</v>
+      </c>
+      <c r="D21" s="19">
+        <v>18</v>
+      </c>
+      <c r="E21" s="18">
+        <v>19</v>
+      </c>
+      <c r="F21" s="19">
+        <v>16</v>
+      </c>
+      <c r="G21" s="19">
+        <v>17</v>
+      </c>
+      <c r="H21" s="18">
+        <v>18</v>
+      </c>
+      <c r="I21" s="19">
+        <v>18</v>
+      </c>
+      <c r="J21" s="19">
+        <v>19</v>
+      </c>
+      <c r="K21" s="36">
+        <v>20</v>
+      </c>
+      <c r="L21" s="19">
+        <v>18</v>
+      </c>
+      <c r="M21" s="19">
+        <v>19</v>
+      </c>
+      <c r="N21" s="36">
+        <v>20</v>
+      </c>
+      <c r="O21" s="2">
+        <f>B21^0.75</f>
+        <v>31.622776601683803</v>
+      </c>
+      <c r="P21" s="2">
+        <f>AVERAGE(C21,F21,I21,L21)</f>
+        <v>17.25</v>
+      </c>
+      <c r="Q21" s="2">
+        <f t="shared" ref="Q21:Q28" si="9">AVERAGE(D21,G21,J21,M21)</f>
+        <v>18.25</v>
+      </c>
+      <c r="R21" s="2">
+        <f t="shared" ref="R21:R28" si="10">AVERAGE(E21,H21,K21,N21)</f>
+        <v>19.25</v>
+      </c>
+      <c r="S21" s="8">
+        <f>P21/$O21</f>
+        <v>0.5454928963790453</v>
+      </c>
+      <c r="T21" s="8">
+        <f t="shared" ref="T21:T28" si="11">Q21/$O21</f>
+        <v>0.57711567298072908</v>
+      </c>
+      <c r="U21" s="8">
+        <f t="shared" ref="U21:U28" si="12">R21/$O21</f>
+        <v>0.60873844958241285</v>
+      </c>
+    </row>
+    <row r="22" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="20">
+        <v>200</v>
+      </c>
+      <c r="C22" s="21">
+        <v>29</v>
+      </c>
+      <c r="D22" s="22">
+        <v>30</v>
+      </c>
+      <c r="E22" s="21">
+        <v>32</v>
+      </c>
+      <c r="F22" s="22">
+        <v>28</v>
+      </c>
+      <c r="G22" s="22">
+        <v>29</v>
+      </c>
+      <c r="H22" s="21">
+        <v>31</v>
+      </c>
+      <c r="I22" s="22">
+        <v>30</v>
+      </c>
+      <c r="J22" s="22">
+        <v>32</v>
+      </c>
+      <c r="K22" s="37">
+        <v>33</v>
+      </c>
+      <c r="L22" s="22">
+        <v>31</v>
+      </c>
+      <c r="M22" s="22">
+        <v>33</v>
+      </c>
+      <c r="N22" s="37">
+        <v>34</v>
+      </c>
+      <c r="O22" s="2">
+        <f t="shared" ref="O22:O28" si="13">B22^0.75</f>
+        <v>53.182958969449857</v>
+      </c>
+      <c r="P22" s="2">
+        <f t="shared" ref="P22:P28" si="14">AVERAGE(C22,F22,I22,L22)</f>
+        <v>29.5</v>
+      </c>
+      <c r="Q22" s="2">
+        <f t="shared" si="9"/>
+        <v>31</v>
+      </c>
+      <c r="R22" s="2">
+        <f t="shared" si="10"/>
+        <v>32.5</v>
+      </c>
+      <c r="S22" s="8">
+        <f t="shared" ref="S22:S28" si="15">P22/$O22</f>
+        <v>0.55468895623024339</v>
+      </c>
+      <c r="T22" s="8">
+        <f t="shared" si="11"/>
+        <v>0.58289347942839131</v>
+      </c>
+      <c r="U22" s="8">
+        <f t="shared" si="12"/>
+        <v>0.61109800262653935</v>
+      </c>
+    </row>
+    <row r="23" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B23" s="20">
+        <v>300</v>
+      </c>
+      <c r="C23" s="21">
+        <v>39</v>
+      </c>
+      <c r="D23" s="22">
+        <v>41</v>
+      </c>
+      <c r="E23" s="21">
+        <v>43</v>
+      </c>
+      <c r="F23" s="22">
+        <v>38</v>
+      </c>
+      <c r="G23" s="22">
+        <v>40</v>
+      </c>
+      <c r="H23" s="21">
+        <v>42</v>
+      </c>
+      <c r="I23" s="22">
+        <v>41</v>
+      </c>
+      <c r="J23" s="22">
+        <v>43</v>
+      </c>
+      <c r="K23" s="37">
+        <v>45</v>
+      </c>
+      <c r="L23" s="22">
+        <v>42</v>
+      </c>
+      <c r="M23" s="22">
+        <v>44</v>
+      </c>
+      <c r="N23" s="37">
+        <v>46</v>
+      </c>
+      <c r="O23" s="2">
+        <f t="shared" si="13"/>
+        <v>72.084342424042617</v>
+      </c>
+      <c r="P23" s="2">
+        <f t="shared" si="14"/>
+        <v>40</v>
+      </c>
+      <c r="Q23" s="2">
+        <f t="shared" si="9"/>
+        <v>42</v>
+      </c>
+      <c r="R23" s="2">
+        <f t="shared" si="10"/>
+        <v>44</v>
+      </c>
+      <c r="S23" s="8">
+        <f t="shared" si="15"/>
+        <v>0.55490552670504234</v>
+      </c>
+      <c r="T23" s="8">
+        <f t="shared" si="11"/>
+        <v>0.58265080304029448</v>
+      </c>
+      <c r="U23" s="8">
+        <f t="shared" si="12"/>
+        <v>0.61039607937554663</v>
+      </c>
+    </row>
+    <row r="24" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="20">
+        <v>400</v>
+      </c>
+      <c r="C24" s="21">
+        <v>49</v>
+      </c>
+      <c r="D24" s="22">
+        <v>51</v>
+      </c>
+      <c r="E24" s="21">
+        <v>54</v>
+      </c>
+      <c r="F24" s="22">
+        <v>47</v>
+      </c>
+      <c r="G24" s="22">
+        <v>49</v>
+      </c>
+      <c r="H24" s="21">
+        <v>52</v>
+      </c>
+      <c r="I24" s="22">
+        <v>51</v>
+      </c>
+      <c r="J24" s="22">
+        <v>54</v>
+      </c>
+      <c r="K24" s="37">
+        <v>56</v>
+      </c>
+      <c r="L24" s="22">
+        <v>52</v>
+      </c>
+      <c r="M24" s="22">
+        <v>55</v>
+      </c>
+      <c r="N24" s="37">
+        <v>57</v>
+      </c>
+      <c r="O24" s="2">
+        <f t="shared" si="13"/>
+        <v>89.442719099991592</v>
+      </c>
+      <c r="P24" s="2">
+        <f t="shared" si="14"/>
+        <v>49.75</v>
+      </c>
+      <c r="Q24" s="2">
+        <f t="shared" si="9"/>
+        <v>52.25</v>
+      </c>
+      <c r="R24" s="2">
+        <f t="shared" si="10"/>
+        <v>54.75</v>
+      </c>
+      <c r="S24" s="8">
+        <f t="shared" si="15"/>
+        <v>0.5562219094030727</v>
+      </c>
+      <c r="T24" s="8">
+        <f t="shared" si="11"/>
+        <v>0.58417275912181998</v>
+      </c>
+      <c r="U24" s="8">
+        <f t="shared" si="12"/>
+        <v>0.61212360884056738</v>
+      </c>
+    </row>
+    <row r="25" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B25" s="20">
+        <v>500</v>
+      </c>
+      <c r="C25" s="21">
+        <v>58</v>
+      </c>
+      <c r="D25" s="22">
+        <v>61</v>
+      </c>
+      <c r="E25" s="21">
+        <v>64</v>
+      </c>
+      <c r="F25" s="22">
+        <v>55</v>
+      </c>
+      <c r="G25" s="22">
+        <v>58</v>
+      </c>
+      <c r="H25" s="21">
+        <v>61</v>
+      </c>
+      <c r="I25" s="22">
+        <v>60</v>
+      </c>
+      <c r="J25" s="22">
+        <v>63</v>
+      </c>
+      <c r="K25" s="37">
+        <v>66</v>
+      </c>
+      <c r="L25" s="22">
+        <v>61</v>
+      </c>
+      <c r="M25" s="22">
+        <v>64</v>
+      </c>
+      <c r="N25" s="37">
+        <v>67</v>
+      </c>
+      <c r="O25" s="2">
+        <f t="shared" si="13"/>
+        <v>105.73712634405643</v>
+      </c>
+      <c r="P25" s="2">
+        <f t="shared" si="14"/>
+        <v>58.5</v>
+      </c>
+      <c r="Q25" s="2">
+        <f t="shared" si="9"/>
+        <v>61.5</v>
+      </c>
+      <c r="R25" s="2">
+        <f t="shared" si="10"/>
+        <v>64.5</v>
+      </c>
+      <c r="S25" s="8">
+        <f t="shared" si="15"/>
+        <v>0.55325884126685776</v>
+      </c>
+      <c r="T25" s="8">
+        <f t="shared" si="11"/>
+        <v>0.58163108953695297</v>
+      </c>
+      <c r="U25" s="8">
+        <f t="shared" si="12"/>
+        <v>0.6100033378070483</v>
+      </c>
+    </row>
+    <row r="26" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B26" s="20">
+        <v>600</v>
+      </c>
+      <c r="C26" s="21">
+        <v>66</v>
+      </c>
+      <c r="D26" s="22">
+        <v>69</v>
+      </c>
+      <c r="E26" s="21">
+        <v>73</v>
+      </c>
+      <c r="F26" s="22">
+        <v>63</v>
+      </c>
+      <c r="G26" s="22">
+        <v>66</v>
+      </c>
+      <c r="H26" s="21">
+        <v>69</v>
+      </c>
+      <c r="I26" s="22">
+        <v>69</v>
+      </c>
+      <c r="J26" s="22">
+        <v>72</v>
+      </c>
+      <c r="K26" s="37">
+        <v>76</v>
+      </c>
+      <c r="L26" s="22">
+        <v>70</v>
+      </c>
+      <c r="M26" s="22">
+        <v>74</v>
+      </c>
+      <c r="N26" s="37">
+        <v>77</v>
+      </c>
+      <c r="O26" s="2">
+        <f t="shared" si="13"/>
+        <v>121.23093028059735</v>
+      </c>
+      <c r="P26" s="2">
+        <f t="shared" si="14"/>
+        <v>67</v>
+      </c>
+      <c r="Q26" s="2">
+        <f t="shared" si="9"/>
+        <v>70.25</v>
+      </c>
+      <c r="R26" s="2">
+        <f t="shared" si="10"/>
+        <v>73.75</v>
+      </c>
+      <c r="S26" s="8">
+        <f t="shared" si="15"/>
+        <v>0.55266424042877405</v>
+      </c>
+      <c r="T26" s="8">
+        <f t="shared" si="11"/>
+        <v>0.57947258044957284</v>
+      </c>
+      <c r="U26" s="8">
+        <f t="shared" si="12"/>
+        <v>0.60834310047197149</v>
+      </c>
+    </row>
+    <row r="27" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B27" s="20">
+        <v>700</v>
+      </c>
+      <c r="C27" s="21">
+        <v>75</v>
+      </c>
+      <c r="D27" s="22">
+        <v>79</v>
+      </c>
+      <c r="E27" s="21">
+        <v>83</v>
+      </c>
+      <c r="F27" s="22">
+        <v>71</v>
+      </c>
+      <c r="G27" s="22">
+        <v>75</v>
+      </c>
+      <c r="H27" s="21">
+        <v>78</v>
+      </c>
+      <c r="I27" s="22">
+        <v>78</v>
+      </c>
+      <c r="J27" s="22">
+        <v>82</v>
+      </c>
+      <c r="K27" s="37">
+        <v>86</v>
+      </c>
+      <c r="L27" s="22">
+        <v>79</v>
+      </c>
+      <c r="M27" s="22">
+        <v>83</v>
+      </c>
+      <c r="N27" s="37">
+        <v>87</v>
+      </c>
+      <c r="O27" s="2">
+        <f t="shared" si="13"/>
+        <v>136.0891589269774</v>
+      </c>
+      <c r="P27" s="2">
+        <f t="shared" si="14"/>
+        <v>75.75</v>
+      </c>
+      <c r="Q27" s="2">
+        <f t="shared" si="9"/>
+        <v>79.75</v>
+      </c>
+      <c r="R27" s="2">
+        <f t="shared" si="10"/>
+        <v>83.5</v>
+      </c>
+      <c r="S27" s="8">
+        <f t="shared" si="15"/>
+        <v>0.55662038473355446</v>
+      </c>
+      <c r="T27" s="8">
+        <f t="shared" si="11"/>
+        <v>0.58601288029704246</v>
+      </c>
+      <c r="U27" s="8">
+        <f t="shared" si="12"/>
+        <v>0.61356834488781253</v>
+      </c>
+    </row>
+    <row r="28" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B28" s="23">
+        <v>800</v>
+      </c>
+      <c r="C28" s="24">
+        <v>82</v>
+      </c>
+      <c r="D28" s="25">
+        <v>86</v>
+      </c>
+      <c r="E28" s="24">
+        <v>90</v>
+      </c>
+      <c r="F28" s="25">
+        <v>78</v>
+      </c>
+      <c r="G28" s="25">
+        <v>82</v>
+      </c>
+      <c r="H28" s="24">
+        <v>86</v>
+      </c>
+      <c r="I28" s="25">
+        <v>86</v>
+      </c>
+      <c r="J28" s="25">
+        <v>90</v>
+      </c>
+      <c r="K28" s="38">
+        <v>95</v>
+      </c>
+      <c r="L28" s="25">
+        <v>87</v>
+      </c>
+      <c r="M28" s="25">
+        <v>91</v>
+      </c>
+      <c r="N28" s="38">
+        <v>96</v>
+      </c>
+      <c r="O28" s="2">
+        <f t="shared" si="13"/>
+        <v>150.42412372345569</v>
+      </c>
+      <c r="P28" s="2">
+        <f t="shared" si="14"/>
+        <v>83.25</v>
+      </c>
+      <c r="Q28" s="2">
+        <f t="shared" si="9"/>
+        <v>87.25</v>
+      </c>
+      <c r="R28" s="2">
+        <f t="shared" si="10"/>
+        <v>91.75</v>
+      </c>
+      <c r="S28" s="8">
+        <f t="shared" si="15"/>
+        <v>0.55343516677583804</v>
+      </c>
+      <c r="T28" s="8">
+        <f t="shared" si="11"/>
+        <v>0.58002664626056299</v>
+      </c>
+      <c r="U28" s="8">
+        <f t="shared" si="12"/>
+        <v>0.60994206068087853</v>
+      </c>
+    </row>
+    <row r="29" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="P29" s="9"/>
+      <c r="Q29" s="9"/>
+      <c r="R29" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="S29" s="27">
+        <f>AVERAGE(S21:S28)</f>
+        <v>0.55341099024030349</v>
+      </c>
+      <c r="T29" s="27">
+        <f t="shared" ref="T29:U29" si="16">AVERAGE(T21:T28)</f>
+        <v>0.58174698888942067</v>
+      </c>
+      <c r="U29" s="27">
+        <f t="shared" si="16"/>
+        <v>0.6105266230340971</v>
+      </c>
+    </row>
+    <row r="30" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="R30" t="s">
+        <v>53</v>
+      </c>
+      <c r="S30" s="8">
+        <f>_xlfn.STDEV.P(S21:S28)</f>
+        <v>3.2662267098387964E-3</v>
+      </c>
+      <c r="T30" s="8">
+        <f t="shared" ref="T30:U30" si="17">_xlfn.STDEV.P(T21:T28)</f>
+        <v>2.6412247044506464E-3</v>
+      </c>
+      <c r="U30" s="8">
+        <f t="shared" si="17"/>
+        <v>1.6096128196383399E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="B17:O18"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="B3:O3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="L4:N4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/data/prod_parameters/HorseHerd.xlsx
+++ b/data/prod_parameters/HorseHerd.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="default" sheetId="1" r:id="rId1"/>
-    <sheet name="ME req young horses" sheetId="2" r:id="rId2"/>
+    <sheet name="Feed rations" sheetId="3" r:id="rId2"/>
+    <sheet name="ME req young horses" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="86">
   <si>
     <t>f_breed</t>
   </si>
@@ -191,6 +192,93 @@
   </si>
   <si>
     <t>No activity adjustment</t>
+  </si>
+  <si>
+    <t>Assumes lower activity than "lätt träning" but some</t>
+  </si>
+  <si>
+    <t>breed</t>
+  </si>
+  <si>
+    <t>animal</t>
+  </si>
+  <si>
+    <t>Roughage</t>
+  </si>
+  <si>
+    <t>Concentrates</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>From feed industry statistics (2011)</t>
+  </si>
+  <si>
+    <t>Havre</t>
+  </si>
+  <si>
+    <t>Kli av skalad havre</t>
+  </si>
+  <si>
+    <t>Havreskal med kli</t>
+  </si>
+  <si>
+    <t>Korn</t>
+  </si>
+  <si>
+    <t>Vete</t>
+  </si>
+  <si>
+    <t>Vetefodermjöl</t>
+  </si>
+  <si>
+    <t>Vetekli</t>
+  </si>
+  <si>
+    <t>Vegetabilisk olja</t>
+  </si>
+  <si>
+    <t>(socker)betmassa</t>
+  </si>
+  <si>
+    <t>(socker)betmelass</t>
+  </si>
+  <si>
+    <t>Melasserad pressmassa</t>
+  </si>
+  <si>
+    <t>Potatisprotein</t>
+  </si>
+  <si>
+    <t>Lussernmjöl</t>
+  </si>
+  <si>
+    <t>Grönmjöl</t>
+  </si>
+  <si>
+    <t>Kalciumkarbonat</t>
+  </si>
+  <si>
+    <t>Koksalt</t>
+  </si>
+  <si>
+    <t>SE</t>
+  </si>
+  <si>
+    <t>INF</t>
+  </si>
+  <si>
+    <t>% av totalen</t>
+  </si>
+  <si>
+    <t>% imported</t>
+  </si>
+  <si>
+    <t>% of TOTAL</t>
+  </si>
+  <si>
+    <t>Need to add the concentrates!</t>
   </si>
 </sst>
 </file>
@@ -201,7 +289,7 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -280,6 +368,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -322,10 +417,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -388,6 +484,20 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" indent="2" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" indent="2" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" indent="2" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -403,21 +513,15 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" indent="2" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" indent="2" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" indent="2" shrinkToFit="1"/>
-    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3140,7 +3244,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.85546875" bestFit="1" customWidth="1"/>
@@ -3562,10 +3666,10 @@
         <v>24</v>
       </c>
       <c r="F27" s="9">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -3610,6 +3714,9 @@
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C32" t="s">
+        <v>9</v>
+      </c>
       <c r="D32" t="s">
         <v>49</v>
       </c>
@@ -3617,12 +3724,15 @@
         <v>45</v>
       </c>
       <c r="F32" s="2">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="G32" s="29"/>
       <c r="H32" s="29"/>
     </row>
-    <row r="33" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C33" s="42" t="s">
+        <v>9</v>
+      </c>
       <c r="D33" t="s">
         <v>50</v>
       </c>
@@ -3630,7 +3740,96 @@
         <v>45</v>
       </c>
       <c r="F33">
-        <v>20</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C34" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="E34" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="F34" s="43">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C35" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="F35" s="42">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C36" t="s">
+        <v>4</v>
+      </c>
+      <c r="D36" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="E36" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="F36" s="43">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C37" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="D37" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="E37" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="F37" s="42">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C38" t="s">
+        <v>5</v>
+      </c>
+      <c r="D38" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="E38" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="F38" s="43">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C39" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="D39" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="E39" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="F39" s="42">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -3641,29 +3840,1014 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="C1:X62"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="E1" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="E2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="41">
+        <f>1-H4</f>
+        <v>0.99</v>
+      </c>
+      <c r="F4" s="41">
+        <f>1-G4</f>
+        <v>0.66666666666666674</v>
+      </c>
+      <c r="G4" s="44">
+        <f>(3+2*0.5)/12</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="H4" s="41">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="41">
+        <f t="shared" ref="E5:E19" si="0">1-H5</f>
+        <v>0.98</v>
+      </c>
+      <c r="F5" s="45">
+        <f t="shared" ref="F5:F19" si="1">1-G5</f>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="G5" s="44">
+        <f>(3*0.5+2*0.25)/12</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="H5" s="41">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="41">
+        <f t="shared" si="0"/>
+        <v>0.92999999999999994</v>
+      </c>
+      <c r="F6" s="45">
+        <f t="shared" si="1"/>
+        <v>0.66666666666666674</v>
+      </c>
+      <c r="G6" s="44">
+        <f>(3+2*0.5)/12</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="H6" s="41">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="41">
+        <f t="shared" si="0"/>
+        <v>0.92</v>
+      </c>
+      <c r="F7" s="45">
+        <f t="shared" si="1"/>
+        <v>0.66666666666666674</v>
+      </c>
+      <c r="G7" s="44">
+        <f>(3+2*0.5)/12</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="H7" s="41">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="8" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="41">
+        <f t="shared" si="0"/>
+        <v>0.99</v>
+      </c>
+      <c r="F8" s="45">
+        <f>1-G8</f>
+        <v>0.66666666666666674</v>
+      </c>
+      <c r="G8" s="44">
+        <f>(3+2*0.5)/12</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="H8" s="41">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="9" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="41">
+        <f t="shared" si="0"/>
+        <v>0.98</v>
+      </c>
+      <c r="F9" s="45">
+        <f t="shared" si="1"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="G9" s="44">
+        <f>(3*0.5+2*0.25)/12</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="H9" s="41">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="41">
+        <f t="shared" si="0"/>
+        <v>0.92999999999999994</v>
+      </c>
+      <c r="F10" s="45">
+        <f t="shared" si="1"/>
+        <v>0.66666666666666674</v>
+      </c>
+      <c r="G10" s="44">
+        <f>(3+2*0.5)/12</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="H10" s="41">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="41">
+        <f t="shared" si="0"/>
+        <v>0.97</v>
+      </c>
+      <c r="F11" s="45">
+        <f t="shared" si="1"/>
+        <v>0.66666666666666674</v>
+      </c>
+      <c r="G11" s="44">
+        <f>(3+2*0.5)/12</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="H11" s="41">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="12" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="41">
+        <f t="shared" si="0"/>
+        <v>0.99</v>
+      </c>
+      <c r="F12" s="45">
+        <f>1-G12</f>
+        <v>0.66666666666666674</v>
+      </c>
+      <c r="G12" s="44">
+        <f>(3+2*0.5)/12</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="H12" s="41">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="13" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="41">
+        <f t="shared" si="0"/>
+        <v>0.96</v>
+      </c>
+      <c r="F13" s="45">
+        <f t="shared" si="1"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="G13" s="44">
+        <f>(3*0.5+2*0.25)/12</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="H13" s="41">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="14" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="D14" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="41">
+        <f t="shared" si="0"/>
+        <v>0.92999999999999994</v>
+      </c>
+      <c r="F14" s="45">
+        <f t="shared" si="1"/>
+        <v>0.66666666666666674</v>
+      </c>
+      <c r="G14" s="44">
+        <f>(3+2*0.5)/12</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="H14" s="41">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="D15" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" s="41">
+        <f t="shared" si="0"/>
+        <v>0.95</v>
+      </c>
+      <c r="F15" s="45">
+        <f t="shared" si="1"/>
+        <v>0.66666666666666674</v>
+      </c>
+      <c r="G15" s="44">
+        <f>(3+2*0.5)/12</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="H15" s="41">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="16" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="41">
+        <f t="shared" si="0"/>
+        <v>0.94</v>
+      </c>
+      <c r="F16" s="45">
+        <f>1-G16</f>
+        <v>0.66666666666666674</v>
+      </c>
+      <c r="G16" s="44">
+        <f>(3+2*0.5)/12</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="H16" s="41">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="17" spans="4:24" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="41">
+        <f t="shared" si="0"/>
+        <v>0.89</v>
+      </c>
+      <c r="F17" s="45">
+        <f t="shared" si="1"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="G17" s="44">
+        <f>(3*0.5+2*0.25)/12</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="H17" s="41">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="18" spans="4:24" x14ac:dyDescent="0.25">
+      <c r="D18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="41">
+        <f t="shared" si="0"/>
+        <v>0.9</v>
+      </c>
+      <c r="F18" s="45">
+        <f t="shared" si="1"/>
+        <v>0.66666666666666674</v>
+      </c>
+      <c r="G18" s="44">
+        <f>(3+2*0.5)/12</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="H18" s="41">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="19" spans="4:24" x14ac:dyDescent="0.25">
+      <c r="D19" t="s">
+        <v>5</v>
+      </c>
+      <c r="E19" s="41">
+        <f t="shared" si="0"/>
+        <v>0.88</v>
+      </c>
+      <c r="F19" s="45">
+        <f t="shared" si="1"/>
+        <v>0.66666666666666674</v>
+      </c>
+      <c r="G19" s="44">
+        <f>(3+2*0.5)/12</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="H19" s="41">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="21" spans="4:24" x14ac:dyDescent="0.25">
+      <c r="G21" s="34" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="4:24" x14ac:dyDescent="0.25">
+      <c r="H22" t="s">
+        <v>62</v>
+      </c>
+      <c r="I22" t="s">
+        <v>64</v>
+      </c>
+      <c r="J22" t="s">
+        <v>67</v>
+      </c>
+      <c r="K22" t="s">
+        <v>68</v>
+      </c>
+      <c r="L22" t="s">
+        <v>65</v>
+      </c>
+      <c r="M22" t="s">
+        <v>66</v>
+      </c>
+      <c r="N22" t="s">
+        <v>69</v>
+      </c>
+      <c r="O22" t="s">
+        <v>70</v>
+      </c>
+      <c r="P22" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>72</v>
+      </c>
+      <c r="R22" t="s">
+        <v>73</v>
+      </c>
+      <c r="S22" t="s">
+        <v>74</v>
+      </c>
+      <c r="T22" t="s">
+        <v>75</v>
+      </c>
+      <c r="U22" t="s">
+        <v>76</v>
+      </c>
+      <c r="V22" t="s">
+        <v>77</v>
+      </c>
+      <c r="W22" t="s">
+        <v>78</v>
+      </c>
+      <c r="X22" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="4:24" x14ac:dyDescent="0.25">
+      <c r="G23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H23">
+        <f>SUM(I23:X23)</f>
+        <v>37089.040000000001</v>
+      </c>
+      <c r="I23">
+        <v>8697.39</v>
+      </c>
+      <c r="J23">
+        <v>2726.58</v>
+      </c>
+      <c r="K23">
+        <v>4044.63</v>
+      </c>
+      <c r="L23">
+        <v>637.71</v>
+      </c>
+      <c r="M23">
+        <v>3923.7</v>
+      </c>
+      <c r="N23">
+        <v>968.31</v>
+      </c>
+      <c r="O23">
+        <v>5403.57</v>
+      </c>
+      <c r="P23">
+        <v>472</v>
+      </c>
+      <c r="Q23">
+        <v>789.30000000000007</v>
+      </c>
+      <c r="R23">
+        <v>1494</v>
+      </c>
+      <c r="S23">
+        <v>1555.9499999999998</v>
+      </c>
+      <c r="T23">
+        <v>607.5</v>
+      </c>
+      <c r="U23">
+        <v>2255.4</v>
+      </c>
+      <c r="V23">
+        <v>1607</v>
+      </c>
+      <c r="W23">
+        <v>1251</v>
+      </c>
+      <c r="X23">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="24" spans="4:24" x14ac:dyDescent="0.25">
+      <c r="G24" t="s">
+        <v>81</v>
+      </c>
+      <c r="H24">
+        <f>SUM(I24:X24)</f>
+        <v>3742.5450000000001</v>
+      </c>
+      <c r="I24">
+        <v>142.68</v>
+      </c>
+      <c r="J24">
+        <v>261.87</v>
+      </c>
+      <c r="K24">
+        <v>90.48</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>26.97</v>
+      </c>
+      <c r="O24">
+        <v>0.87</v>
+      </c>
+      <c r="P24">
+        <v>158</v>
+      </c>
+      <c r="Q24">
+        <v>1229.4000000000001</v>
+      </c>
+      <c r="R24">
+        <v>55.5</v>
+      </c>
+      <c r="S24">
+        <v>711.97499999999991</v>
+      </c>
+      <c r="T24">
+        <v>13.5</v>
+      </c>
+      <c r="U24">
+        <v>591.30000000000007</v>
+      </c>
+      <c r="V24">
+        <v>367</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="25" spans="4:24" x14ac:dyDescent="0.25">
+      <c r="G25" t="s">
+        <v>84</v>
+      </c>
+      <c r="H25" s="35">
+        <f t="shared" ref="H25:X25" si="2">SUM(H23:H24)/SUM($H23:$H24)</f>
+        <v>1</v>
+      </c>
+      <c r="I25" s="35">
+        <f t="shared" si="2"/>
+        <v>0.21650077997217104</v>
+      </c>
+      <c r="J25" s="35">
+        <f t="shared" si="2"/>
+        <v>7.318966432481129E-2</v>
+      </c>
+      <c r="K25" s="35">
+        <f t="shared" si="2"/>
+        <v>0.10127233610941137</v>
+      </c>
+      <c r="L25" s="35">
+        <f t="shared" si="2"/>
+        <v>1.5618056462907332E-2</v>
+      </c>
+      <c r="M25" s="35">
+        <f t="shared" si="2"/>
+        <v>9.609472666809285E-2</v>
+      </c>
+      <c r="N25" s="35">
+        <f t="shared" si="2"/>
+        <v>2.4375247740199162E-2</v>
+      </c>
+      <c r="O25" s="35">
+        <f t="shared" si="2"/>
+        <v>0.13235929979206049</v>
+      </c>
+      <c r="P25" s="35">
+        <f t="shared" si="2"/>
+        <v>1.5429232051609067E-2</v>
+      </c>
+      <c r="Q25" s="35">
+        <f t="shared" si="2"/>
+        <v>4.9439667845370204E-2</v>
+      </c>
+      <c r="R25" s="35">
+        <f t="shared" si="2"/>
+        <v>3.7948563593600396E-2</v>
+      </c>
+      <c r="S25" s="35">
+        <f t="shared" si="2"/>
+        <v>5.5543398572453155E-2</v>
+      </c>
+      <c r="T25" s="35">
+        <f t="shared" si="2"/>
+        <v>1.5208814450871794E-2</v>
+      </c>
+      <c r="U25" s="35">
+        <f t="shared" si="2"/>
+        <v>6.9718087113199267E-2</v>
+      </c>
+      <c r="V25" s="35">
+        <f t="shared" si="2"/>
+        <v>4.8344927095041741E-2</v>
+      </c>
+      <c r="W25" s="35">
+        <f t="shared" si="2"/>
+        <v>3.0638046502480861E-2</v>
+      </c>
+      <c r="X25" s="35">
+        <f t="shared" si="2"/>
+        <v>1.8319151705719971E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="4:24" x14ac:dyDescent="0.25">
+      <c r="G26" t="s">
+        <v>83</v>
+      </c>
+      <c r="H26" s="35">
+        <f>H24/SUM(H23:H24)</f>
+        <v>9.165808772791946E-2</v>
+      </c>
+      <c r="I26" s="35">
+        <f>I24/SUM(I23:I24)</f>
+        <v>1.6140143686645018E-2</v>
+      </c>
+      <c r="J26" s="35">
+        <f>J24/SUM(J23:J24)</f>
+        <v>8.7627365356623008E-2</v>
+      </c>
+      <c r="K26" s="35">
+        <f>K24/SUM(K23:K24)</f>
+        <v>2.1880917315379764E-2</v>
+      </c>
+      <c r="L26" s="35">
+        <f t="shared" ref="L26:M26" si="3">L24/SUM(L23:L24)</f>
+        <v>0</v>
+      </c>
+      <c r="M26" s="35">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N26" s="35">
+        <f t="shared" ref="N26:X26" si="4">N24/SUM(N23:N24)</f>
+        <v>2.7097902097902096E-2</v>
+      </c>
+      <c r="O26" s="35">
+        <f t="shared" si="4"/>
+        <v>1.6097875080489378E-4</v>
+      </c>
+      <c r="P26" s="35">
+        <f t="shared" si="4"/>
+        <v>0.25079365079365079</v>
+      </c>
+      <c r="Q26" s="35">
+        <f t="shared" si="4"/>
+        <v>0.60900579580918413</v>
+      </c>
+      <c r="R26" s="35">
+        <f t="shared" si="4"/>
+        <v>3.5818005808325268E-2</v>
+      </c>
+      <c r="S26" s="35">
+        <f t="shared" si="4"/>
+        <v>0.31393233903237538</v>
+      </c>
+      <c r="T26" s="35">
+        <f t="shared" si="4"/>
+        <v>2.1739130434782608E-2</v>
+      </c>
+      <c r="U26" s="35">
+        <f t="shared" si="4"/>
+        <v>0.207714195384129</v>
+      </c>
+      <c r="V26" s="35">
+        <f t="shared" si="4"/>
+        <v>0.18591691995947315</v>
+      </c>
+      <c r="W26" s="35">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X26" s="35">
+        <f t="shared" si="4"/>
+        <v>0.12433155080213903</v>
+      </c>
+    </row>
+    <row r="46" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="F46" t="s">
+        <v>80</v>
+      </c>
+      <c r="G46" t="s">
+        <v>81</v>
+      </c>
+      <c r="H46" t="s">
+        <v>82</v>
+      </c>
+      <c r="J46" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="47" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E47" t="s">
+        <v>64</v>
+      </c>
+      <c r="F47">
+        <v>8697.39</v>
+      </c>
+      <c r="G47">
+        <v>142.68</v>
+      </c>
+      <c r="H47">
+        <v>0.21650077997217101</v>
+      </c>
+      <c r="J47">
+        <v>1.6140143686645018E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E48" t="s">
+        <v>65</v>
+      </c>
+      <c r="F48">
+        <v>637.71</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>1.5618056462907329E-2</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E49" t="s">
+        <v>66</v>
+      </c>
+      <c r="F49">
+        <v>3923.7</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>9.6094726668092836E-2</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E50" t="s">
+        <v>67</v>
+      </c>
+      <c r="F50">
+        <v>2726.58</v>
+      </c>
+      <c r="G50">
+        <v>261.87</v>
+      </c>
+      <c r="H50">
+        <v>7.3189664324811277E-2</v>
+      </c>
+      <c r="J50">
+        <v>8.7627365356623008E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E51" t="s">
+        <v>68</v>
+      </c>
+      <c r="F51">
+        <v>4044.63</v>
+      </c>
+      <c r="G51">
+        <v>90.48</v>
+      </c>
+      <c r="H51">
+        <v>0.10127233610941136</v>
+      </c>
+      <c r="J51">
+        <v>2.1880917315379764E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E52" t="s">
+        <v>69</v>
+      </c>
+      <c r="F52">
+        <v>968.31</v>
+      </c>
+      <c r="G52">
+        <v>26.97</v>
+      </c>
+      <c r="H52">
+        <v>2.4375247740199158E-2</v>
+      </c>
+      <c r="J52">
+        <v>2.7097902097902096E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E53" t="s">
+        <v>70</v>
+      </c>
+      <c r="F53">
+        <v>5403.57</v>
+      </c>
+      <c r="G53">
+        <v>0.87</v>
+      </c>
+      <c r="H53">
+        <v>0.13235929979206046</v>
+      </c>
+      <c r="J53">
+        <v>1.6097875080489378E-4</v>
+      </c>
+    </row>
+    <row r="54" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E54" t="s">
+        <v>71</v>
+      </c>
+      <c r="F54">
+        <v>472</v>
+      </c>
+      <c r="G54">
+        <v>158</v>
+      </c>
+      <c r="H54">
+        <v>1.5429232051609065E-2</v>
+      </c>
+      <c r="J54">
+        <v>0.25079365079365079</v>
+      </c>
+    </row>
+    <row r="55" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E55" t="s">
+        <v>72</v>
+      </c>
+      <c r="F55">
+        <v>789.30000000000007</v>
+      </c>
+      <c r="G55">
+        <v>1229.4000000000001</v>
+      </c>
+      <c r="H55">
+        <v>4.9439667845370197E-2</v>
+      </c>
+      <c r="J55">
+        <v>0.60900579580918413</v>
+      </c>
+    </row>
+    <row r="56" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E56" t="s">
+        <v>73</v>
+      </c>
+      <c r="F56">
+        <v>1494</v>
+      </c>
+      <c r="G56">
+        <v>55.5</v>
+      </c>
+      <c r="H56">
+        <v>3.7948563593600389E-2</v>
+      </c>
+      <c r="J56">
+        <v>3.5818005808325268E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E57" t="s">
+        <v>74</v>
+      </c>
+      <c r="F57">
+        <v>1555.9499999999998</v>
+      </c>
+      <c r="G57">
+        <v>711.97499999999991</v>
+      </c>
+      <c r="H57">
+        <v>5.5543398572453148E-2</v>
+      </c>
+      <c r="J57">
+        <v>0.31393233903237538</v>
+      </c>
+    </row>
+    <row r="58" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E58" t="s">
+        <v>75</v>
+      </c>
+      <c r="F58">
+        <v>607.5</v>
+      </c>
+      <c r="G58">
+        <v>13.5</v>
+      </c>
+      <c r="H58">
+        <v>1.5208814450871792E-2</v>
+      </c>
+      <c r="J58">
+        <v>2.1739130434782608E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E59" t="s">
+        <v>76</v>
+      </c>
+      <c r="F59">
+        <v>2255.4</v>
+      </c>
+      <c r="G59">
+        <v>591.30000000000007</v>
+      </c>
+      <c r="H59">
+        <v>6.9718087113199254E-2</v>
+      </c>
+      <c r="J59">
+        <v>0.207714195384129</v>
+      </c>
+    </row>
+    <row r="60" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E60" t="s">
+        <v>77</v>
+      </c>
+      <c r="F60">
+        <v>1607</v>
+      </c>
+      <c r="G60">
+        <v>367</v>
+      </c>
+      <c r="H60">
+        <v>4.8344927095041734E-2</v>
+      </c>
+      <c r="J60">
+        <v>0.18591691995947315</v>
+      </c>
+    </row>
+    <row r="61" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E61" t="s">
+        <v>78</v>
+      </c>
+      <c r="F61">
+        <v>1251</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>3.0638046502480858E-2</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E62" t="s">
+        <v>79</v>
+      </c>
+      <c r="F62">
+        <v>655</v>
+      </c>
+      <c r="G62">
+        <v>93</v>
+      </c>
+      <c r="H62">
+        <v>1.8319151705719967E-2</v>
+      </c>
+      <c r="J62">
+        <v>0.12433155080213903</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:U30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="3" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30"/>
-      <c r="N3" s="30"/>
-      <c r="O3" s="30"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="36"/>
+      <c r="L3" s="36"/>
+      <c r="M3" s="36"/>
+      <c r="N3" s="36"/>
+      <c r="O3" s="36"/>
     </row>
     <row r="4" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="37" t="s">
         <v>33</v>
       </c>
       <c r="C4" s="11"/>
@@ -3671,25 +4855,25 @@
         <v>34</v>
       </c>
       <c r="E4" s="11"/>
-      <c r="F4" s="33" t="s">
+      <c r="F4" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="33"/>
+      <c r="G4" s="39"/>
       <c r="H4" s="11"/>
-      <c r="I4" s="33" t="s">
+      <c r="I4" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="J4" s="33"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="33" t="s">
+      <c r="J4" s="39"/>
+      <c r="K4" s="39"/>
+      <c r="L4" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="M4" s="33"/>
-      <c r="N4" s="33"/>
+      <c r="M4" s="39"/>
+      <c r="N4" s="39"/>
       <c r="O4" s="13"/>
     </row>
     <row r="5" spans="2:21" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B5" s="32"/>
+      <c r="B5" s="38"/>
       <c r="C5" s="14" t="s">
         <v>38</v>
       </c>
@@ -4337,41 +5521,41 @@
       </c>
     </row>
     <row r="17" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B17" s="34" t="s">
+      <c r="B17" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="34"/>
-      <c r="J17" s="34"/>
-      <c r="K17" s="34"/>
-      <c r="L17" s="34"/>
-      <c r="M17" s="34"/>
-      <c r="N17" s="34"/>
-      <c r="O17" s="34"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="40"/>
+      <c r="I17" s="40"/>
+      <c r="J17" s="40"/>
+      <c r="K17" s="40"/>
+      <c r="L17" s="40"/>
+      <c r="M17" s="40"/>
+      <c r="N17" s="40"/>
+      <c r="O17" s="40"/>
     </row>
     <row r="18" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B18" s="34"/>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="34"/>
-      <c r="H18" s="34"/>
-      <c r="I18" s="34"/>
-      <c r="J18" s="34"/>
-      <c r="K18" s="34"/>
-      <c r="L18" s="34"/>
-      <c r="M18" s="34"/>
-      <c r="N18" s="34"/>
-      <c r="O18" s="34"/>
+      <c r="B18" s="40"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="40"/>
+      <c r="K18" s="40"/>
+      <c r="L18" s="40"/>
+      <c r="M18" s="40"/>
+      <c r="N18" s="40"/>
+      <c r="O18" s="40"/>
     </row>
     <row r="19" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B19" s="31" t="s">
+      <c r="B19" s="37" t="s">
         <v>33</v>
       </c>
       <c r="C19" s="11"/>
@@ -4379,25 +5563,25 @@
         <v>34</v>
       </c>
       <c r="E19" s="11"/>
-      <c r="F19" s="33" t="s">
+      <c r="F19" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="G19" s="33"/>
+      <c r="G19" s="39"/>
       <c r="H19" s="11"/>
-      <c r="I19" s="33" t="s">
+      <c r="I19" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="J19" s="33"/>
-      <c r="K19" s="33"/>
-      <c r="L19" s="33" t="s">
+      <c r="J19" s="39"/>
+      <c r="K19" s="39"/>
+      <c r="L19" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="M19" s="33"/>
-      <c r="N19" s="33"/>
+      <c r="M19" s="39"/>
+      <c r="N19" s="39"/>
       <c r="O19" s="13"/>
     </row>
     <row r="20" spans="2:21" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B20" s="32"/>
+      <c r="B20" s="38"/>
       <c r="C20" s="14" t="s">
         <v>38</v>
       </c>
@@ -4422,7 +5606,7 @@
       <c r="J20" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="K20" s="35" t="s">
+      <c r="K20" s="30" t="s">
         <v>40</v>
       </c>
       <c r="L20" s="14" t="s">
@@ -4431,7 +5615,7 @@
       <c r="M20" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="N20" s="35" t="s">
+      <c r="N20" s="30" t="s">
         <v>40</v>
       </c>
       <c r="O20" s="26" t="s">
@@ -4484,7 +5668,7 @@
       <c r="J21" s="19">
         <v>19</v>
       </c>
-      <c r="K21" s="36">
+      <c r="K21" s="31">
         <v>20</v>
       </c>
       <c r="L21" s="19">
@@ -4493,7 +5677,7 @@
       <c r="M21" s="19">
         <v>19</v>
       </c>
-      <c r="N21" s="36">
+      <c r="N21" s="31">
         <v>20</v>
       </c>
       <c r="O21" s="2">
@@ -4553,7 +5737,7 @@
       <c r="J22" s="22">
         <v>32</v>
       </c>
-      <c r="K22" s="37">
+      <c r="K22" s="32">
         <v>33</v>
       </c>
       <c r="L22" s="22">
@@ -4562,7 +5746,7 @@
       <c r="M22" s="22">
         <v>33</v>
       </c>
-      <c r="N22" s="37">
+      <c r="N22" s="32">
         <v>34</v>
       </c>
       <c r="O22" s="2">
@@ -4622,7 +5806,7 @@
       <c r="J23" s="22">
         <v>43</v>
       </c>
-      <c r="K23" s="37">
+      <c r="K23" s="32">
         <v>45</v>
       </c>
       <c r="L23" s="22">
@@ -4631,7 +5815,7 @@
       <c r="M23" s="22">
         <v>44</v>
       </c>
-      <c r="N23" s="37">
+      <c r="N23" s="32">
         <v>46</v>
       </c>
       <c r="O23" s="2">
@@ -4691,7 +5875,7 @@
       <c r="J24" s="22">
         <v>54</v>
       </c>
-      <c r="K24" s="37">
+      <c r="K24" s="32">
         <v>56</v>
       </c>
       <c r="L24" s="22">
@@ -4700,7 +5884,7 @@
       <c r="M24" s="22">
         <v>55</v>
       </c>
-      <c r="N24" s="37">
+      <c r="N24" s="32">
         <v>57</v>
       </c>
       <c r="O24" s="2">
@@ -4760,7 +5944,7 @@
       <c r="J25" s="22">
         <v>63</v>
       </c>
-      <c r="K25" s="37">
+      <c r="K25" s="32">
         <v>66</v>
       </c>
       <c r="L25" s="22">
@@ -4769,7 +5953,7 @@
       <c r="M25" s="22">
         <v>64</v>
       </c>
-      <c r="N25" s="37">
+      <c r="N25" s="32">
         <v>67</v>
       </c>
       <c r="O25" s="2">
@@ -4829,7 +6013,7 @@
       <c r="J26" s="22">
         <v>72</v>
       </c>
-      <c r="K26" s="37">
+      <c r="K26" s="32">
         <v>76</v>
       </c>
       <c r="L26" s="22">
@@ -4838,7 +6022,7 @@
       <c r="M26" s="22">
         <v>74</v>
       </c>
-      <c r="N26" s="37">
+      <c r="N26" s="32">
         <v>77</v>
       </c>
       <c r="O26" s="2">
@@ -4898,7 +6082,7 @@
       <c r="J27" s="22">
         <v>82</v>
       </c>
-      <c r="K27" s="37">
+      <c r="K27" s="32">
         <v>86</v>
       </c>
       <c r="L27" s="22">
@@ -4907,7 +6091,7 @@
       <c r="M27" s="22">
         <v>83</v>
       </c>
-      <c r="N27" s="37">
+      <c r="N27" s="32">
         <v>87</v>
       </c>
       <c r="O27" s="2">
@@ -4967,7 +6151,7 @@
       <c r="J28" s="25">
         <v>90</v>
       </c>
-      <c r="K28" s="38">
+      <c r="K28" s="33">
         <v>95</v>
       </c>
       <c r="L28" s="25">
@@ -4976,7 +6160,7 @@
       <c r="M28" s="25">
         <v>91</v>
       </c>
-      <c r="N28" s="38">
+      <c r="N28" s="33">
         <v>96</v>
       </c>
       <c r="O28" s="2">

--- a/data/prod_parameters/HorseHerd.xlsx
+++ b/data/prod_parameters/HorseHerd.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="98">
   <si>
     <t>f_breed</t>
   </si>
@@ -278,7 +278,43 @@
     <t>% of TOTAL</t>
   </si>
   <si>
-    <t>Need to add the concentrates!</t>
+    <t>hay of rough</t>
+  </si>
+  <si>
+    <t>grazing of rough</t>
+  </si>
+  <si>
+    <t>Total feed ration</t>
+  </si>
+  <si>
+    <t>oats</t>
+  </si>
+  <si>
+    <t>barley</t>
+  </si>
+  <si>
+    <t>wheat</t>
+  </si>
+  <si>
+    <t>wheat bran, fine</t>
+  </si>
+  <si>
+    <t>vegetable oils</t>
+  </si>
+  <si>
+    <t>wheat bran</t>
+  </si>
+  <si>
+    <t>sugar beet molasses</t>
+  </si>
+  <si>
+    <t>sugar beet pulp</t>
+  </si>
+  <si>
+    <t>potatoe protein</t>
+  </si>
+  <si>
+    <t>luzern meal</t>
   </si>
 </sst>
 </file>
@@ -498,8 +534,13 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
@@ -511,13 +552,8 @@
       <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3244,7 +3280,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I227"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.85546875" bestFit="1" customWidth="1"/>
@@ -3713,123 +3749,3844 @@
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C32" t="s">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D33" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="E32" t="s">
-        <v>45</v>
-      </c>
-      <c r="F32" s="2">
-        <v>67</v>
-      </c>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C33" s="42" t="s">
+      <c r="E33" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F33" s="9">
+        <f t="array" ref="F33">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A33='Feed rations'!$C$4:$C$19)*(C33='Feed rations'!$D$4:$D$19),0),
+MATCH(D33, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C34" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D34" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="E33" t="s">
-        <v>45</v>
-      </c>
-      <c r="F33">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C34" t="s">
+      <c r="E34" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F34" s="9">
+        <f t="array" ref="F34">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A34='Feed rations'!$C$4:$C$19)*(C34='Feed rations'!$D$4:$D$19),0),
+MATCH(D34, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>32.999999999999993</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C35" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="E35" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F35" s="9">
+        <f t="array" ref="F35">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A35='Feed rations'!$C$4:$C$19)*(C35='Feed rations'!$D$4:$D$19),0),
+MATCH(D35, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.22764567437372507</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C36" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="E36" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F36" s="9">
+        <f t="array" ref="F36">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A36='Feed rations'!$C$4:$C$19)*(C36='Feed rations'!$D$4:$D$19),0),
+MATCH(D36, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>7.6957276987869846E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C37" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="E37" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F37" s="9">
+        <f t="array" ref="F37">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A37='Feed rations'!$C$4:$C$19)*(C37='Feed rations'!$D$4:$D$19),0),
+MATCH(D37, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.10648557133139604</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C38" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="E38" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F38" s="9">
+        <f t="array" ref="F38">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A38='Feed rations'!$C$4:$C$19)*(C38='Feed rations'!$D$4:$D$19),0),
+MATCH(D38, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>2.5630021797415754E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C39" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="E39" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F39" s="9">
+        <f t="array" ref="F39">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A39='Feed rations'!$C$4:$C$19)*(C39='Feed rations'!$D$4:$D$19),0),
+MATCH(D39, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.25663627595227045</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C40" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="E40" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F40" s="9">
+        <f t="array" ref="F40">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A40='Feed rations'!$C$4:$C$19)*(C40='Feed rations'!$D$4:$D$19),0),
+MATCH(D40, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>1.6223488598557115E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C41" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="E41" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F41" s="9">
+        <f t="array" ref="F41">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A41='Feed rations'!$C$4:$C$19)*(C41='Feed rations'!$D$4:$D$19),0),
+MATCH(D41, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>8.1186006545791389E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="E42" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F42" s="9">
+        <f t="array" ref="F42">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A42='Feed rations'!$C$4:$C$19)*(C42='Feed rations'!$D$4:$D$19),0),
+MATCH(D42, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>6.9103370275246934E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C43" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="E43" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F43" s="9">
+        <f t="array" ref="F43">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A43='Feed rations'!$C$4:$C$19)*(C43='Feed rations'!$D$4:$D$19),0),
+MATCH(D43, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>1.5991724475720583E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C44" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="E44" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F44" s="9">
+        <f t="array" ref="F44">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A44='Feed rations'!$C$4:$C$19)*(C44='Feed rations'!$D$4:$D$19),0),
+MATCH(D44, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.12414058966200681</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C45" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="D34" s="42" t="s">
+      <c r="D45" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="E34" s="42" t="s">
-        <v>45</v>
-      </c>
-      <c r="F34" s="43">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C35" s="42" t="s">
+      <c r="E45" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F45" s="9">
+        <f t="array" ref="F45">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A45='Feed rations'!$C$4:$C$19)*(C45='Feed rations'!$D$4:$D$19),0),
+MATCH(D45, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>81.666666666666671</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C46" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="D35" s="42" t="s">
+      <c r="D46" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="E35" s="42" t="s">
-        <v>45</v>
-      </c>
-      <c r="F35" s="42">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C36" t="s">
+      <c r="E46" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F46" s="9">
+        <f t="array" ref="F46">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A46='Feed rations'!$C$4:$C$19)*(C46='Feed rations'!$D$4:$D$19),0),
+MATCH(D46, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>16.333333333333332</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C47" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D47" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="E47" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F47" s="9">
+        <f t="array" ref="F47">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A47='Feed rations'!$C$4:$C$19)*(C47='Feed rations'!$D$4:$D$19),0),
+MATCH(D47, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.45529134874745014</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C48" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="E48" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F48" s="9">
+        <f t="array" ref="F48">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A48='Feed rations'!$C$4:$C$19)*(C48='Feed rations'!$D$4:$D$19),0),
+MATCH(D48, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.15391455397573969</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C49" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D49" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="E49" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F49" s="9">
+        <f t="array" ref="F49">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A49='Feed rations'!$C$4:$C$19)*(C49='Feed rations'!$D$4:$D$19),0),
+MATCH(D49, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.21297114266279207</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C50" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D50" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="E50" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F50" s="9">
+        <f t="array" ref="F50">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A50='Feed rations'!$C$4:$C$19)*(C50='Feed rations'!$D$4:$D$19),0),
+MATCH(D50, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>5.1260043594831509E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C51" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D51" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="E51" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F51" s="9">
+        <f t="array" ref="F51">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A51='Feed rations'!$C$4:$C$19)*(C51='Feed rations'!$D$4:$D$19),0),
+MATCH(D51, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.51327255190454091</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C52" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="E52" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F52" s="9">
+        <f t="array" ref="F52">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A52='Feed rations'!$C$4:$C$19)*(C52='Feed rations'!$D$4:$D$19),0),
+MATCH(D52, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>3.244697719711423E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C53" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="E53" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F53" s="9">
+        <f t="array" ref="F53">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A53='Feed rations'!$C$4:$C$19)*(C53='Feed rations'!$D$4:$D$19),0),
+MATCH(D53, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.16237201309158278</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C54" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="E54" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F54" s="9">
+        <f t="array" ref="F54">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A54='Feed rations'!$C$4:$C$19)*(C54='Feed rations'!$D$4:$D$19),0),
+MATCH(D54, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.13820674055049387</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C55" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D55" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="E55" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F55" s="9">
+        <f t="array" ref="F55">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A55='Feed rations'!$C$4:$C$19)*(C55='Feed rations'!$D$4:$D$19),0),
+MATCH(D55, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>3.1983448951441167E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C56" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D56" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="E56" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F56" s="9">
+        <f t="array" ref="F56">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A56='Feed rations'!$C$4:$C$19)*(C56='Feed rations'!$D$4:$D$19),0),
+MATCH(D56, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.24828117932401361</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C57" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="D36" s="42" t="s">
+      <c r="D57" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="E36" s="42" t="s">
-        <v>45</v>
-      </c>
-      <c r="F36" s="43">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C37" s="42" t="s">
+      <c r="E57" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F57" s="9">
+        <f t="array" ref="F57">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A57='Feed rations'!$C$4:$C$19)*(C57='Feed rations'!$D$4:$D$19),0),
+MATCH(D57, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C58" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="D37" s="42" t="s">
+      <c r="D58" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="E37" s="42" t="s">
-        <v>45</v>
-      </c>
-      <c r="F37" s="42">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C38" t="s">
+      <c r="E58" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F58" s="9">
+        <f t="array" ref="F58">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A58='Feed rations'!$C$4:$C$19)*(C58='Feed rations'!$D$4:$D$19),0),
+MATCH(D58, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>30.999999999999993</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C59" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D59" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="E59" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F59" s="9">
+        <f t="array" ref="F59">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A59='Feed rations'!$C$4:$C$19)*(C59='Feed rations'!$D$4:$D$19),0),
+MATCH(D59, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>1.5935197206160754</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C60" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D60" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="E60" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F60" s="9">
+        <f t="array" ref="F60">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A60='Feed rations'!$C$4:$C$19)*(C60='Feed rations'!$D$4:$D$19),0),
+MATCH(D60, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.53870093891508897</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C61" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D61" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="E61" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F61" s="9">
+        <f t="array" ref="F61">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A61='Feed rations'!$C$4:$C$19)*(C61='Feed rations'!$D$4:$D$19),0),
+MATCH(D61, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.74539899931977227</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C62" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D62" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="E62" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F62" s="9">
+        <f t="array" ref="F62">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A62='Feed rations'!$C$4:$C$19)*(C62='Feed rations'!$D$4:$D$19),0),
+MATCH(D62, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.17941015258191029</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C63" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D63" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="E63" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F63" s="9">
+        <f t="array" ref="F63">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A63='Feed rations'!$C$4:$C$19)*(C63='Feed rations'!$D$4:$D$19),0),
+MATCH(D63, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>1.7964539316658934</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C64" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D64" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="E64" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F64" s="9">
+        <f t="array" ref="F64">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A64='Feed rations'!$C$4:$C$19)*(C64='Feed rations'!$D$4:$D$19),0),
+MATCH(D64, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.1135644201898998</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C65" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D65" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="E65" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F65" s="9">
+        <f t="array" ref="F65">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A65='Feed rations'!$C$4:$C$19)*(C65='Feed rations'!$D$4:$D$19),0),
+MATCH(D65, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.56830204582053978</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C66" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D66" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="E66" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F66" s="9">
+        <f t="array" ref="F66">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A66='Feed rations'!$C$4:$C$19)*(C66='Feed rations'!$D$4:$D$19),0),
+MATCH(D66, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.48372359192672859</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C67" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D67" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="E67" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F67" s="9">
+        <f t="array" ref="F67">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A67='Feed rations'!$C$4:$C$19)*(C67='Feed rations'!$D$4:$D$19),0),
+MATCH(D67, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.11194207133004409</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C68" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D68" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="E68" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F68" s="9">
+        <f t="array" ref="F68">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A68='Feed rations'!$C$4:$C$19)*(C68='Feed rations'!$D$4:$D$19),0),
+MATCH(D68, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.86898412763404764</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C69" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="D38" s="42" t="s">
+      <c r="D69" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="E38" s="42" t="s">
-        <v>45</v>
-      </c>
-      <c r="F38" s="43">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C39" s="42" t="s">
+      <c r="E69" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F69" s="9">
+        <f t="array" ref="F69">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A69='Feed rations'!$C$4:$C$19)*(C69='Feed rations'!$D$4:$D$19),0),
+MATCH(D69, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>61.333333333333343</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C70" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="D39" s="42" t="s">
+      <c r="D70" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="E39" s="42" t="s">
-        <v>45</v>
-      </c>
-      <c r="F39" s="42">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
-        <v>85</v>
+      <c r="E70" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F70" s="9">
+        <f t="array" ref="F70">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A70='Feed rations'!$C$4:$C$19)*(C70='Feed rations'!$D$4:$D$19),0),
+MATCH(D70, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>30.666666666666664</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C71" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D71" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="E71" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F71" s="9">
+        <f t="array" ref="F71">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A71='Feed rations'!$C$4:$C$19)*(C71='Feed rations'!$D$4:$D$19),0),
+MATCH(D71, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>1.8211653949898006</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C72" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D72" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="E72" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F72" s="9">
+        <f t="array" ref="F72">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A72='Feed rations'!$C$4:$C$19)*(C72='Feed rations'!$D$4:$D$19),0),
+MATCH(D72, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.61565821590295877</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C73" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D73" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="E73" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F73" s="9">
+        <f t="array" ref="F73">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A73='Feed rations'!$C$4:$C$19)*(C73='Feed rations'!$D$4:$D$19),0),
+MATCH(D73, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.85188457065116829</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C74" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D74" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="E74" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F74" s="9">
+        <f t="array" ref="F74">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A74='Feed rations'!$C$4:$C$19)*(C74='Feed rations'!$D$4:$D$19),0),
+MATCH(D74, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.20504017437932603</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C75" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D75" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="E75" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F75" s="9">
+        <f t="array" ref="F75">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A75='Feed rations'!$C$4:$C$19)*(C75='Feed rations'!$D$4:$D$19),0),
+MATCH(D75, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>2.0530902076181636</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C76" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D76" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="E76" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F76" s="9">
+        <f t="array" ref="F76">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A76='Feed rations'!$C$4:$C$19)*(C76='Feed rations'!$D$4:$D$19),0),
+MATCH(D76, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.12978790878845692</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C77" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D77" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="E77" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F77" s="9">
+        <f t="array" ref="F77">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A77='Feed rations'!$C$4:$C$19)*(C77='Feed rations'!$D$4:$D$19),0),
+MATCH(D77, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.64948805236633111</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C78" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D78" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="E78" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F78" s="9">
+        <f t="array" ref="F78">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A78='Feed rations'!$C$4:$C$19)*(C78='Feed rations'!$D$4:$D$19),0),
+MATCH(D78, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.55282696220197547</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C79" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D79" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="E79" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F79" s="9">
+        <f t="array" ref="F79">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A79='Feed rations'!$C$4:$C$19)*(C79='Feed rations'!$D$4:$D$19),0),
+MATCH(D79, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.12793379580576467</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C80" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D80" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="E80" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F80" s="9">
+        <f t="array" ref="F80">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A80='Feed rations'!$C$4:$C$19)*(C80='Feed rations'!$D$4:$D$19),0),
+MATCH(D80, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.99312471729605445</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D82" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="E82" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F82" s="9">
+        <f t="array" ref="F82">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A82='Feed rations'!$C$4:$C$19)*(C82='Feed rations'!$D$4:$D$19),0),
+MATCH(D82, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D83" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="E83" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F83" s="9">
+        <f t="array" ref="F83">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A83='Feed rations'!$C$4:$C$19)*(C83='Feed rations'!$D$4:$D$19),0),
+MATCH(D83, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>32.999999999999993</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D84" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="E84" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F84" s="9">
+        <f t="array" ref="F84">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A84='Feed rations'!$C$4:$C$19)*(C84='Feed rations'!$D$4:$D$19),0),
+MATCH(D84, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.22764567437372507</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D85" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="E85" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F85" s="9">
+        <f t="array" ref="F85">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A85='Feed rations'!$C$4:$C$19)*(C85='Feed rations'!$D$4:$D$19),0),
+MATCH(D85, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>7.6957276987869846E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D86" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="E86" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F86" s="9">
+        <f t="array" ref="F86">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A86='Feed rations'!$C$4:$C$19)*(C86='Feed rations'!$D$4:$D$19),0),
+MATCH(D86, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.10648557133139604</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D87" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="E87" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F87" s="9">
+        <f t="array" ref="F87">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A87='Feed rations'!$C$4:$C$19)*(C87='Feed rations'!$D$4:$D$19),0),
+MATCH(D87, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>2.5630021797415754E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C88" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D88" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="E88" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F88" s="9">
+        <f t="array" ref="F88">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A88='Feed rations'!$C$4:$C$19)*(C88='Feed rations'!$D$4:$D$19),0),
+MATCH(D88, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.25663627595227045</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D89" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="E89" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F89" s="9">
+        <f t="array" ref="F89">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A89='Feed rations'!$C$4:$C$19)*(C89='Feed rations'!$D$4:$D$19),0),
+MATCH(D89, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>1.6223488598557115E-2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D90" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="E90" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F90" s="9">
+        <f t="array" ref="F90">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A90='Feed rations'!$C$4:$C$19)*(C90='Feed rations'!$D$4:$D$19),0),
+MATCH(D90, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>8.1186006545791389E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D91" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="E91" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F91" s="9">
+        <f t="array" ref="F91">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A91='Feed rations'!$C$4:$C$19)*(C91='Feed rations'!$D$4:$D$19),0),
+MATCH(D91, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>6.9103370275246934E-2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D92" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="E92" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F92" s="9">
+        <f t="array" ref="F92">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A92='Feed rations'!$C$4:$C$19)*(C92='Feed rations'!$D$4:$D$19),0),
+MATCH(D92, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>1.5991724475720583E-2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D93" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="E93" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F93" s="9">
+        <f t="array" ref="F93">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A93='Feed rations'!$C$4:$C$19)*(C93='Feed rations'!$D$4:$D$19),0),
+MATCH(D93, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.12414058966200681</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D94" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="E94" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F94" s="9">
+        <f t="array" ref="F94">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A94='Feed rations'!$C$4:$C$19)*(C94='Feed rations'!$D$4:$D$19),0),
+MATCH(D94, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>81.666666666666671</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D95" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="E95" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F95" s="9">
+        <f t="array" ref="F95">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A95='Feed rations'!$C$4:$C$19)*(C95='Feed rations'!$D$4:$D$19),0),
+MATCH(D95, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>16.333333333333332</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C96" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D96" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="E96" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F96" s="9">
+        <f t="array" ref="F96">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A96='Feed rations'!$C$4:$C$19)*(C96='Feed rations'!$D$4:$D$19),0),
+MATCH(D96, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.45529134874745014</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D97" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="E97" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F97" s="9">
+        <f t="array" ref="F97">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A97='Feed rations'!$C$4:$C$19)*(C97='Feed rations'!$D$4:$D$19),0),
+MATCH(D97, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.15391455397573969</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D98" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="E98" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F98" s="9">
+        <f t="array" ref="F98">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A98='Feed rations'!$C$4:$C$19)*(C98='Feed rations'!$D$4:$D$19),0),
+MATCH(D98, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.21297114266279207</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D99" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="E99" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F99" s="9">
+        <f t="array" ref="F99">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A99='Feed rations'!$C$4:$C$19)*(C99='Feed rations'!$D$4:$D$19),0),
+MATCH(D99, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>5.1260043594831509E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C100" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D100" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="E100" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F100" s="9">
+        <f t="array" ref="F100">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A100='Feed rations'!$C$4:$C$19)*(C100='Feed rations'!$D$4:$D$19),0),
+MATCH(D100, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.51327255190454091</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D101" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="E101" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F101" s="9">
+        <f t="array" ref="F101">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A101='Feed rations'!$C$4:$C$19)*(C101='Feed rations'!$D$4:$D$19),0),
+MATCH(D101, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>3.244697719711423E-2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C102" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D102" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="E102" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F102" s="9">
+        <f t="array" ref="F102">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A102='Feed rations'!$C$4:$C$19)*(C102='Feed rations'!$D$4:$D$19),0),
+MATCH(D102, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.16237201309158278</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C103" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D103" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="E103" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F103" s="9">
+        <f t="array" ref="F103">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A103='Feed rations'!$C$4:$C$19)*(C103='Feed rations'!$D$4:$D$19),0),
+MATCH(D103, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.13820674055049387</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C104" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D104" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="E104" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F104" s="9">
+        <f t="array" ref="F104">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A104='Feed rations'!$C$4:$C$19)*(C104='Feed rations'!$D$4:$D$19),0),
+MATCH(D104, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>3.1983448951441167E-2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C105" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D105" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="E105" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F105" s="9">
+        <f t="array" ref="F105">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A105='Feed rations'!$C$4:$C$19)*(C105='Feed rations'!$D$4:$D$19),0),
+MATCH(D105, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.24828117932401361</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C106" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D106" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="E106" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F106" s="9">
+        <f t="array" ref="F106">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A106='Feed rations'!$C$4:$C$19)*(C106='Feed rations'!$D$4:$D$19),0),
+MATCH(D106, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C107" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D107" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="E107" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F107" s="9">
+        <f t="array" ref="F107">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A107='Feed rations'!$C$4:$C$19)*(C107='Feed rations'!$D$4:$D$19),0),
+MATCH(D107, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>30.999999999999993</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C108" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D108" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="E108" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F108" s="9">
+        <f t="array" ref="F108">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A108='Feed rations'!$C$4:$C$19)*(C108='Feed rations'!$D$4:$D$19),0),
+MATCH(D108, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>1.5935197206160754</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C109" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D109" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="E109" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F109" s="9">
+        <f t="array" ref="F109">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A109='Feed rations'!$C$4:$C$19)*(C109='Feed rations'!$D$4:$D$19),0),
+MATCH(D109, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.53870093891508897</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C110" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D110" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="E110" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F110" s="9">
+        <f t="array" ref="F110">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A110='Feed rations'!$C$4:$C$19)*(C110='Feed rations'!$D$4:$D$19),0),
+MATCH(D110, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.74539899931977227</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C111" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D111" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="E111" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F111" s="9">
+        <f t="array" ref="F111">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A111='Feed rations'!$C$4:$C$19)*(C111='Feed rations'!$D$4:$D$19),0),
+MATCH(D111, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.17941015258191029</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C112" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D112" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="E112" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F112" s="9">
+        <f t="array" ref="F112">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A112='Feed rations'!$C$4:$C$19)*(C112='Feed rations'!$D$4:$D$19),0),
+MATCH(D112, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>1.7964539316658934</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C113" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D113" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="E113" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F113" s="9">
+        <f t="array" ref="F113">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A113='Feed rations'!$C$4:$C$19)*(C113='Feed rations'!$D$4:$D$19),0),
+MATCH(D113, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.1135644201898998</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C114" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D114" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="E114" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F114" s="9">
+        <f t="array" ref="F114">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A114='Feed rations'!$C$4:$C$19)*(C114='Feed rations'!$D$4:$D$19),0),
+MATCH(D114, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.56830204582053978</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C115" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D115" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="E115" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F115" s="9">
+        <f t="array" ref="F115">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A115='Feed rations'!$C$4:$C$19)*(C115='Feed rations'!$D$4:$D$19),0),
+MATCH(D115, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.48372359192672859</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C116" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D116" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="E116" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F116" s="9">
+        <f t="array" ref="F116">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A116='Feed rations'!$C$4:$C$19)*(C116='Feed rations'!$D$4:$D$19),0),
+MATCH(D116, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.11194207133004409</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C117" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D117" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="E117" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F117" s="9">
+        <f t="array" ref="F117">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A117='Feed rations'!$C$4:$C$19)*(C117='Feed rations'!$D$4:$D$19),0),
+MATCH(D117, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.86898412763404764</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C118" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D118" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="E118" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F118" s="9">
+        <f t="array" ref="F118">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A118='Feed rations'!$C$4:$C$19)*(C118='Feed rations'!$D$4:$D$19),0),
+MATCH(D118, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>64.666666666666671</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C119" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D119" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="E119" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F119" s="9">
+        <f t="array" ref="F119">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A119='Feed rations'!$C$4:$C$19)*(C119='Feed rations'!$D$4:$D$19),0),
+MATCH(D119, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>32.333333333333329</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C120" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D120" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="E120" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F120" s="9">
+        <f t="array" ref="F120">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A120='Feed rations'!$C$4:$C$19)*(C120='Feed rations'!$D$4:$D$19),0),
+MATCH(D120, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.6829370231211751</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C121" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D121" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="E121" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F121" s="9">
+        <f t="array" ref="F121">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A121='Feed rations'!$C$4:$C$19)*(C121='Feed rations'!$D$4:$D$19),0),
+MATCH(D121, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.23087183096360953</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C122" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D122" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="E122" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F122" s="9">
+        <f t="array" ref="F122">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A122='Feed rations'!$C$4:$C$19)*(C122='Feed rations'!$D$4:$D$19),0),
+MATCH(D122, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.31945671399418812</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C123" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D123" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="E123" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F123" s="9">
+        <f t="array" ref="F123">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A123='Feed rations'!$C$4:$C$19)*(C123='Feed rations'!$D$4:$D$19),0),
+MATCH(D123, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>7.6890065392247256E-2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C124" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D124" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="E124" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F124" s="9">
+        <f t="array" ref="F124">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A124='Feed rations'!$C$4:$C$19)*(C124='Feed rations'!$D$4:$D$19),0),
+MATCH(D124, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.76990882785681136</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C125" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D125" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="E125" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F125" s="9">
+        <f t="array" ref="F125">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A125='Feed rations'!$C$4:$C$19)*(C125='Feed rations'!$D$4:$D$19),0),
+MATCH(D125, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>4.8670465795671344E-2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C126" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D126" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="E126" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F126" s="9">
+        <f t="array" ref="F126">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A126='Feed rations'!$C$4:$C$19)*(C126='Feed rations'!$D$4:$D$19),0),
+MATCH(D126, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.24355801963737417</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C127" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D127" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="E127" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F127" s="9">
+        <f t="array" ref="F127">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A127='Feed rations'!$C$4:$C$19)*(C127='Feed rations'!$D$4:$D$19),0),
+MATCH(D127, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.20731011082574077</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C128" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D128" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="E128" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F128" s="9">
+        <f t="array" ref="F128">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A128='Feed rations'!$C$4:$C$19)*(C128='Feed rations'!$D$4:$D$19),0),
+MATCH(D128, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>4.7975173427161746E-2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C129" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D129" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="E129" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F129" s="9">
+        <f t="array" ref="F129">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A129='Feed rations'!$C$4:$C$19)*(C129='Feed rations'!$D$4:$D$19),0),
+MATCH(D129, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.37242176898602036</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C131" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D131" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="E131" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F131" s="9">
+        <f t="array" ref="F131">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A131='Feed rations'!$C$4:$C$19)*(C131='Feed rations'!$D$4:$D$19),0),
+MATCH(D131, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C132" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D132" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="E132" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F132" s="9">
+        <f t="array" ref="F132">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A132='Feed rations'!$C$4:$C$19)*(C132='Feed rations'!$D$4:$D$19),0),
+MATCH(D132, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>32.999999999999993</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C133" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D133" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="E133" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F133" s="9">
+        <f t="array" ref="F133">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A133='Feed rations'!$C$4:$C$19)*(C133='Feed rations'!$D$4:$D$19),0),
+MATCH(D133, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.22764567437372507</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C134" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D134" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="E134" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F134" s="9">
+        <f t="array" ref="F134">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A134='Feed rations'!$C$4:$C$19)*(C134='Feed rations'!$D$4:$D$19),0),
+MATCH(D134, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>7.6957276987869846E-2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C135" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D135" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="E135" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F135" s="9">
+        <f t="array" ref="F135">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A135='Feed rations'!$C$4:$C$19)*(C135='Feed rations'!$D$4:$D$19),0),
+MATCH(D135, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.10648557133139604</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C136" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D136" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="E136" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F136" s="9">
+        <f t="array" ref="F136">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A136='Feed rations'!$C$4:$C$19)*(C136='Feed rations'!$D$4:$D$19),0),
+MATCH(D136, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>2.5630021797415754E-2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C137" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D137" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="E137" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F137" s="9">
+        <f t="array" ref="F137">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A137='Feed rations'!$C$4:$C$19)*(C137='Feed rations'!$D$4:$D$19),0),
+MATCH(D137, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.25663627595227045</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C138" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D138" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="E138" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F138" s="9">
+        <f t="array" ref="F138">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A138='Feed rations'!$C$4:$C$19)*(C138='Feed rations'!$D$4:$D$19),0),
+MATCH(D138, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>1.6223488598557115E-2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C139" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D139" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="E139" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F139" s="9">
+        <f t="array" ref="F139">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A139='Feed rations'!$C$4:$C$19)*(C139='Feed rations'!$D$4:$D$19),0),
+MATCH(D139, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>8.1186006545791389E-2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C140" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D140" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="E140" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F140" s="9">
+        <f t="array" ref="F140">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A140='Feed rations'!$C$4:$C$19)*(C140='Feed rations'!$D$4:$D$19),0),
+MATCH(D140, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>6.9103370275246934E-2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C141" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D141" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="E141" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F141" s="9">
+        <f t="array" ref="F141">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A141='Feed rations'!$C$4:$C$19)*(C141='Feed rations'!$D$4:$D$19),0),
+MATCH(D141, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>1.5991724475720583E-2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C142" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D142" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="E142" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F142" s="9">
+        <f t="array" ref="F142">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A142='Feed rations'!$C$4:$C$19)*(C142='Feed rations'!$D$4:$D$19),0),
+MATCH(D142, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.12414058966200681</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C143" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D143" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="E143" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F143" s="9">
+        <f t="array" ref="F143">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A143='Feed rations'!$C$4:$C$19)*(C143='Feed rations'!$D$4:$D$19),0),
+MATCH(D143, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C144" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D144" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="E144" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F144" s="9">
+        <f t="array" ref="F144">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A144='Feed rations'!$C$4:$C$19)*(C144='Feed rations'!$D$4:$D$19),0),
+MATCH(D144, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>15.999999999999998</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C145" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D145" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="E145" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F145" s="9">
+        <f t="array" ref="F145">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A145='Feed rations'!$C$4:$C$19)*(C145='Feed rations'!$D$4:$D$19),0),
+MATCH(D145, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.91058269749490028</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A146" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C146" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D146" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="E146" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F146" s="9">
+        <f t="array" ref="F146">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A146='Feed rations'!$C$4:$C$19)*(C146='Feed rations'!$D$4:$D$19),0),
+MATCH(D146, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.30782910795147939</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C147" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D147" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="E147" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F147" s="9">
+        <f t="array" ref="F147">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A147='Feed rations'!$C$4:$C$19)*(C147='Feed rations'!$D$4:$D$19),0),
+MATCH(D147, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.42594228532558415</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C148" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D148" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="E148" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F148" s="9">
+        <f t="array" ref="F148">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A148='Feed rations'!$C$4:$C$19)*(C148='Feed rations'!$D$4:$D$19),0),
+MATCH(D148, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.10252008718966302</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A149" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C149" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D149" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="E149" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F149" s="9">
+        <f t="array" ref="F149">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A149='Feed rations'!$C$4:$C$19)*(C149='Feed rations'!$D$4:$D$19),0),
+MATCH(D149, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>1.0265451038090818</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A150" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C150" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D150" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="E150" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F150" s="9">
+        <f t="array" ref="F150">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A150='Feed rations'!$C$4:$C$19)*(C150='Feed rations'!$D$4:$D$19),0),
+MATCH(D150, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>6.4893954394228459E-2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C151" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D151" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="E151" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F151" s="9">
+        <f t="array" ref="F151">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A151='Feed rations'!$C$4:$C$19)*(C151='Feed rations'!$D$4:$D$19),0),
+MATCH(D151, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.32474402618316556</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C152" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D152" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="E152" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F152" s="9">
+        <f t="array" ref="F152">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A152='Feed rations'!$C$4:$C$19)*(C152='Feed rations'!$D$4:$D$19),0),
+MATCH(D152, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.27641348110098773</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C153" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D153" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="E153" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F153" s="9">
+        <f t="array" ref="F153">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A153='Feed rations'!$C$4:$C$19)*(C153='Feed rations'!$D$4:$D$19),0),
+MATCH(D153, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>6.3966897902882333E-2</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A154" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C154" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D154" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="E154" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F154" s="9">
+        <f t="array" ref="F154">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A154='Feed rations'!$C$4:$C$19)*(C154='Feed rations'!$D$4:$D$19),0),
+MATCH(D154, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.49656235864802722</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A155" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C155" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D155" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="E155" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F155" s="9">
+        <f t="array" ref="F155">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A155='Feed rations'!$C$4:$C$19)*(C155='Feed rations'!$D$4:$D$19),0),
+MATCH(D155, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A156" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C156" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D156" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="E156" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F156" s="9">
+        <f t="array" ref="F156">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A156='Feed rations'!$C$4:$C$19)*(C156='Feed rations'!$D$4:$D$19),0),
+MATCH(D156, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>30.999999999999993</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A157" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C157" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D157" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="E157" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F157" s="9">
+        <f t="array" ref="F157">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A157='Feed rations'!$C$4:$C$19)*(C157='Feed rations'!$D$4:$D$19),0),
+MATCH(D157, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>1.5935197206160754</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C158" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D158" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="E158" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F158" s="9">
+        <f t="array" ref="F158">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A158='Feed rations'!$C$4:$C$19)*(C158='Feed rations'!$D$4:$D$19),0),
+MATCH(D158, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.53870093891508897</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A159" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C159" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D159" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="E159" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F159" s="9">
+        <f t="array" ref="F159">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A159='Feed rations'!$C$4:$C$19)*(C159='Feed rations'!$D$4:$D$19),0),
+MATCH(D159, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.74539899931977227</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C160" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D160" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="E160" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F160" s="9">
+        <f t="array" ref="F160">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A160='Feed rations'!$C$4:$C$19)*(C160='Feed rations'!$D$4:$D$19),0),
+MATCH(D160, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.17941015258191029</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A161" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C161" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D161" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="E161" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F161" s="9">
+        <f t="array" ref="F161">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A161='Feed rations'!$C$4:$C$19)*(C161='Feed rations'!$D$4:$D$19),0),
+MATCH(D161, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>1.7964539316658934</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A162" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C162" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D162" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="E162" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F162" s="9">
+        <f t="array" ref="F162">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A162='Feed rations'!$C$4:$C$19)*(C162='Feed rations'!$D$4:$D$19),0),
+MATCH(D162, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.1135644201898998</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A163" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C163" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D163" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="E163" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F163" s="9">
+        <f t="array" ref="F163">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A163='Feed rations'!$C$4:$C$19)*(C163='Feed rations'!$D$4:$D$19),0),
+MATCH(D163, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.56830204582053978</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A164" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C164" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D164" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="E164" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F164" s="9">
+        <f t="array" ref="F164">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A164='Feed rations'!$C$4:$C$19)*(C164='Feed rations'!$D$4:$D$19),0),
+MATCH(D164, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.48372359192672859</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A165" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C165" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D165" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="E165" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F165" s="9">
+        <f t="array" ref="F165">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A165='Feed rations'!$C$4:$C$19)*(C165='Feed rations'!$D$4:$D$19),0),
+MATCH(D165, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.11194207133004409</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A166" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C166" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D166" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="E166" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F166" s="9">
+        <f t="array" ref="F166">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A166='Feed rations'!$C$4:$C$19)*(C166='Feed rations'!$D$4:$D$19),0),
+MATCH(D166, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.86898412763404764</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A167" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C167" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D167" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="E167" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F167" s="9">
+        <f t="array" ref="F167">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A167='Feed rations'!$C$4:$C$19)*(C167='Feed rations'!$D$4:$D$19),0),
+MATCH(D167, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>63.333333333333343</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A168" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C168" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D168" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="E168" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F168" s="9">
+        <f t="array" ref="F168">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A168='Feed rations'!$C$4:$C$19)*(C168='Feed rations'!$D$4:$D$19),0),
+MATCH(D168, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>31.666666666666664</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A169" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C169" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D169" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="E169" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F169" s="9">
+        <f t="array" ref="F169">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A169='Feed rations'!$C$4:$C$19)*(C169='Feed rations'!$D$4:$D$19),0),
+MATCH(D169, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>1.1382283718686252</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A170" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C170" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D170" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="E170" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F170" s="9">
+        <f t="array" ref="F170">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A170='Feed rations'!$C$4:$C$19)*(C170='Feed rations'!$D$4:$D$19),0),
+MATCH(D170, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.38478638493934925</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A171" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C171" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D171" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="E171" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F171" s="9">
+        <f t="array" ref="F171">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A171='Feed rations'!$C$4:$C$19)*(C171='Feed rations'!$D$4:$D$19),0),
+MATCH(D171, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.53242785665698023</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A172" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C172" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D172" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="E172" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F172" s="9">
+        <f t="array" ref="F172">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A172='Feed rations'!$C$4:$C$19)*(C172='Feed rations'!$D$4:$D$19),0),
+MATCH(D172, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.12815010898707879</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A173" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C173" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D173" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="E173" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F173" s="9">
+        <f t="array" ref="F173">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A173='Feed rations'!$C$4:$C$19)*(C173='Feed rations'!$D$4:$D$19),0),
+MATCH(D173, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>1.2831813797613523</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A174" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C174" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D174" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="E174" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F174" s="9">
+        <f t="array" ref="F174">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A174='Feed rations'!$C$4:$C$19)*(C174='Feed rations'!$D$4:$D$19),0),
+MATCH(D174, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>8.1117442992785574E-2</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A175" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C175" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D175" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="E175" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F175" s="9">
+        <f t="array" ref="F175">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A175='Feed rations'!$C$4:$C$19)*(C175='Feed rations'!$D$4:$D$19),0),
+MATCH(D175, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.40593003272895695</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A176" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C176" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D176" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="E176" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F176" s="9">
+        <f t="array" ref="F176">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A176='Feed rations'!$C$4:$C$19)*(C176='Feed rations'!$D$4:$D$19),0),
+MATCH(D176, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.34551685137623467</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A177" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C177" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D177" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="E177" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F177" s="9">
+        <f t="array" ref="F177">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A177='Feed rations'!$C$4:$C$19)*(C177='Feed rations'!$D$4:$D$19),0),
+MATCH(D177, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>7.995862237860292E-2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A178" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C178" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D178" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="E178" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F178" s="9">
+        <f t="array" ref="F178">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A178='Feed rations'!$C$4:$C$19)*(C178='Feed rations'!$D$4:$D$19),0),
+MATCH(D178, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.62070294831003403</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A180" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C180" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D180" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="E180" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F180" s="9">
+        <f t="array" ref="F180">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A180='Feed rations'!$C$4:$C$19)*(C180='Feed rations'!$D$4:$D$19),0),
+MATCH(D180, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>62.666666666666671</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A181" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C181" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D181" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="E181" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F181" s="9">
+        <f t="array" ref="F181">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A181='Feed rations'!$C$4:$C$19)*(C181='Feed rations'!$D$4:$D$19),0),
+MATCH(D181, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>31.333333333333329</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A182" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C182" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D182" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="E182" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F182" s="9">
+        <f t="array" ref="F182">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A182='Feed rations'!$C$4:$C$19)*(C182='Feed rations'!$D$4:$D$19),0),
+MATCH(D182, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>1.3658740462423502</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A183" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C183" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D183" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="E183" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F183" s="9">
+        <f t="array" ref="F183">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A183='Feed rations'!$C$4:$C$19)*(C183='Feed rations'!$D$4:$D$19),0),
+MATCH(D183, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.46174366192721905</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A184" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C184" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D184" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="E184" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F184" s="9">
+        <f t="array" ref="F184">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A184='Feed rations'!$C$4:$C$19)*(C184='Feed rations'!$D$4:$D$19),0),
+MATCH(D184, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.63891342798837625</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A185" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C185" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D185" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="E185" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F185" s="9">
+        <f t="array" ref="F185">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A185='Feed rations'!$C$4:$C$19)*(C185='Feed rations'!$D$4:$D$19),0),
+MATCH(D185, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.15378013078449451</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A186" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C186" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D186" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="E186" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F186" s="9">
+        <f t="array" ref="F186">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A186='Feed rations'!$C$4:$C$19)*(C186='Feed rations'!$D$4:$D$19),0),
+MATCH(D186, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>1.5398176557136227</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A187" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C187" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D187" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="E187" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F187" s="9">
+        <f t="array" ref="F187">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A187='Feed rations'!$C$4:$C$19)*(C187='Feed rations'!$D$4:$D$19),0),
+MATCH(D187, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>9.7340931591342689E-2</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A188" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C188" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D188" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="E188" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F188" s="9">
+        <f t="array" ref="F188">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A188='Feed rations'!$C$4:$C$19)*(C188='Feed rations'!$D$4:$D$19),0),
+MATCH(D188, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.48711603927474834</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A189" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C189" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D189" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="E189" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F189" s="9">
+        <f t="array" ref="F189">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A189='Feed rations'!$C$4:$C$19)*(C189='Feed rations'!$D$4:$D$19),0),
+MATCH(D189, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.41462022165148155</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A190" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C190" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D190" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="E190" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F190" s="9">
+        <f t="array" ref="F190">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A190='Feed rations'!$C$4:$C$19)*(C190='Feed rations'!$D$4:$D$19),0),
+MATCH(D190, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>9.5950346854323493E-2</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A191" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C191" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D191" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="E191" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F191" s="9">
+        <f t="array" ref="F191">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A191='Feed rations'!$C$4:$C$19)*(C191='Feed rations'!$D$4:$D$19),0),
+MATCH(D191, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.74484353797204073</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A192" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C192" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D192" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="E192" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F192" s="9">
+        <f t="array" ref="F192">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A192='Feed rations'!$C$4:$C$19)*(C192='Feed rations'!$D$4:$D$19),0),
+MATCH(D192, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>74.166666666666671</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A193" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C193" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D193" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="E193" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F193" s="9">
+        <f t="array" ref="F193">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A193='Feed rations'!$C$4:$C$19)*(C193='Feed rations'!$D$4:$D$19),0),
+MATCH(D193, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>14.833333333333332</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A194" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C194" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D194" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="E194" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F194" s="9">
+        <f t="array" ref="F194">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A194='Feed rations'!$C$4:$C$19)*(C194='Feed rations'!$D$4:$D$19),0),
+MATCH(D194, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>2.5041024181109752</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A195" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C195" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D195" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="E195" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F195" s="9">
+        <f t="array" ref="F195">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A195='Feed rations'!$C$4:$C$19)*(C195='Feed rations'!$D$4:$D$19),0),
+MATCH(D195, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.8465300468665683</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A196" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C196" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D196" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="E196" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F196" s="9">
+        <f t="array" ref="F196">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A196='Feed rations'!$C$4:$C$19)*(C196='Feed rations'!$D$4:$D$19),0),
+MATCH(D196, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>1.1713412846453564</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A197" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C197" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D197" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="E197" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F197" s="9">
+        <f t="array" ref="F197">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A197='Feed rations'!$C$4:$C$19)*(C197='Feed rations'!$D$4:$D$19),0),
+MATCH(D197, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.28193023977157328</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A198" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C198" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D198" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="E198" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F198" s="9">
+        <f t="array" ref="F198">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A198='Feed rations'!$C$4:$C$19)*(C198='Feed rations'!$D$4:$D$19),0),
+MATCH(D198, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>2.8229990354749752</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A199" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C199" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D199" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="E199" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F199" s="9">
+        <f t="array" ref="F199">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A199='Feed rations'!$C$4:$C$19)*(C199='Feed rations'!$D$4:$D$19),0),
+MATCH(D199, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.17845837458412825</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A200" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C200" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D200" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="E200" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F200" s="9">
+        <f t="array" ref="F200">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A200='Feed rations'!$C$4:$C$19)*(C200='Feed rations'!$D$4:$D$19),0),
+MATCH(D200, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.89304607200370534</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A201" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C201" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D201" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="E201" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F201" s="9">
+        <f t="array" ref="F201">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A201='Feed rations'!$C$4:$C$19)*(C201='Feed rations'!$D$4:$D$19),0),
+MATCH(D201, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.76013707302771627</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A202" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C202" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D202" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="E202" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F202" s="9">
+        <f t="array" ref="F202">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A202='Feed rations'!$C$4:$C$19)*(C202='Feed rations'!$D$4:$D$19),0),
+MATCH(D202, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.17590896923292643</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A203" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C203" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D203" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="E203" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F203" s="9">
+        <f t="array" ref="F203">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A203='Feed rations'!$C$4:$C$19)*(C203='Feed rations'!$D$4:$D$19),0),
+MATCH(D203, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>1.3655464862820748</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A204" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C204" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D204" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="E204" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F204" s="9">
+        <f t="array" ref="F204">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A204='Feed rations'!$C$4:$C$19)*(C204='Feed rations'!$D$4:$D$19),0),
+MATCH(D204, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>60.000000000000007</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A205" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C205" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D205" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="E205" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F205" s="9">
+        <f t="array" ref="F205">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A205='Feed rations'!$C$4:$C$19)*(C205='Feed rations'!$D$4:$D$19),0),
+MATCH(D205, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A206" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C206" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D206" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="E206" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F206" s="9">
+        <f t="array" ref="F206">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A206='Feed rations'!$C$4:$C$19)*(C206='Feed rations'!$D$4:$D$19),0),
+MATCH(D206, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>2.2764567437372505</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A207" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C207" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D207" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="E207" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F207" s="9">
+        <f t="array" ref="F207">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A207='Feed rations'!$C$4:$C$19)*(C207='Feed rations'!$D$4:$D$19),0),
+MATCH(D207, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.76957276987869849</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A208" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C208" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D208" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="E208" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F208" s="9">
+        <f t="array" ref="F208">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A208='Feed rations'!$C$4:$C$19)*(C208='Feed rations'!$D$4:$D$19),0),
+MATCH(D208, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>1.0648557133139605</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A209" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C209" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D209" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="E209" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F209" s="9">
+        <f t="array" ref="F209">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A209='Feed rations'!$C$4:$C$19)*(C209='Feed rations'!$D$4:$D$19),0),
+MATCH(D209, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.25630021797415758</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A210" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C210" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D210" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="E210" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F210" s="9">
+        <f t="array" ref="F210">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A210='Feed rations'!$C$4:$C$19)*(C210='Feed rations'!$D$4:$D$19),0),
+MATCH(D210, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>2.5663627595227045</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A211" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C211" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D211" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="E211" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F211" s="9">
+        <f t="array" ref="F211">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A211='Feed rations'!$C$4:$C$19)*(C211='Feed rations'!$D$4:$D$19),0),
+MATCH(D211, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.16223488598557115</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A212" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C212" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D212" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="E212" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F212" s="9">
+        <f t="array" ref="F212">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A212='Feed rations'!$C$4:$C$19)*(C212='Feed rations'!$D$4:$D$19),0),
+MATCH(D212, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.81186006545791389</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A213" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C213" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D213" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="E213" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F213" s="9">
+        <f t="array" ref="F213">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A213='Feed rations'!$C$4:$C$19)*(C213='Feed rations'!$D$4:$D$19),0),
+MATCH(D213, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.69103370275246934</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A214" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C214" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D214" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="E214" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F214" s="9">
+        <f t="array" ref="F214">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A214='Feed rations'!$C$4:$C$19)*(C214='Feed rations'!$D$4:$D$19),0),
+MATCH(D214, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.15991724475720584</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A215" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C215" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D215" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="E215" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F215" s="9">
+        <f t="array" ref="F215">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A215='Feed rations'!$C$4:$C$19)*(C215='Feed rations'!$D$4:$D$19),0),
+MATCH(D215, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>1.2414058966200681</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A216" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C216" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D216" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="E216" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F216" s="9">
+        <f t="array" ref="F216">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A216='Feed rations'!$C$4:$C$19)*(C216='Feed rations'!$D$4:$D$19),0),
+MATCH(D216, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>58.666666666666679</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A217" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C217" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D217" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="E217" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F217" s="9">
+        <f t="array" ref="F217">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A217='Feed rations'!$C$4:$C$19)*(C217='Feed rations'!$D$4:$D$19),0),
+MATCH(D217, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>29.333333333333332</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A218" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C218" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D218" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="E218" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F218" s="9">
+        <f t="array" ref="F218">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A218='Feed rations'!$C$4:$C$19)*(C218='Feed rations'!$D$4:$D$19),0),
+MATCH(D218, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>2.7317480924847004</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A219" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C219" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D219" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="E219" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F219" s="9">
+        <f t="array" ref="F219">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A219='Feed rations'!$C$4:$C$19)*(C219='Feed rations'!$D$4:$D$19),0),
+MATCH(D219, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.9234873238544381</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A220" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C220" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D220" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="E220" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F220" s="9">
+        <f t="array" ref="F220">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A220='Feed rations'!$C$4:$C$19)*(C220='Feed rations'!$D$4:$D$19),0),
+MATCH(D220, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>1.2778268559767525</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A221" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C221" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D221" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="E221" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F221" s="9">
+        <f t="array" ref="F221">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A221='Feed rations'!$C$4:$C$19)*(C221='Feed rations'!$D$4:$D$19),0),
+MATCH(D221, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.30756026156898902</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A222" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C222" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D222" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="E222" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F222" s="9">
+        <f t="array" ref="F222">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A222='Feed rations'!$C$4:$C$19)*(C222='Feed rations'!$D$4:$D$19),0),
+MATCH(D222, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>3.0796353114272454</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A223" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C223" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D223" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="E223" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F223" s="9">
+        <f t="array" ref="F223">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A223='Feed rations'!$C$4:$C$19)*(C223='Feed rations'!$D$4:$D$19),0),
+MATCH(D223, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.19468186318268538</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A224" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C224" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D224" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="E224" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F224" s="9">
+        <f t="array" ref="F224">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A224='Feed rations'!$C$4:$C$19)*(C224='Feed rations'!$D$4:$D$19),0),
+MATCH(D224, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.97423207854949667</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A225" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C225" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D225" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="E225" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F225" s="9">
+        <f t="array" ref="F225">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A225='Feed rations'!$C$4:$C$19)*(C225='Feed rations'!$D$4:$D$19),0),
+MATCH(D225, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.82924044330296309</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A226" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C226" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D226" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="E226" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F226" s="9">
+        <f t="array" ref="F226">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A226='Feed rations'!$C$4:$C$19)*(C226='Feed rations'!$D$4:$D$19),0),
+MATCH(D226, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>0.19190069370864699</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A227" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C227" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D227" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="E227" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F227" s="9">
+        <f t="array" ref="F227">INDEX('Feed rations'!$J$4:$AA$19,
+MATCH(1, (A227='Feed rations'!$C$4:$C$19)*(C227='Feed rations'!$D$4:$D$19),0),
+MATCH(D227, 'Feed rations'!$J$3:$AA$3, 0))</f>
+        <v>1.4896870759440815</v>
       </c>
     </row>
   </sheetData>
@@ -3840,28 +7597,34 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C1:X62"/>
+  <dimension ref="C1:AA62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="25.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.140625" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" style="37"/>
+    <col min="12" max="12" width="8.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="3:25" x14ac:dyDescent="0.25">
       <c r="E1" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:25" x14ac:dyDescent="0.25">
       <c r="E2" s="1" t="s">
         <v>60</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="3" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C3" s="1" t="s">
         <v>58</v>
       </c>
@@ -3872,666 +7635,1573 @@
         <v>62</v>
       </c>
       <c r="F3" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="G3" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="H3" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="J3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L3" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="M3" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="N3" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="R3" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="S3" t="s">
+        <v>92</v>
+      </c>
+      <c r="T3" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="U3" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="W3" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="X3" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y3" s="37"/>
+    </row>
+    <row r="4" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>3</v>
       </c>
       <c r="D4" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="41">
+      <c r="E4" s="36">
         <f>1-H4</f>
         <v>0.99</v>
       </c>
-      <c r="F4" s="41">
+      <c r="F4" s="36">
         <f>1-G4</f>
         <v>0.66666666666666674</v>
       </c>
-      <c r="G4" s="44">
+      <c r="G4" s="39">
         <f>(3+2*0.5)/12</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="H4" s="41">
+      <c r="H4" s="36">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="I4" s="40"/>
+      <c r="J4" s="38">
+        <f>E4*F4*100</f>
+        <v>66</v>
+      </c>
+      <c r="K4" s="38">
+        <f>E4*G4*100</f>
+        <v>32.999999999999993</v>
+      </c>
+      <c r="L4" s="9">
+        <f>$H4*L$25*100</f>
+        <v>0.22764567437372507</v>
+      </c>
+      <c r="M4" s="9">
+        <f t="shared" ref="M4:N19" si="0">$H4*M$25*100</f>
+        <v>7.6957276987869846E-2</v>
+      </c>
+      <c r="N4" s="9">
+        <f t="shared" si="0"/>
+        <v>0.10648557133139604</v>
+      </c>
+      <c r="Q4" s="9">
+        <f t="shared" ref="Q4:X19" si="1">$H4*Q$25*100</f>
+        <v>2.5630021797415754E-2</v>
+      </c>
+      <c r="R4" s="9">
+        <f>$H4*SUM(R$25,O$25:P$25)*100</f>
+        <v>0.25663627595227045</v>
+      </c>
+      <c r="S4" s="9">
+        <f t="shared" si="1"/>
+        <v>1.6223488598557115E-2</v>
+      </c>
+      <c r="T4" s="9">
+        <f>$H4*SUM(T$25,V$25*0.5)*100</f>
+        <v>8.1186006545791389E-2</v>
+      </c>
+      <c r="U4" s="9">
+        <f>$H4*SUM(U$25,V$25*0.5)*100</f>
+        <v>6.9103370275246934E-2</v>
+      </c>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9">
+        <f t="shared" si="1"/>
+        <v>1.5991724475720583E-2</v>
+      </c>
+      <c r="X4" s="9">
+        <f>$H4*SUM(X$25,Y$25)*100</f>
+        <v>0.12414058966200681</v>
+      </c>
+    </row>
+    <row r="5" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C5" s="37" t="s">
+        <v>3</v>
+      </c>
       <c r="D5" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="41">
-        <f t="shared" ref="E5:E19" si="0">1-H5</f>
+      <c r="E5" s="36">
+        <f t="shared" ref="E5:E19" si="2">1-H5</f>
         <v>0.98</v>
       </c>
-      <c r="F5" s="45">
-        <f t="shared" ref="F5:F19" si="1">1-G5</f>
+      <c r="F5" s="40">
+        <f t="shared" ref="F5:F19" si="3">1-G5</f>
         <v>0.83333333333333337</v>
       </c>
-      <c r="G5" s="44">
+      <c r="G5" s="39">
         <f>(3*0.5+2*0.25)/12</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="H5" s="41">
+      <c r="H5" s="36">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="I5" s="40"/>
+      <c r="J5" s="38">
+        <f t="shared" ref="J5:J19" si="4">E5*F5*100</f>
+        <v>81.666666666666671</v>
+      </c>
+      <c r="K5" s="38">
+        <f t="shared" ref="K5:K19" si="5">E5*G5*100</f>
+        <v>16.333333333333332</v>
+      </c>
+      <c r="L5" s="9">
+        <f t="shared" ref="L5:L19" si="6">$H5*L$25*100</f>
+        <v>0.45529134874745014</v>
+      </c>
+      <c r="M5" s="9">
+        <f t="shared" si="0"/>
+        <v>0.15391455397573969</v>
+      </c>
+      <c r="N5" s="9">
+        <f t="shared" si="0"/>
+        <v>0.21297114266279207</v>
+      </c>
+      <c r="O5" s="37"/>
+      <c r="P5" s="37"/>
+      <c r="Q5" s="9">
+        <f t="shared" si="1"/>
+        <v>5.1260043594831509E-2</v>
+      </c>
+      <c r="R5" s="9">
+        <f t="shared" ref="R5:R19" si="7">$H5*SUM(R$25,O$25:P$25)*100</f>
+        <v>0.51327255190454091</v>
+      </c>
+      <c r="S5" s="9">
+        <f t="shared" si="1"/>
+        <v>3.244697719711423E-2</v>
+      </c>
+      <c r="T5" s="9">
+        <f t="shared" ref="T5:T19" si="8">$H5*SUM(T$25,V$25*0.5)*100</f>
+        <v>0.16237201309158278</v>
+      </c>
+      <c r="U5" s="9">
+        <f t="shared" ref="U5:U19" si="9">$H5*SUM(U$25,V$25*0.5)*100</f>
+        <v>0.13820674055049387</v>
+      </c>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9">
+        <f t="shared" si="1"/>
+        <v>3.1983448951441167E-2</v>
+      </c>
+      <c r="X5" s="9">
+        <f t="shared" ref="X5:X19" si="10">$H5*SUM(X$25,Y$25)*100</f>
+        <v>0.24828117932401361</v>
+      </c>
+    </row>
+    <row r="6" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C6" s="37" t="s">
+        <v>3</v>
+      </c>
       <c r="D6" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="41">
-        <f t="shared" si="0"/>
+      <c r="E6" s="36">
+        <f t="shared" si="2"/>
         <v>0.92999999999999994</v>
       </c>
-      <c r="F6" s="45">
-        <f t="shared" si="1"/>
+      <c r="F6" s="40">
+        <f t="shared" si="3"/>
         <v>0.66666666666666674</v>
       </c>
-      <c r="G6" s="44">
+      <c r="G6" s="39">
         <f>(3+2*0.5)/12</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="H6" s="41">
+      <c r="H6" s="36">
         <v>7.0000000000000007E-2</v>
       </c>
-    </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="I6" s="40"/>
+      <c r="J6" s="38">
+        <f t="shared" si="4"/>
+        <v>62</v>
+      </c>
+      <c r="K6" s="38">
+        <f t="shared" si="5"/>
+        <v>30.999999999999993</v>
+      </c>
+      <c r="L6" s="9">
+        <f t="shared" si="6"/>
+        <v>1.5935197206160754</v>
+      </c>
+      <c r="M6" s="9">
+        <f t="shared" si="0"/>
+        <v>0.53870093891508897</v>
+      </c>
+      <c r="N6" s="9">
+        <f t="shared" si="0"/>
+        <v>0.74539899931977227</v>
+      </c>
+      <c r="O6" s="37"/>
+      <c r="P6" s="37"/>
+      <c r="Q6" s="9">
+        <f t="shared" si="1"/>
+        <v>0.17941015258191029</v>
+      </c>
+      <c r="R6" s="9">
+        <f t="shared" si="7"/>
+        <v>1.7964539316658934</v>
+      </c>
+      <c r="S6" s="9">
+        <f t="shared" si="1"/>
+        <v>0.1135644201898998</v>
+      </c>
+      <c r="T6" s="9">
+        <f t="shared" si="8"/>
+        <v>0.56830204582053978</v>
+      </c>
+      <c r="U6" s="9">
+        <f t="shared" si="9"/>
+        <v>0.48372359192672859</v>
+      </c>
+      <c r="V6" s="9"/>
+      <c r="W6" s="9">
+        <f t="shared" si="1"/>
+        <v>0.11194207133004409</v>
+      </c>
+      <c r="X6" s="9">
+        <f t="shared" si="10"/>
+        <v>0.86898412763404764</v>
+      </c>
+    </row>
+    <row r="7" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C7" s="37" t="s">
+        <v>3</v>
+      </c>
       <c r="D7" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="41">
-        <f t="shared" si="0"/>
+      <c r="E7" s="36">
+        <f t="shared" si="2"/>
         <v>0.92</v>
       </c>
-      <c r="F7" s="45">
-        <f t="shared" si="1"/>
+      <c r="F7" s="40">
+        <f t="shared" si="3"/>
         <v>0.66666666666666674</v>
       </c>
-      <c r="G7" s="44">
+      <c r="G7" s="39">
         <f>(3+2*0.5)/12</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="H7" s="41">
+      <c r="H7" s="36">
         <v>0.08</v>
       </c>
-    </row>
-    <row r="8" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="I7" s="40"/>
+      <c r="J7" s="38">
+        <f t="shared" si="4"/>
+        <v>61.333333333333343</v>
+      </c>
+      <c r="K7" s="38">
+        <f t="shared" si="5"/>
+        <v>30.666666666666664</v>
+      </c>
+      <c r="L7" s="9">
+        <f t="shared" si="6"/>
+        <v>1.8211653949898006</v>
+      </c>
+      <c r="M7" s="9">
+        <f t="shared" si="0"/>
+        <v>0.61565821590295877</v>
+      </c>
+      <c r="N7" s="9">
+        <f t="shared" si="0"/>
+        <v>0.85188457065116829</v>
+      </c>
+      <c r="O7" s="37"/>
+      <c r="P7" s="37"/>
+      <c r="Q7" s="9">
+        <f t="shared" si="1"/>
+        <v>0.20504017437932603</v>
+      </c>
+      <c r="R7" s="9">
+        <f t="shared" si="7"/>
+        <v>2.0530902076181636</v>
+      </c>
+      <c r="S7" s="9">
+        <f t="shared" si="1"/>
+        <v>0.12978790878845692</v>
+      </c>
+      <c r="T7" s="9">
+        <f t="shared" si="8"/>
+        <v>0.64948805236633111</v>
+      </c>
+      <c r="U7" s="9">
+        <f t="shared" si="9"/>
+        <v>0.55282696220197547</v>
+      </c>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9">
+        <f t="shared" si="1"/>
+        <v>0.12793379580576467</v>
+      </c>
+      <c r="X7" s="9">
+        <f t="shared" si="10"/>
+        <v>0.99312471729605445</v>
+      </c>
+    </row>
+    <row r="8" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>6</v>
       </c>
       <c r="D8" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="41">
-        <f t="shared" si="0"/>
+      <c r="E8" s="36">
+        <f t="shared" si="2"/>
         <v>0.99</v>
       </c>
-      <c r="F8" s="45">
+      <c r="F8" s="40">
         <f>1-G8</f>
         <v>0.66666666666666674</v>
       </c>
-      <c r="G8" s="44">
+      <c r="G8" s="39">
         <f>(3+2*0.5)/12</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="H8" s="41">
+      <c r="H8" s="36">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="9" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="I8" s="40"/>
+      <c r="J8" s="38">
+        <f t="shared" si="4"/>
+        <v>66</v>
+      </c>
+      <c r="K8" s="38">
+        <f t="shared" si="5"/>
+        <v>32.999999999999993</v>
+      </c>
+      <c r="L8" s="9">
+        <f t="shared" si="6"/>
+        <v>0.22764567437372507</v>
+      </c>
+      <c r="M8" s="9">
+        <f t="shared" si="0"/>
+        <v>7.6957276987869846E-2</v>
+      </c>
+      <c r="N8" s="9">
+        <f t="shared" si="0"/>
+        <v>0.10648557133139604</v>
+      </c>
+      <c r="O8" s="37"/>
+      <c r="P8" s="37"/>
+      <c r="Q8" s="9">
+        <f t="shared" si="1"/>
+        <v>2.5630021797415754E-2</v>
+      </c>
+      <c r="R8" s="9">
+        <f t="shared" si="7"/>
+        <v>0.25663627595227045</v>
+      </c>
+      <c r="S8" s="9">
+        <f t="shared" si="1"/>
+        <v>1.6223488598557115E-2</v>
+      </c>
+      <c r="T8" s="9">
+        <f t="shared" si="8"/>
+        <v>8.1186006545791389E-2</v>
+      </c>
+      <c r="U8" s="9">
+        <f t="shared" si="9"/>
+        <v>6.9103370275246934E-2</v>
+      </c>
+      <c r="V8" s="9"/>
+      <c r="W8" s="9">
+        <f t="shared" si="1"/>
+        <v>1.5991724475720583E-2</v>
+      </c>
+      <c r="X8" s="9">
+        <f t="shared" si="10"/>
+        <v>0.12414058966200681</v>
+      </c>
+    </row>
+    <row r="9" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C9" s="37" t="s">
+        <v>6</v>
+      </c>
       <c r="D9" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="41">
-        <f t="shared" si="0"/>
+      <c r="E9" s="36">
+        <f t="shared" si="2"/>
         <v>0.98</v>
       </c>
-      <c r="F9" s="45">
-        <f t="shared" si="1"/>
+      <c r="F9" s="40">
+        <f t="shared" si="3"/>
         <v>0.83333333333333337</v>
       </c>
-      <c r="G9" s="44">
+      <c r="G9" s="39">
         <f>(3*0.5+2*0.25)/12</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="H9" s="41">
+      <c r="H9" s="36">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="I9" s="40"/>
+      <c r="J9" s="38">
+        <f t="shared" si="4"/>
+        <v>81.666666666666671</v>
+      </c>
+      <c r="K9" s="38">
+        <f t="shared" si="5"/>
+        <v>16.333333333333332</v>
+      </c>
+      <c r="L9" s="9">
+        <f t="shared" si="6"/>
+        <v>0.45529134874745014</v>
+      </c>
+      <c r="M9" s="9">
+        <f t="shared" si="0"/>
+        <v>0.15391455397573969</v>
+      </c>
+      <c r="N9" s="9">
+        <f t="shared" si="0"/>
+        <v>0.21297114266279207</v>
+      </c>
+      <c r="O9" s="37"/>
+      <c r="P9" s="37"/>
+      <c r="Q9" s="9">
+        <f t="shared" si="1"/>
+        <v>5.1260043594831509E-2</v>
+      </c>
+      <c r="R9" s="9">
+        <f t="shared" si="7"/>
+        <v>0.51327255190454091</v>
+      </c>
+      <c r="S9" s="9">
+        <f t="shared" si="1"/>
+        <v>3.244697719711423E-2</v>
+      </c>
+      <c r="T9" s="9">
+        <f t="shared" si="8"/>
+        <v>0.16237201309158278</v>
+      </c>
+      <c r="U9" s="9">
+        <f t="shared" si="9"/>
+        <v>0.13820674055049387</v>
+      </c>
+      <c r="V9" s="9"/>
+      <c r="W9" s="9">
+        <f t="shared" si="1"/>
+        <v>3.1983448951441167E-2</v>
+      </c>
+      <c r="X9" s="9">
+        <f t="shared" si="10"/>
+        <v>0.24828117932401361</v>
+      </c>
+    </row>
+    <row r="10" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C10" s="37" t="s">
+        <v>6</v>
+      </c>
       <c r="D10" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="41">
-        <f t="shared" si="0"/>
+      <c r="E10" s="36">
+        <f t="shared" si="2"/>
         <v>0.92999999999999994</v>
       </c>
-      <c r="F10" s="45">
-        <f t="shared" si="1"/>
+      <c r="F10" s="40">
+        <f t="shared" si="3"/>
         <v>0.66666666666666674</v>
       </c>
-      <c r="G10" s="44">
+      <c r="G10" s="39">
         <f>(3+2*0.5)/12</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="H10" s="41">
+      <c r="H10" s="36">
         <v>7.0000000000000007E-2</v>
       </c>
-    </row>
-    <row r="11" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="I10" s="40"/>
+      <c r="J10" s="38">
+        <f t="shared" si="4"/>
+        <v>62</v>
+      </c>
+      <c r="K10" s="38">
+        <f t="shared" si="5"/>
+        <v>30.999999999999993</v>
+      </c>
+      <c r="L10" s="9">
+        <f t="shared" si="6"/>
+        <v>1.5935197206160754</v>
+      </c>
+      <c r="M10" s="9">
+        <f t="shared" si="0"/>
+        <v>0.53870093891508897</v>
+      </c>
+      <c r="N10" s="9">
+        <f t="shared" si="0"/>
+        <v>0.74539899931977227</v>
+      </c>
+      <c r="O10" s="37"/>
+      <c r="P10" s="37"/>
+      <c r="Q10" s="9">
+        <f t="shared" si="1"/>
+        <v>0.17941015258191029</v>
+      </c>
+      <c r="R10" s="9">
+        <f t="shared" si="7"/>
+        <v>1.7964539316658934</v>
+      </c>
+      <c r="S10" s="9">
+        <f t="shared" si="1"/>
+        <v>0.1135644201898998</v>
+      </c>
+      <c r="T10" s="9">
+        <f t="shared" si="8"/>
+        <v>0.56830204582053978</v>
+      </c>
+      <c r="U10" s="9">
+        <f t="shared" si="9"/>
+        <v>0.48372359192672859</v>
+      </c>
+      <c r="V10" s="9"/>
+      <c r="W10" s="9">
+        <f t="shared" si="1"/>
+        <v>0.11194207133004409</v>
+      </c>
+      <c r="X10" s="9">
+        <f t="shared" si="10"/>
+        <v>0.86898412763404764</v>
+      </c>
+    </row>
+    <row r="11" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C11" s="37" t="s">
+        <v>6</v>
+      </c>
       <c r="D11" t="s">
         <v>5</v>
       </c>
-      <c r="E11" s="41">
-        <f t="shared" si="0"/>
+      <c r="E11" s="36">
+        <f t="shared" si="2"/>
         <v>0.97</v>
       </c>
-      <c r="F11" s="45">
-        <f t="shared" si="1"/>
+      <c r="F11" s="40">
+        <f t="shared" si="3"/>
         <v>0.66666666666666674</v>
       </c>
-      <c r="G11" s="44">
+      <c r="G11" s="39">
         <f>(3+2*0.5)/12</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="H11" s="41">
+      <c r="H11" s="36">
         <v>0.03</v>
       </c>
-    </row>
-    <row r="12" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="I11" s="40"/>
+      <c r="J11" s="38">
+        <f t="shared" si="4"/>
+        <v>64.666666666666671</v>
+      </c>
+      <c r="K11" s="38">
+        <f t="shared" si="5"/>
+        <v>32.333333333333329</v>
+      </c>
+      <c r="L11" s="9">
+        <f t="shared" si="6"/>
+        <v>0.6829370231211751</v>
+      </c>
+      <c r="M11" s="9">
+        <f t="shared" si="0"/>
+        <v>0.23087183096360953</v>
+      </c>
+      <c r="N11" s="9">
+        <f t="shared" si="0"/>
+        <v>0.31945671399418812</v>
+      </c>
+      <c r="O11" s="37"/>
+      <c r="P11" s="37"/>
+      <c r="Q11" s="9">
+        <f t="shared" si="1"/>
+        <v>7.6890065392247256E-2</v>
+      </c>
+      <c r="R11" s="9">
+        <f t="shared" si="7"/>
+        <v>0.76990882785681136</v>
+      </c>
+      <c r="S11" s="9">
+        <f t="shared" si="1"/>
+        <v>4.8670465795671344E-2</v>
+      </c>
+      <c r="T11" s="9">
+        <f t="shared" si="8"/>
+        <v>0.24355801963737417</v>
+      </c>
+      <c r="U11" s="9">
+        <f t="shared" si="9"/>
+        <v>0.20731011082574077</v>
+      </c>
+      <c r="V11" s="9"/>
+      <c r="W11" s="9">
+        <f t="shared" si="1"/>
+        <v>4.7975173427161746E-2</v>
+      </c>
+      <c r="X11" s="9">
+        <f t="shared" si="10"/>
+        <v>0.37242176898602036</v>
+      </c>
+    </row>
+    <row r="12" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
         <v>7</v>
       </c>
       <c r="D12" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="41">
-        <f t="shared" si="0"/>
+      <c r="E12" s="36">
+        <f t="shared" si="2"/>
         <v>0.99</v>
       </c>
-      <c r="F12" s="45">
+      <c r="F12" s="40">
         <f>1-G12</f>
         <v>0.66666666666666674</v>
       </c>
-      <c r="G12" s="44">
+      <c r="G12" s="39">
         <f>(3+2*0.5)/12</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="H12" s="41">
+      <c r="H12" s="36">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="13" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="I12" s="40"/>
+      <c r="J12" s="38">
+        <f t="shared" si="4"/>
+        <v>66</v>
+      </c>
+      <c r="K12" s="38">
+        <f t="shared" si="5"/>
+        <v>32.999999999999993</v>
+      </c>
+      <c r="L12" s="9">
+        <f t="shared" si="6"/>
+        <v>0.22764567437372507</v>
+      </c>
+      <c r="M12" s="9">
+        <f t="shared" si="0"/>
+        <v>7.6957276987869846E-2</v>
+      </c>
+      <c r="N12" s="9">
+        <f t="shared" si="0"/>
+        <v>0.10648557133139604</v>
+      </c>
+      <c r="O12" s="37"/>
+      <c r="P12" s="37"/>
+      <c r="Q12" s="9">
+        <f t="shared" si="1"/>
+        <v>2.5630021797415754E-2</v>
+      </c>
+      <c r="R12" s="9">
+        <f t="shared" si="7"/>
+        <v>0.25663627595227045</v>
+      </c>
+      <c r="S12" s="9">
+        <f t="shared" si="1"/>
+        <v>1.6223488598557115E-2</v>
+      </c>
+      <c r="T12" s="9">
+        <f t="shared" si="8"/>
+        <v>8.1186006545791389E-2</v>
+      </c>
+      <c r="U12" s="9">
+        <f t="shared" si="9"/>
+        <v>6.9103370275246934E-2</v>
+      </c>
+      <c r="V12" s="9"/>
+      <c r="W12" s="9">
+        <f t="shared" si="1"/>
+        <v>1.5991724475720583E-2</v>
+      </c>
+      <c r="X12" s="9">
+        <f t="shared" si="10"/>
+        <v>0.12414058966200681</v>
+      </c>
+    </row>
+    <row r="13" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C13" s="37" t="s">
+        <v>7</v>
+      </c>
       <c r="D13" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="41">
-        <f t="shared" si="0"/>
+      <c r="E13" s="36">
+        <f t="shared" si="2"/>
         <v>0.96</v>
       </c>
-      <c r="F13" s="45">
-        <f t="shared" si="1"/>
+      <c r="F13" s="40">
+        <f t="shared" si="3"/>
         <v>0.83333333333333337</v>
       </c>
-      <c r="G13" s="44">
+      <c r="G13" s="39">
         <f>(3*0.5+2*0.25)/12</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="H13" s="41">
+      <c r="H13" s="36">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="14" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="I13" s="40"/>
+      <c r="J13" s="38">
+        <f t="shared" si="4"/>
+        <v>80</v>
+      </c>
+      <c r="K13" s="38">
+        <f t="shared" si="5"/>
+        <v>15.999999999999998</v>
+      </c>
+      <c r="L13" s="9">
+        <f t="shared" si="6"/>
+        <v>0.91058269749490028</v>
+      </c>
+      <c r="M13" s="9">
+        <f t="shared" si="0"/>
+        <v>0.30782910795147939</v>
+      </c>
+      <c r="N13" s="9">
+        <f t="shared" si="0"/>
+        <v>0.42594228532558415</v>
+      </c>
+      <c r="O13" s="37"/>
+      <c r="P13" s="37"/>
+      <c r="Q13" s="9">
+        <f t="shared" si="1"/>
+        <v>0.10252008718966302</v>
+      </c>
+      <c r="R13" s="9">
+        <f t="shared" si="7"/>
+        <v>1.0265451038090818</v>
+      </c>
+      <c r="S13" s="9">
+        <f t="shared" si="1"/>
+        <v>6.4893954394228459E-2</v>
+      </c>
+      <c r="T13" s="9">
+        <f t="shared" si="8"/>
+        <v>0.32474402618316556</v>
+      </c>
+      <c r="U13" s="9">
+        <f t="shared" si="9"/>
+        <v>0.27641348110098773</v>
+      </c>
+      <c r="V13" s="9"/>
+      <c r="W13" s="9">
+        <f t="shared" si="1"/>
+        <v>6.3966897902882333E-2</v>
+      </c>
+      <c r="X13" s="9">
+        <f t="shared" si="10"/>
+        <v>0.49656235864802722</v>
+      </c>
+    </row>
+    <row r="14" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C14" s="37" t="s">
+        <v>7</v>
+      </c>
       <c r="D14" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="41">
-        <f t="shared" si="0"/>
+      <c r="E14" s="36">
+        <f t="shared" si="2"/>
         <v>0.92999999999999994</v>
       </c>
-      <c r="F14" s="45">
-        <f t="shared" si="1"/>
+      <c r="F14" s="40">
+        <f t="shared" si="3"/>
         <v>0.66666666666666674</v>
       </c>
-      <c r="G14" s="44">
+      <c r="G14" s="39">
         <f>(3+2*0.5)/12</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="H14" s="41">
+      <c r="H14" s="36">
         <v>7.0000000000000007E-2</v>
       </c>
-    </row>
-    <row r="15" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="I14" s="40"/>
+      <c r="J14" s="38">
+        <f t="shared" si="4"/>
+        <v>62</v>
+      </c>
+      <c r="K14" s="38">
+        <f t="shared" si="5"/>
+        <v>30.999999999999993</v>
+      </c>
+      <c r="L14" s="9">
+        <f t="shared" si="6"/>
+        <v>1.5935197206160754</v>
+      </c>
+      <c r="M14" s="9">
+        <f t="shared" si="0"/>
+        <v>0.53870093891508897</v>
+      </c>
+      <c r="N14" s="9">
+        <f t="shared" si="0"/>
+        <v>0.74539899931977227</v>
+      </c>
+      <c r="O14" s="37"/>
+      <c r="P14" s="37"/>
+      <c r="Q14" s="9">
+        <f t="shared" si="1"/>
+        <v>0.17941015258191029</v>
+      </c>
+      <c r="R14" s="9">
+        <f t="shared" si="7"/>
+        <v>1.7964539316658934</v>
+      </c>
+      <c r="S14" s="9">
+        <f t="shared" si="1"/>
+        <v>0.1135644201898998</v>
+      </c>
+      <c r="T14" s="9">
+        <f t="shared" si="8"/>
+        <v>0.56830204582053978</v>
+      </c>
+      <c r="U14" s="9">
+        <f t="shared" si="9"/>
+        <v>0.48372359192672859</v>
+      </c>
+      <c r="V14" s="9"/>
+      <c r="W14" s="9">
+        <f t="shared" si="1"/>
+        <v>0.11194207133004409</v>
+      </c>
+      <c r="X14" s="9">
+        <f t="shared" si="10"/>
+        <v>0.86898412763404764</v>
+      </c>
+    </row>
+    <row r="15" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C15" s="37" t="s">
+        <v>7</v>
+      </c>
       <c r="D15" t="s">
         <v>5</v>
       </c>
-      <c r="E15" s="41">
-        <f t="shared" si="0"/>
+      <c r="E15" s="36">
+        <f t="shared" si="2"/>
         <v>0.95</v>
       </c>
-      <c r="F15" s="45">
-        <f t="shared" si="1"/>
+      <c r="F15" s="40">
+        <f t="shared" si="3"/>
         <v>0.66666666666666674</v>
       </c>
-      <c r="G15" s="44">
+      <c r="G15" s="39">
         <f>(3+2*0.5)/12</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="H15" s="41">
+      <c r="H15" s="36">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="16" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="I15" s="40"/>
+      <c r="J15" s="38">
+        <f t="shared" si="4"/>
+        <v>63.333333333333343</v>
+      </c>
+      <c r="K15" s="38">
+        <f t="shared" si="5"/>
+        <v>31.666666666666664</v>
+      </c>
+      <c r="L15" s="9">
+        <f t="shared" si="6"/>
+        <v>1.1382283718686252</v>
+      </c>
+      <c r="M15" s="9">
+        <f t="shared" si="0"/>
+        <v>0.38478638493934925</v>
+      </c>
+      <c r="N15" s="9">
+        <f t="shared" si="0"/>
+        <v>0.53242785665698023</v>
+      </c>
+      <c r="O15" s="37"/>
+      <c r="P15" s="37"/>
+      <c r="Q15" s="9">
+        <f t="shared" si="1"/>
+        <v>0.12815010898707879</v>
+      </c>
+      <c r="R15" s="9">
+        <f t="shared" si="7"/>
+        <v>1.2831813797613523</v>
+      </c>
+      <c r="S15" s="9">
+        <f t="shared" si="1"/>
+        <v>8.1117442992785574E-2</v>
+      </c>
+      <c r="T15" s="9">
+        <f t="shared" si="8"/>
+        <v>0.40593003272895695</v>
+      </c>
+      <c r="U15" s="9">
+        <f t="shared" si="9"/>
+        <v>0.34551685137623467</v>
+      </c>
+      <c r="V15" s="9"/>
+      <c r="W15" s="9">
+        <f t="shared" si="1"/>
+        <v>7.995862237860292E-2</v>
+      </c>
+      <c r="X15" s="9">
+        <f t="shared" si="10"/>
+        <v>0.62070294831003403</v>
+      </c>
+    </row>
+    <row r="16" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
         <v>8</v>
       </c>
       <c r="D16" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="41">
-        <f t="shared" si="0"/>
+      <c r="E16" s="36">
+        <f t="shared" si="2"/>
         <v>0.94</v>
       </c>
-      <c r="F16" s="45">
+      <c r="F16" s="40">
         <f>1-G16</f>
         <v>0.66666666666666674</v>
       </c>
-      <c r="G16" s="44">
+      <c r="G16" s="39">
         <f>(3+2*0.5)/12</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="H16" s="41">
+      <c r="H16" s="36">
         <v>0.06</v>
       </c>
-    </row>
-    <row r="17" spans="4:24" x14ac:dyDescent="0.25">
+      <c r="I16" s="40"/>
+      <c r="J16" s="38">
+        <f t="shared" si="4"/>
+        <v>62.666666666666671</v>
+      </c>
+      <c r="K16" s="38">
+        <f t="shared" si="5"/>
+        <v>31.333333333333329</v>
+      </c>
+      <c r="L16" s="9">
+        <f t="shared" si="6"/>
+        <v>1.3658740462423502</v>
+      </c>
+      <c r="M16" s="9">
+        <f t="shared" si="0"/>
+        <v>0.46174366192721905</v>
+      </c>
+      <c r="N16" s="9">
+        <f t="shared" si="0"/>
+        <v>0.63891342798837625</v>
+      </c>
+      <c r="O16" s="37"/>
+      <c r="P16" s="37"/>
+      <c r="Q16" s="9">
+        <f t="shared" si="1"/>
+        <v>0.15378013078449451</v>
+      </c>
+      <c r="R16" s="9">
+        <f t="shared" si="7"/>
+        <v>1.5398176557136227</v>
+      </c>
+      <c r="S16" s="9">
+        <f t="shared" si="1"/>
+        <v>9.7340931591342689E-2</v>
+      </c>
+      <c r="T16" s="9">
+        <f t="shared" si="8"/>
+        <v>0.48711603927474834</v>
+      </c>
+      <c r="U16" s="9">
+        <f t="shared" si="9"/>
+        <v>0.41462022165148155</v>
+      </c>
+      <c r="V16" s="9"/>
+      <c r="W16" s="9">
+        <f t="shared" si="1"/>
+        <v>9.5950346854323493E-2</v>
+      </c>
+      <c r="X16" s="9">
+        <f t="shared" si="10"/>
+        <v>0.74484353797204073</v>
+      </c>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.25">
+      <c r="C17" s="37" t="s">
+        <v>8</v>
+      </c>
       <c r="D17" t="s">
         <v>10</v>
       </c>
-      <c r="E17" s="41">
-        <f t="shared" si="0"/>
+      <c r="E17" s="36">
+        <f t="shared" si="2"/>
         <v>0.89</v>
       </c>
-      <c r="F17" s="45">
-        <f t="shared" si="1"/>
+      <c r="F17" s="40">
+        <f t="shared" si="3"/>
         <v>0.83333333333333337</v>
       </c>
-      <c r="G17" s="44">
+      <c r="G17" s="39">
         <f>(3*0.5+2*0.25)/12</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="H17" s="41">
+      <c r="H17" s="36">
         <v>0.11</v>
       </c>
-    </row>
-    <row r="18" spans="4:24" x14ac:dyDescent="0.25">
+      <c r="I17" s="40"/>
+      <c r="J17" s="38">
+        <f t="shared" si="4"/>
+        <v>74.166666666666671</v>
+      </c>
+      <c r="K17" s="38">
+        <f t="shared" si="5"/>
+        <v>14.833333333333332</v>
+      </c>
+      <c r="L17" s="9">
+        <f t="shared" si="6"/>
+        <v>2.5041024181109752</v>
+      </c>
+      <c r="M17" s="9">
+        <f t="shared" si="0"/>
+        <v>0.8465300468665683</v>
+      </c>
+      <c r="N17" s="9">
+        <f t="shared" si="0"/>
+        <v>1.1713412846453564</v>
+      </c>
+      <c r="O17" s="37"/>
+      <c r="P17" s="37"/>
+      <c r="Q17" s="9">
+        <f t="shared" si="1"/>
+        <v>0.28193023977157328</v>
+      </c>
+      <c r="R17" s="9">
+        <f t="shared" si="7"/>
+        <v>2.8229990354749752</v>
+      </c>
+      <c r="S17" s="9">
+        <f t="shared" si="1"/>
+        <v>0.17845837458412825</v>
+      </c>
+      <c r="T17" s="9">
+        <f t="shared" si="8"/>
+        <v>0.89304607200370534</v>
+      </c>
+      <c r="U17" s="9">
+        <f t="shared" si="9"/>
+        <v>0.76013707302771627</v>
+      </c>
+      <c r="V17" s="9"/>
+      <c r="W17" s="9">
+        <f t="shared" si="1"/>
+        <v>0.17590896923292643</v>
+      </c>
+      <c r="X17" s="9">
+        <f t="shared" si="10"/>
+        <v>1.3655464862820748</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.25">
+      <c r="C18" s="37" t="s">
+        <v>8</v>
+      </c>
       <c r="D18" t="s">
         <v>4</v>
       </c>
-      <c r="E18" s="41">
-        <f t="shared" si="0"/>
+      <c r="E18" s="36">
+        <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
-      <c r="F18" s="45">
-        <f t="shared" si="1"/>
+      <c r="F18" s="40">
+        <f t="shared" si="3"/>
         <v>0.66666666666666674</v>
       </c>
-      <c r="G18" s="44">
+      <c r="G18" s="39">
         <f>(3+2*0.5)/12</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="H18" s="41">
+      <c r="H18" s="36">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="19" spans="4:24" x14ac:dyDescent="0.25">
+      <c r="I18" s="40"/>
+      <c r="J18" s="38">
+        <f t="shared" si="4"/>
+        <v>60.000000000000007</v>
+      </c>
+      <c r="K18" s="38">
+        <f t="shared" si="5"/>
+        <v>30</v>
+      </c>
+      <c r="L18" s="9">
+        <f t="shared" si="6"/>
+        <v>2.2764567437372505</v>
+      </c>
+      <c r="M18" s="9">
+        <f t="shared" si="0"/>
+        <v>0.76957276987869849</v>
+      </c>
+      <c r="N18" s="9">
+        <f t="shared" si="0"/>
+        <v>1.0648557133139605</v>
+      </c>
+      <c r="O18" s="37"/>
+      <c r="P18" s="37"/>
+      <c r="Q18" s="9">
+        <f t="shared" si="1"/>
+        <v>0.25630021797415758</v>
+      </c>
+      <c r="R18" s="9">
+        <f t="shared" si="7"/>
+        <v>2.5663627595227045</v>
+      </c>
+      <c r="S18" s="9">
+        <f t="shared" si="1"/>
+        <v>0.16223488598557115</v>
+      </c>
+      <c r="T18" s="9">
+        <f t="shared" si="8"/>
+        <v>0.81186006545791389</v>
+      </c>
+      <c r="U18" s="9">
+        <f t="shared" si="9"/>
+        <v>0.69103370275246934</v>
+      </c>
+      <c r="V18" s="9"/>
+      <c r="W18" s="9">
+        <f t="shared" si="1"/>
+        <v>0.15991724475720584</v>
+      </c>
+      <c r="X18" s="9">
+        <f t="shared" si="10"/>
+        <v>1.2414058966200681</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.25">
+      <c r="C19" s="37" t="s">
+        <v>8</v>
+      </c>
       <c r="D19" t="s">
         <v>5</v>
       </c>
-      <c r="E19" s="41">
-        <f t="shared" si="0"/>
+      <c r="E19" s="36">
+        <f t="shared" si="2"/>
         <v>0.88</v>
       </c>
-      <c r="F19" s="45">
-        <f t="shared" si="1"/>
+      <c r="F19" s="40">
+        <f t="shared" si="3"/>
         <v>0.66666666666666674</v>
       </c>
-      <c r="G19" s="44">
+      <c r="G19" s="39">
         <f>(3+2*0.5)/12</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="H19" s="41">
+      <c r="H19" s="36">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="21" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="G21" s="34" t="s">
+      <c r="I19" s="40"/>
+      <c r="J19" s="38">
+        <f t="shared" si="4"/>
+        <v>58.666666666666679</v>
+      </c>
+      <c r="K19" s="38">
+        <f t="shared" si="5"/>
+        <v>29.333333333333332</v>
+      </c>
+      <c r="L19" s="9">
+        <f t="shared" si="6"/>
+        <v>2.7317480924847004</v>
+      </c>
+      <c r="M19" s="9">
+        <f t="shared" si="0"/>
+        <v>0.9234873238544381</v>
+      </c>
+      <c r="N19" s="9">
+        <f t="shared" si="0"/>
+        <v>1.2778268559767525</v>
+      </c>
+      <c r="O19" s="37"/>
+      <c r="P19" s="37"/>
+      <c r="Q19" s="9">
+        <f t="shared" si="1"/>
+        <v>0.30756026156898902</v>
+      </c>
+      <c r="R19" s="9">
+        <f t="shared" si="7"/>
+        <v>3.0796353114272454</v>
+      </c>
+      <c r="S19" s="9">
+        <f t="shared" si="1"/>
+        <v>0.19468186318268538</v>
+      </c>
+      <c r="T19" s="9">
+        <f t="shared" si="8"/>
+        <v>0.97423207854949667</v>
+      </c>
+      <c r="U19" s="9">
+        <f t="shared" si="9"/>
+        <v>0.82924044330296309</v>
+      </c>
+      <c r="V19" s="9"/>
+      <c r="W19" s="9">
+        <f t="shared" si="1"/>
+        <v>0.19190069370864699</v>
+      </c>
+      <c r="X19" s="9">
+        <f t="shared" si="10"/>
+        <v>1.4896870759440815</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.25">
+      <c r="J21" s="34" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="H22" t="s">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.25">
+      <c r="K22" t="s">
         <v>62</v>
       </c>
-      <c r="I22" t="s">
+      <c r="L22" t="s">
         <v>64</v>
       </c>
-      <c r="J22" t="s">
+      <c r="M22" t="s">
         <v>67</v>
       </c>
-      <c r="K22" t="s">
+      <c r="N22" t="s">
         <v>68</v>
       </c>
-      <c r="L22" t="s">
+      <c r="O22" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="M22" t="s">
+      <c r="P22" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="N22" t="s">
+      <c r="Q22" t="s">
         <v>69</v>
       </c>
-      <c r="O22" t="s">
+      <c r="R22" t="s">
         <v>70</v>
       </c>
-      <c r="P22" t="s">
+      <c r="S22" t="s">
         <v>71</v>
       </c>
-      <c r="Q22" t="s">
+      <c r="T22" t="s">
         <v>72</v>
       </c>
-      <c r="R22" t="s">
+      <c r="U22" t="s">
         <v>73</v>
       </c>
-      <c r="S22" t="s">
+      <c r="V22" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="T22" t="s">
+      <c r="W22" t="s">
         <v>75</v>
       </c>
-      <c r="U22" t="s">
+      <c r="X22" t="s">
         <v>76</v>
       </c>
-      <c r="V22" t="s">
+      <c r="Y22" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="W22" t="s">
+      <c r="Z22" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="X22" t="s">
+      <c r="AA22" s="4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="G23" t="s">
+    <row r="23" spans="3:27" x14ac:dyDescent="0.25">
+      <c r="J23" t="s">
         <v>80</v>
       </c>
-      <c r="H23">
-        <f>SUM(I23:X23)</f>
-        <v>37089.040000000001</v>
-      </c>
-      <c r="I23">
+      <c r="K23">
+        <f>SUM(L23:Y23)</f>
+        <v>35183.040000000001</v>
+      </c>
+      <c r="L23">
         <v>8697.39</v>
       </c>
-      <c r="J23">
+      <c r="M23">
         <v>2726.58</v>
       </c>
-      <c r="K23">
+      <c r="N23">
         <v>4044.63</v>
       </c>
-      <c r="L23">
+      <c r="O23">
         <v>637.71</v>
       </c>
-      <c r="M23">
+      <c r="P23">
         <v>3923.7</v>
       </c>
-      <c r="N23">
+      <c r="Q23">
         <v>968.31</v>
       </c>
-      <c r="O23">
+      <c r="R23">
         <v>5403.57</v>
       </c>
-      <c r="P23">
+      <c r="S23">
         <v>472</v>
       </c>
-      <c r="Q23">
+      <c r="T23">
         <v>789.30000000000007</v>
       </c>
-      <c r="R23">
+      <c r="U23">
         <v>1494</v>
       </c>
-      <c r="S23">
+      <c r="V23">
         <v>1555.9499999999998</v>
       </c>
-      <c r="T23">
+      <c r="W23">
         <v>607.5</v>
       </c>
-      <c r="U23">
+      <c r="X23">
         <v>2255.4</v>
       </c>
-      <c r="V23">
+      <c r="Y23">
         <v>1607</v>
       </c>
-      <c r="W23">
+      <c r="Z23">
         <v>1251</v>
       </c>
-      <c r="X23">
+      <c r="AA23">
         <v>655</v>
       </c>
     </row>
-    <row r="24" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="G24" t="s">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.25">
+      <c r="J24" t="s">
         <v>81</v>
       </c>
-      <c r="H24">
-        <f>SUM(I24:X24)</f>
-        <v>3742.5450000000001</v>
-      </c>
-      <c r="I24">
+      <c r="K24" s="37">
+        <f>SUM(L24:Y24)</f>
+        <v>3649.5450000000001</v>
+      </c>
+      <c r="L24">
         <v>142.68</v>
       </c>
-      <c r="J24">
+      <c r="M24">
         <v>261.87</v>
       </c>
-      <c r="K24">
+      <c r="N24">
         <v>90.48</v>
       </c>
-      <c r="L24">
+      <c r="O24">
         <v>0</v>
       </c>
-      <c r="M24">
+      <c r="P24">
         <v>0</v>
       </c>
-      <c r="N24">
+      <c r="Q24">
         <v>26.97</v>
       </c>
-      <c r="O24">
+      <c r="R24">
         <v>0.87</v>
       </c>
-      <c r="P24">
+      <c r="S24">
         <v>158</v>
       </c>
-      <c r="Q24">
+      <c r="T24">
         <v>1229.4000000000001</v>
       </c>
-      <c r="R24">
+      <c r="U24">
         <v>55.5</v>
       </c>
-      <c r="S24">
+      <c r="V24">
         <v>711.97499999999991</v>
       </c>
-      <c r="T24">
+      <c r="W24">
         <v>13.5</v>
       </c>
-      <c r="U24">
+      <c r="X24">
         <v>591.30000000000007</v>
       </c>
-      <c r="V24">
+      <c r="Y24">
         <v>367</v>
       </c>
-      <c r="W24">
+      <c r="Z24">
         <v>0</v>
       </c>
-      <c r="X24">
+      <c r="AA24">
         <v>93</v>
       </c>
     </row>
-    <row r="25" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="G25" t="s">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.25">
+      <c r="I25" s="39"/>
+      <c r="J25" t="s">
         <v>84</v>
       </c>
-      <c r="H25" s="35">
-        <f t="shared" ref="H25:X25" si="2">SUM(H23:H24)/SUM($H23:$H24)</f>
+      <c r="K25" s="35">
+        <f>SUM(K23:K24)/SUM($K23:$K24)</f>
         <v>1</v>
       </c>
-      <c r="I25" s="35">
-        <f t="shared" si="2"/>
-        <v>0.21650077997217104</v>
-      </c>
-      <c r="J25" s="35">
-        <f t="shared" si="2"/>
-        <v>7.318966432481129E-2</v>
-      </c>
-      <c r="K25" s="35">
-        <f t="shared" si="2"/>
-        <v>0.10127233610941137</v>
-      </c>
       <c r="L25" s="35">
-        <f t="shared" si="2"/>
-        <v>1.5618056462907332E-2</v>
+        <f>SUM(L23:L24)/SUM($K23:$K24)</f>
+        <v>0.22764567437372504</v>
       </c>
       <c r="M25" s="35">
-        <f t="shared" si="2"/>
-        <v>9.609472666809285E-2</v>
+        <f>SUM(M23:M24)/SUM($K23:$K24)</f>
+        <v>7.6957276987869846E-2</v>
       </c>
       <c r="N25" s="35">
-        <f t="shared" si="2"/>
-        <v>2.4375247740199162E-2</v>
+        <f>SUM(N23:N24)/SUM($K23:$K24)</f>
+        <v>0.10648557133139604</v>
       </c>
       <c r="O25" s="35">
-        <f t="shared" si="2"/>
-        <v>0.13235929979206049</v>
+        <f>SUM(O23:O24)/SUM($K23:$K24)</f>
+        <v>1.6422033197120409E-2</v>
       </c>
       <c r="P25" s="35">
-        <f t="shared" si="2"/>
-        <v>1.5429232051609067E-2</v>
+        <f>SUM(P23:P24)/SUM($K23:$K24)</f>
+        <v>0.10104143208596594</v>
       </c>
       <c r="Q25" s="35">
-        <f t="shared" si="2"/>
-        <v>4.9439667845370204E-2</v>
+        <f>SUM(Q23:Q24)/SUM($K23:$K24)</f>
+        <v>2.5630021797415754E-2</v>
       </c>
       <c r="R25" s="35">
-        <f t="shared" si="2"/>
-        <v>3.7948563593600396E-2</v>
+        <f>SUM(R23:R24)/SUM($K23:$K24)</f>
+        <v>0.13917281066918413</v>
       </c>
       <c r="S25" s="35">
-        <f t="shared" si="2"/>
-        <v>5.5543398572453155E-2</v>
+        <f>SUM(S23:S24)/SUM($K23:$K24)</f>
+        <v>1.6223488598557115E-2</v>
       </c>
       <c r="T25" s="35">
-        <f t="shared" si="2"/>
-        <v>1.5208814450871794E-2</v>
+        <f>SUM(T23:T24)/SUM($K23:$K24)</f>
+        <v>5.1984692752233733E-2</v>
       </c>
       <c r="U25" s="35">
-        <f t="shared" si="2"/>
-        <v>6.9718087113199267E-2</v>
+        <f>SUM(U23:U24)/SUM($K23:$K24)</f>
+        <v>3.9902056481689284E-2</v>
       </c>
       <c r="V25" s="35">
-        <f t="shared" si="2"/>
-        <v>4.8344927095041741E-2</v>
+        <f>SUM(V23:V24)/SUM($K23:$K24)</f>
+        <v>5.8402627587115299E-2</v>
       </c>
       <c r="W25" s="35">
-        <f t="shared" si="2"/>
-        <v>3.0638046502480861E-2</v>
+        <f>SUM(W23:W24)/SUM($K23:$K24)</f>
+        <v>1.5991724475720583E-2</v>
       </c>
       <c r="X25" s="35">
-        <f t="shared" si="2"/>
-        <v>1.8319151705719971E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="G26" t="s">
+        <f>SUM(X23:X24)/SUM($K23:$K24)</f>
+        <v>7.3306992053194506E-2</v>
+      </c>
+      <c r="Y25" s="35">
+        <f>SUM(Y23:Y24)/SUM($K23:$K24)</f>
+        <v>5.0833597608812293E-2</v>
+      </c>
+      <c r="Z25" s="35">
+        <f>SUM(Z23:Z24)/SUM($K23:$K24)</f>
+        <v>3.2215213074277702E-2</v>
+      </c>
+      <c r="AA25" s="35">
+        <f>SUM(AA23:AA24)/SUM($K23:$K24)</f>
+        <v>1.9262173764636067E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.25">
+      <c r="I26" s="39"/>
+      <c r="J26" t="s">
         <v>83</v>
-      </c>
-      <c r="H26" s="35">
-        <f>H24/SUM(H23:H24)</f>
-        <v>9.165808772791946E-2</v>
-      </c>
-      <c r="I26" s="35">
-        <f>I24/SUM(I23:I24)</f>
-        <v>1.6140143686645018E-2</v>
-      </c>
-      <c r="J26" s="35">
-        <f>J24/SUM(J23:J24)</f>
-        <v>8.7627365356623008E-2</v>
       </c>
       <c r="K26" s="35">
         <f>K24/SUM(K23:K24)</f>
+        <v>9.3981510630827186E-2</v>
+      </c>
+      <c r="L26" s="35">
+        <f>L24/SUM(L23:L24)</f>
+        <v>1.6140143686645018E-2</v>
+      </c>
+      <c r="M26" s="35">
+        <f>M24/SUM(M23:M24)</f>
+        <v>8.7627365356623008E-2</v>
+      </c>
+      <c r="N26" s="35">
+        <f>N24/SUM(N23:N24)</f>
         <v>2.1880917315379764E-2</v>
       </c>
-      <c r="L26" s="35">
-        <f t="shared" ref="L26:M26" si="3">L24/SUM(L23:L24)</f>
+      <c r="O26" s="35">
+        <f t="shared" ref="O26:P26" si="11">O24/SUM(O23:O24)</f>
         <v>0</v>
       </c>
-      <c r="M26" s="35">
-        <f t="shared" si="3"/>
+      <c r="P26" s="35">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="N26" s="35">
-        <f t="shared" ref="N26:X26" si="4">N24/SUM(N23:N24)</f>
+      <c r="Q26" s="35">
+        <f t="shared" ref="Q26:AA26" si="12">Q24/SUM(Q23:Q24)</f>
         <v>2.7097902097902096E-2</v>
       </c>
-      <c r="O26" s="35">
-        <f t="shared" si="4"/>
+      <c r="R26" s="35">
+        <f t="shared" si="12"/>
         <v>1.6097875080489378E-4</v>
       </c>
-      <c r="P26" s="35">
-        <f t="shared" si="4"/>
+      <c r="S26" s="35">
+        <f t="shared" si="12"/>
         <v>0.25079365079365079</v>
       </c>
-      <c r="Q26" s="35">
-        <f t="shared" si="4"/>
+      <c r="T26" s="35">
+        <f t="shared" si="12"/>
         <v>0.60900579580918413</v>
       </c>
-      <c r="R26" s="35">
-        <f t="shared" si="4"/>
+      <c r="U26" s="35">
+        <f t="shared" si="12"/>
         <v>3.5818005808325268E-2</v>
       </c>
-      <c r="S26" s="35">
-        <f t="shared" si="4"/>
+      <c r="V26" s="35">
+        <f t="shared" si="12"/>
         <v>0.31393233903237538</v>
       </c>
-      <c r="T26" s="35">
-        <f t="shared" si="4"/>
+      <c r="W26" s="35">
+        <f t="shared" si="12"/>
         <v>2.1739130434782608E-2</v>
       </c>
-      <c r="U26" s="35">
-        <f t="shared" si="4"/>
+      <c r="X26" s="35">
+        <f t="shared" si="12"/>
         <v>0.207714195384129</v>
       </c>
-      <c r="V26" s="35">
-        <f t="shared" si="4"/>
+      <c r="Y26" s="35">
+        <f t="shared" si="12"/>
         <v>0.18591691995947315</v>
       </c>
-      <c r="W26" s="35">
-        <f t="shared" si="4"/>
+      <c r="Z26" s="35">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="X26" s="35">
-        <f t="shared" si="4"/>
+      <c r="AA26" s="35">
+        <f t="shared" si="12"/>
         <v>0.12433155080213903</v>
       </c>
     </row>
-    <row r="46" spans="5:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="5:11" x14ac:dyDescent="0.25">
       <c r="F46" t="s">
         <v>80</v>
       </c>
@@ -4541,11 +9211,11 @@
       <c r="H46" t="s">
         <v>82</v>
       </c>
-      <c r="J46" t="s">
+      <c r="K46" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="47" spans="5:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E47" t="s">
         <v>64</v>
       </c>
@@ -4558,11 +9228,11 @@
       <c r="H47">
         <v>0.21650077997217101</v>
       </c>
-      <c r="J47">
+      <c r="K47">
         <v>1.6140143686645018E-2</v>
       </c>
     </row>
-    <row r="48" spans="5:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E48" t="s">
         <v>65</v>
       </c>
@@ -4575,11 +9245,11 @@
       <c r="H48">
         <v>1.5618056462907329E-2</v>
       </c>
-      <c r="J48">
+      <c r="K48">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="5:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E49" t="s">
         <v>66</v>
       </c>
@@ -4592,11 +9262,11 @@
       <c r="H49">
         <v>9.6094726668092836E-2</v>
       </c>
-      <c r="J49">
+      <c r="K49">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="5:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E50" t="s">
         <v>67</v>
       </c>
@@ -4609,11 +9279,11 @@
       <c r="H50">
         <v>7.3189664324811277E-2</v>
       </c>
-      <c r="J50">
+      <c r="K50">
         <v>8.7627365356623008E-2</v>
       </c>
     </row>
-    <row r="51" spans="5:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E51" t="s">
         <v>68</v>
       </c>
@@ -4626,11 +9296,11 @@
       <c r="H51">
         <v>0.10127233610941136</v>
       </c>
-      <c r="J51">
+      <c r="K51">
         <v>2.1880917315379764E-2</v>
       </c>
     </row>
-    <row r="52" spans="5:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E52" t="s">
         <v>69</v>
       </c>
@@ -4643,11 +9313,11 @@
       <c r="H52">
         <v>2.4375247740199158E-2</v>
       </c>
-      <c r="J52">
+      <c r="K52">
         <v>2.7097902097902096E-2</v>
       </c>
     </row>
-    <row r="53" spans="5:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E53" t="s">
         <v>70</v>
       </c>
@@ -4660,11 +9330,11 @@
       <c r="H53">
         <v>0.13235929979206046</v>
       </c>
-      <c r="J53">
+      <c r="K53">
         <v>1.6097875080489378E-4</v>
       </c>
     </row>
-    <row r="54" spans="5:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E54" t="s">
         <v>71</v>
       </c>
@@ -4677,11 +9347,11 @@
       <c r="H54">
         <v>1.5429232051609065E-2</v>
       </c>
-      <c r="J54">
+      <c r="K54">
         <v>0.25079365079365079</v>
       </c>
     </row>
-    <row r="55" spans="5:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E55" t="s">
         <v>72</v>
       </c>
@@ -4694,11 +9364,11 @@
       <c r="H55">
         <v>4.9439667845370197E-2</v>
       </c>
-      <c r="J55">
+      <c r="K55">
         <v>0.60900579580918413</v>
       </c>
     </row>
-    <row r="56" spans="5:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E56" t="s">
         <v>73</v>
       </c>
@@ -4711,11 +9381,11 @@
       <c r="H56">
         <v>3.7948563593600389E-2</v>
       </c>
-      <c r="J56">
+      <c r="K56">
         <v>3.5818005808325268E-2</v>
       </c>
     </row>
-    <row r="57" spans="5:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E57" t="s">
         <v>74</v>
       </c>
@@ -4728,11 +9398,11 @@
       <c r="H57">
         <v>5.5543398572453148E-2</v>
       </c>
-      <c r="J57">
+      <c r="K57">
         <v>0.31393233903237538</v>
       </c>
     </row>
-    <row r="58" spans="5:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E58" t="s">
         <v>75</v>
       </c>
@@ -4745,11 +9415,11 @@
       <c r="H58">
         <v>1.5208814450871792E-2</v>
       </c>
-      <c r="J58">
+      <c r="K58">
         <v>2.1739130434782608E-2</v>
       </c>
     </row>
-    <row r="59" spans="5:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E59" t="s">
         <v>76</v>
       </c>
@@ -4762,11 +9432,11 @@
       <c r="H59">
         <v>6.9718087113199254E-2</v>
       </c>
-      <c r="J59">
+      <c r="K59">
         <v>0.207714195384129</v>
       </c>
     </row>
-    <row r="60" spans="5:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E60" t="s">
         <v>77</v>
       </c>
@@ -4779,11 +9449,11 @@
       <c r="H60">
         <v>4.8344927095041734E-2</v>
       </c>
-      <c r="J60">
+      <c r="K60">
         <v>0.18591691995947315</v>
       </c>
     </row>
-    <row r="61" spans="5:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E61" t="s">
         <v>78</v>
       </c>
@@ -4796,11 +9466,11 @@
       <c r="H61">
         <v>3.0638046502480858E-2</v>
       </c>
-      <c r="J61">
+      <c r="K61">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="5:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E62" t="s">
         <v>79</v>
       </c>
@@ -4813,7 +9483,7 @@
       <c r="H62">
         <v>1.8319151705719967E-2</v>
       </c>
-      <c r="J62">
+      <c r="K62">
         <v>0.12433155080213903</v>
       </c>
     </row>
@@ -4829,25 +9499,25 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="3" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36"/>
-      <c r="L3" s="36"/>
-      <c r="M3" s="36"/>
-      <c r="N3" s="36"/>
-      <c r="O3" s="36"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="45"/>
+      <c r="O3" s="45"/>
     </row>
     <row r="4" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="42" t="s">
         <v>33</v>
       </c>
       <c r="C4" s="11"/>
@@ -4855,25 +9525,25 @@
         <v>34</v>
       </c>
       <c r="E4" s="11"/>
-      <c r="F4" s="39" t="s">
+      <c r="F4" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="39"/>
+      <c r="G4" s="44"/>
       <c r="H4" s="11"/>
-      <c r="I4" s="39" t="s">
+      <c r="I4" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="J4" s="39"/>
-      <c r="K4" s="39"/>
-      <c r="L4" s="39" t="s">
+      <c r="J4" s="44"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="M4" s="39"/>
-      <c r="N4" s="39"/>
+      <c r="M4" s="44"/>
+      <c r="N4" s="44"/>
       <c r="O4" s="13"/>
     </row>
     <row r="5" spans="2:21" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B5" s="38"/>
+      <c r="B5" s="43"/>
       <c r="C5" s="14" t="s">
         <v>38</v>
       </c>
@@ -5521,41 +10191,41 @@
       </c>
     </row>
     <row r="17" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B17" s="40" t="s">
+      <c r="B17" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="40"/>
-      <c r="D17" s="40"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="40"/>
-      <c r="G17" s="40"/>
-      <c r="H17" s="40"/>
-      <c r="I17" s="40"/>
-      <c r="J17" s="40"/>
-      <c r="K17" s="40"/>
-      <c r="L17" s="40"/>
-      <c r="M17" s="40"/>
-      <c r="N17" s="40"/>
-      <c r="O17" s="40"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="41"/>
+      <c r="K17" s="41"/>
+      <c r="L17" s="41"/>
+      <c r="M17" s="41"/>
+      <c r="N17" s="41"/>
+      <c r="O17" s="41"/>
     </row>
     <row r="18" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B18" s="40"/>
-      <c r="C18" s="40"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="40"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="40"/>
-      <c r="I18" s="40"/>
-      <c r="J18" s="40"/>
-      <c r="K18" s="40"/>
-      <c r="L18" s="40"/>
-      <c r="M18" s="40"/>
-      <c r="N18" s="40"/>
-      <c r="O18" s="40"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="41"/>
+      <c r="K18" s="41"/>
+      <c r="L18" s="41"/>
+      <c r="M18" s="41"/>
+      <c r="N18" s="41"/>
+      <c r="O18" s="41"/>
     </row>
     <row r="19" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B19" s="37" t="s">
+      <c r="B19" s="42" t="s">
         <v>33</v>
       </c>
       <c r="C19" s="11"/>
@@ -5563,25 +10233,25 @@
         <v>34</v>
       </c>
       <c r="E19" s="11"/>
-      <c r="F19" s="39" t="s">
+      <c r="F19" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="G19" s="39"/>
+      <c r="G19" s="44"/>
       <c r="H19" s="11"/>
-      <c r="I19" s="39" t="s">
+      <c r="I19" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="J19" s="39"/>
-      <c r="K19" s="39"/>
-      <c r="L19" s="39" t="s">
+      <c r="J19" s="44"/>
+      <c r="K19" s="44"/>
+      <c r="L19" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="M19" s="39"/>
-      <c r="N19" s="39"/>
+      <c r="M19" s="44"/>
+      <c r="N19" s="44"/>
       <c r="O19" s="13"/>
     </row>
     <row r="20" spans="2:21" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B20" s="38"/>
+      <c r="B20" s="43"/>
       <c r="C20" s="14" t="s">
         <v>38</v>
       </c>
@@ -6230,16 +10900,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B3:O3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="L4:N4"/>
     <mergeCell ref="B17:O18"/>
     <mergeCell ref="B19:B20"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="I19:K19"/>
     <mergeCell ref="L19:N19"/>
-    <mergeCell ref="B3:O3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="L4:N4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data/prod_parameters/HorseHerd.xlsx
+++ b/data/prod_parameters/HorseHerd.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="11400"/>
   </bookViews>
   <sheets>
     <sheet name="default" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="101">
   <si>
     <t>f_breed</t>
   </si>
@@ -212,9 +212,6 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>From feed industry statistics (2011)</t>
-  </si>
-  <si>
     <t>Havre</t>
   </si>
   <si>
@@ -230,24 +227,15 @@
     <t>Vete</t>
   </si>
   <si>
-    <t>Vetefodermjöl</t>
-  </si>
-  <si>
     <t>Vetekli</t>
   </si>
   <si>
     <t>Vegetabilisk olja</t>
   </si>
   <si>
-    <t>(socker)betmassa</t>
-  </si>
-  <si>
     <t>(socker)betmelass</t>
   </si>
   <si>
-    <t>Melasserad pressmassa</t>
-  </si>
-  <si>
     <t>Potatisprotein</t>
   </si>
   <si>
@@ -269,9 +257,6 @@
     <t>INF</t>
   </si>
   <si>
-    <t>% av totalen</t>
-  </si>
-  <si>
     <t>% imported</t>
   </si>
   <si>
@@ -315,6 +300,30 @@
   </si>
   <si>
     <t>luzern meal</t>
+  </si>
+  <si>
+    <t>Vetefodermjöl (plus fodervete 2022)</t>
+  </si>
+  <si>
+    <t>(socker)betmassa (torkad betmassa</t>
+  </si>
+  <si>
+    <t>Melasserad pressmassa (melasseard torkad betma.. 2022)</t>
+  </si>
+  <si>
+    <t>From feed industry statistics (2022)</t>
+  </si>
+  <si>
+    <t>oat bran</t>
+  </si>
+  <si>
+    <t>oat hulls</t>
+  </si>
+  <si>
+    <t>minerals</t>
+  </si>
+  <si>
+    <t>HorseHerd-feed_rations.csv</t>
   </si>
 </sst>
 </file>
@@ -457,7 +466,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -540,7 +549,7 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
@@ -552,8 +561,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3280,7 +3290,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I227"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.85546875" bestFit="1" customWidth="1"/>
@@ -3749,3844 +3759,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C33" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="E33" s="37" t="s">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E32" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="F33" s="9">
-        <f t="array" ref="F33">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A33='Feed rations'!$C$4:$C$19)*(C33='Feed rations'!$D$4:$D$19),0),
-MATCH(D33, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>66</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C34" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="37" t="s">
-        <v>50</v>
-      </c>
-      <c r="E34" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F34" s="9">
-        <f t="array" ref="F34">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A34='Feed rations'!$C$4:$C$19)*(C34='Feed rations'!$D$4:$D$19),0),
-MATCH(D34, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>32.999999999999993</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C35" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="E35" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F35" s="9">
-        <f t="array" ref="F35">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A35='Feed rations'!$C$4:$C$19)*(C35='Feed rations'!$D$4:$D$19),0),
-MATCH(D35, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.22764567437372507</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C36" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="E36" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F36" s="9">
-        <f t="array" ref="F36">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A36='Feed rations'!$C$4:$C$19)*(C36='Feed rations'!$D$4:$D$19),0),
-MATCH(D36, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>7.6957276987869846E-2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C37" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="37" t="s">
-        <v>90</v>
-      </c>
-      <c r="E37" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F37" s="9">
-        <f t="array" ref="F37">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A37='Feed rations'!$C$4:$C$19)*(C37='Feed rations'!$D$4:$D$19),0),
-MATCH(D37, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.10648557133139604</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C38" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="E38" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F38" s="9">
-        <f t="array" ref="F38">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A38='Feed rations'!$C$4:$C$19)*(C38='Feed rations'!$D$4:$D$19),0),
-MATCH(D38, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>2.5630021797415754E-2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C39" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="E39" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F39" s="9">
-        <f t="array" ref="F39">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A39='Feed rations'!$C$4:$C$19)*(C39='Feed rations'!$D$4:$D$19),0),
-MATCH(D39, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.25663627595227045</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C40" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="37" t="s">
-        <v>92</v>
-      </c>
-      <c r="E40" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F40" s="9">
-        <f t="array" ref="F40">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A40='Feed rations'!$C$4:$C$19)*(C40='Feed rations'!$D$4:$D$19),0),
-MATCH(D40, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>1.6223488598557115E-2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C41" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="E41" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F41" s="9">
-        <f t="array" ref="F41">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A41='Feed rations'!$C$4:$C$19)*(C41='Feed rations'!$D$4:$D$19),0),
-MATCH(D41, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>8.1186006545791389E-2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C42" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="E42" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F42" s="9">
-        <f t="array" ref="F42">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A42='Feed rations'!$C$4:$C$19)*(C42='Feed rations'!$D$4:$D$19),0),
-MATCH(D42, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>6.9103370275246934E-2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C43" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="E43" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F43" s="9">
-        <f t="array" ref="F43">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A43='Feed rations'!$C$4:$C$19)*(C43='Feed rations'!$D$4:$D$19),0),
-MATCH(D43, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>1.5991724475720583E-2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C44" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="E44" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F44" s="9">
-        <f t="array" ref="F44">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A44='Feed rations'!$C$4:$C$19)*(C44='Feed rations'!$D$4:$D$19),0),
-MATCH(D44, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.12414058966200681</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C45" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D45" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="E45" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F45" s="9">
-        <f t="array" ref="F45">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A45='Feed rations'!$C$4:$C$19)*(C45='Feed rations'!$D$4:$D$19),0),
-MATCH(D45, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>81.666666666666671</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C46" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D46" s="37" t="s">
-        <v>50</v>
-      </c>
-      <c r="E46" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F46" s="9">
-        <f t="array" ref="F46">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A46='Feed rations'!$C$4:$C$19)*(C46='Feed rations'!$D$4:$D$19),0),
-MATCH(D46, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>16.333333333333332</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C47" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D47" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="E47" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F47" s="9">
-        <f t="array" ref="F47">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A47='Feed rations'!$C$4:$C$19)*(C47='Feed rations'!$D$4:$D$19),0),
-MATCH(D47, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.45529134874745014</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C48" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D48" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="E48" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F48" s="9">
-        <f t="array" ref="F48">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A48='Feed rations'!$C$4:$C$19)*(C48='Feed rations'!$D$4:$D$19),0),
-MATCH(D48, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.15391455397573969</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C49" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D49" s="37" t="s">
-        <v>90</v>
-      </c>
-      <c r="E49" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F49" s="9">
-        <f t="array" ref="F49">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A49='Feed rations'!$C$4:$C$19)*(C49='Feed rations'!$D$4:$D$19),0),
-MATCH(D49, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.21297114266279207</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C50" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D50" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="E50" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F50" s="9">
-        <f t="array" ref="F50">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A50='Feed rations'!$C$4:$C$19)*(C50='Feed rations'!$D$4:$D$19),0),
-MATCH(D50, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>5.1260043594831509E-2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C51" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D51" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="E51" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F51" s="9">
-        <f t="array" ref="F51">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A51='Feed rations'!$C$4:$C$19)*(C51='Feed rations'!$D$4:$D$19),0),
-MATCH(D51, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.51327255190454091</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C52" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D52" s="37" t="s">
-        <v>92</v>
-      </c>
-      <c r="E52" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F52" s="9">
-        <f t="array" ref="F52">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A52='Feed rations'!$C$4:$C$19)*(C52='Feed rations'!$D$4:$D$19),0),
-MATCH(D52, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>3.244697719711423E-2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C53" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D53" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="E53" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F53" s="9">
-        <f t="array" ref="F53">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A53='Feed rations'!$C$4:$C$19)*(C53='Feed rations'!$D$4:$D$19),0),
-MATCH(D53, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.16237201309158278</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C54" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D54" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="E54" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F54" s="9">
-        <f t="array" ref="F54">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A54='Feed rations'!$C$4:$C$19)*(C54='Feed rations'!$D$4:$D$19),0),
-MATCH(D54, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.13820674055049387</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C55" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D55" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="E55" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F55" s="9">
-        <f t="array" ref="F55">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A55='Feed rations'!$C$4:$C$19)*(C55='Feed rations'!$D$4:$D$19),0),
-MATCH(D55, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>3.1983448951441167E-2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C56" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D56" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="E56" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F56" s="9">
-        <f t="array" ref="F56">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A56='Feed rations'!$C$4:$C$19)*(C56='Feed rations'!$D$4:$D$19),0),
-MATCH(D56, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.24828117932401361</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C57" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D57" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="E57" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F57" s="9">
-        <f t="array" ref="F57">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A57='Feed rations'!$C$4:$C$19)*(C57='Feed rations'!$D$4:$D$19),0),
-MATCH(D57, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C58" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D58" s="37" t="s">
-        <v>50</v>
-      </c>
-      <c r="E58" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F58" s="9">
-        <f t="array" ref="F58">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A58='Feed rations'!$C$4:$C$19)*(C58='Feed rations'!$D$4:$D$19),0),
-MATCH(D58, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>30.999999999999993</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C59" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D59" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="E59" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F59" s="9">
-        <f t="array" ref="F59">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A59='Feed rations'!$C$4:$C$19)*(C59='Feed rations'!$D$4:$D$19),0),
-MATCH(D59, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>1.5935197206160754</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C60" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D60" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="E60" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F60" s="9">
-        <f t="array" ref="F60">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A60='Feed rations'!$C$4:$C$19)*(C60='Feed rations'!$D$4:$D$19),0),
-MATCH(D60, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.53870093891508897</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C61" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D61" s="37" t="s">
-        <v>90</v>
-      </c>
-      <c r="E61" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F61" s="9">
-        <f t="array" ref="F61">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A61='Feed rations'!$C$4:$C$19)*(C61='Feed rations'!$D$4:$D$19),0),
-MATCH(D61, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.74539899931977227</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C62" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D62" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="E62" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F62" s="9">
-        <f t="array" ref="F62">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A62='Feed rations'!$C$4:$C$19)*(C62='Feed rations'!$D$4:$D$19),0),
-MATCH(D62, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.17941015258191029</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C63" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D63" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="E63" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F63" s="9">
-        <f t="array" ref="F63">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A63='Feed rations'!$C$4:$C$19)*(C63='Feed rations'!$D$4:$D$19),0),
-MATCH(D63, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>1.7964539316658934</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C64" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D64" s="37" t="s">
-        <v>92</v>
-      </c>
-      <c r="E64" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F64" s="9">
-        <f t="array" ref="F64">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A64='Feed rations'!$C$4:$C$19)*(C64='Feed rations'!$D$4:$D$19),0),
-MATCH(D64, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.1135644201898998</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C65" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D65" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="E65" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F65" s="9">
-        <f t="array" ref="F65">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A65='Feed rations'!$C$4:$C$19)*(C65='Feed rations'!$D$4:$D$19),0),
-MATCH(D65, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.56830204582053978</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C66" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D66" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="E66" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F66" s="9">
-        <f t="array" ref="F66">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A66='Feed rations'!$C$4:$C$19)*(C66='Feed rations'!$D$4:$D$19),0),
-MATCH(D66, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.48372359192672859</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C67" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D67" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="E67" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F67" s="9">
-        <f t="array" ref="F67">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A67='Feed rations'!$C$4:$C$19)*(C67='Feed rations'!$D$4:$D$19),0),
-MATCH(D67, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.11194207133004409</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C68" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D68" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="E68" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F68" s="9">
-        <f t="array" ref="F68">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A68='Feed rations'!$C$4:$C$19)*(C68='Feed rations'!$D$4:$D$19),0),
-MATCH(D68, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.86898412763404764</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C69" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D69" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="E69" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F69" s="9">
-        <f t="array" ref="F69">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A69='Feed rations'!$C$4:$C$19)*(C69='Feed rations'!$D$4:$D$19),0),
-MATCH(D69, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>61.333333333333343</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C70" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D70" s="37" t="s">
-        <v>50</v>
-      </c>
-      <c r="E70" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F70" s="9">
-        <f t="array" ref="F70">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A70='Feed rations'!$C$4:$C$19)*(C70='Feed rations'!$D$4:$D$19),0),
-MATCH(D70, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>30.666666666666664</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C71" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D71" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="E71" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F71" s="9">
-        <f t="array" ref="F71">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A71='Feed rations'!$C$4:$C$19)*(C71='Feed rations'!$D$4:$D$19),0),
-MATCH(D71, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>1.8211653949898006</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C72" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D72" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="E72" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F72" s="9">
-        <f t="array" ref="F72">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A72='Feed rations'!$C$4:$C$19)*(C72='Feed rations'!$D$4:$D$19),0),
-MATCH(D72, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.61565821590295877</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C73" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D73" s="37" t="s">
-        <v>90</v>
-      </c>
-      <c r="E73" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F73" s="9">
-        <f t="array" ref="F73">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A73='Feed rations'!$C$4:$C$19)*(C73='Feed rations'!$D$4:$D$19),0),
-MATCH(D73, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.85188457065116829</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C74" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D74" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="E74" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F74" s="9">
-        <f t="array" ref="F74">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A74='Feed rations'!$C$4:$C$19)*(C74='Feed rations'!$D$4:$D$19),0),
-MATCH(D74, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.20504017437932603</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C75" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D75" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="E75" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F75" s="9">
-        <f t="array" ref="F75">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A75='Feed rations'!$C$4:$C$19)*(C75='Feed rations'!$D$4:$D$19),0),
-MATCH(D75, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>2.0530902076181636</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C76" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D76" s="37" t="s">
-        <v>92</v>
-      </c>
-      <c r="E76" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F76" s="9">
-        <f t="array" ref="F76">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A76='Feed rations'!$C$4:$C$19)*(C76='Feed rations'!$D$4:$D$19),0),
-MATCH(D76, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.12978790878845692</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C77" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D77" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="E77" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F77" s="9">
-        <f t="array" ref="F77">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A77='Feed rations'!$C$4:$C$19)*(C77='Feed rations'!$D$4:$D$19),0),
-MATCH(D77, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.64948805236633111</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C78" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D78" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="E78" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F78" s="9">
-        <f t="array" ref="F78">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A78='Feed rations'!$C$4:$C$19)*(C78='Feed rations'!$D$4:$D$19),0),
-MATCH(D78, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.55282696220197547</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C79" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D79" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="E79" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F79" s="9">
-        <f t="array" ref="F79">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A79='Feed rations'!$C$4:$C$19)*(C79='Feed rations'!$D$4:$D$19),0),
-MATCH(D79, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.12793379580576467</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C80" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D80" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="E80" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F80" s="9">
-        <f t="array" ref="F80">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A80='Feed rations'!$C$4:$C$19)*(C80='Feed rations'!$D$4:$D$19),0),
-MATCH(D80, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.99312471729605445</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C82" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D82" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="E82" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F82" s="9">
-        <f t="array" ref="F82">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A82='Feed rations'!$C$4:$C$19)*(C82='Feed rations'!$D$4:$D$19),0),
-MATCH(D82, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>66</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C83" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D83" s="37" t="s">
-        <v>50</v>
-      </c>
-      <c r="E83" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F83" s="9">
-        <f t="array" ref="F83">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A83='Feed rations'!$C$4:$C$19)*(C83='Feed rations'!$D$4:$D$19),0),
-MATCH(D83, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>32.999999999999993</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C84" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D84" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="E84" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F84" s="9">
-        <f t="array" ref="F84">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A84='Feed rations'!$C$4:$C$19)*(C84='Feed rations'!$D$4:$D$19),0),
-MATCH(D84, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.22764567437372507</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C85" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D85" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="E85" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F85" s="9">
-        <f t="array" ref="F85">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A85='Feed rations'!$C$4:$C$19)*(C85='Feed rations'!$D$4:$D$19),0),
-MATCH(D85, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>7.6957276987869846E-2</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C86" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D86" s="37" t="s">
-        <v>90</v>
-      </c>
-      <c r="E86" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F86" s="9">
-        <f t="array" ref="F86">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A86='Feed rations'!$C$4:$C$19)*(C86='Feed rations'!$D$4:$D$19),0),
-MATCH(D86, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.10648557133139604</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C87" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D87" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="E87" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F87" s="9">
-        <f t="array" ref="F87">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A87='Feed rations'!$C$4:$C$19)*(C87='Feed rations'!$D$4:$D$19),0),
-MATCH(D87, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>2.5630021797415754E-2</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C88" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D88" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="E88" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F88" s="9">
-        <f t="array" ref="F88">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A88='Feed rations'!$C$4:$C$19)*(C88='Feed rations'!$D$4:$D$19),0),
-MATCH(D88, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.25663627595227045</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C89" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D89" s="37" t="s">
-        <v>92</v>
-      </c>
-      <c r="E89" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F89" s="9">
-        <f t="array" ref="F89">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A89='Feed rations'!$C$4:$C$19)*(C89='Feed rations'!$D$4:$D$19),0),
-MATCH(D89, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>1.6223488598557115E-2</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C90" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D90" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="E90" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F90" s="9">
-        <f t="array" ref="F90">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A90='Feed rations'!$C$4:$C$19)*(C90='Feed rations'!$D$4:$D$19),0),
-MATCH(D90, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>8.1186006545791389E-2</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C91" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D91" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="E91" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F91" s="9">
-        <f t="array" ref="F91">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A91='Feed rations'!$C$4:$C$19)*(C91='Feed rations'!$D$4:$D$19),0),
-MATCH(D91, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>6.9103370275246934E-2</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C92" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D92" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="E92" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F92" s="9">
-        <f t="array" ref="F92">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A92='Feed rations'!$C$4:$C$19)*(C92='Feed rations'!$D$4:$D$19),0),
-MATCH(D92, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>1.5991724475720583E-2</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C93" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D93" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="E93" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F93" s="9">
-        <f t="array" ref="F93">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A93='Feed rations'!$C$4:$C$19)*(C93='Feed rations'!$D$4:$D$19),0),
-MATCH(D93, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.12414058966200681</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C94" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D94" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="E94" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F94" s="9">
-        <f t="array" ref="F94">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A94='Feed rations'!$C$4:$C$19)*(C94='Feed rations'!$D$4:$D$19),0),
-MATCH(D94, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>81.666666666666671</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C95" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D95" s="37" t="s">
-        <v>50</v>
-      </c>
-      <c r="E95" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F95" s="9">
-        <f t="array" ref="F95">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A95='Feed rations'!$C$4:$C$19)*(C95='Feed rations'!$D$4:$D$19),0),
-MATCH(D95, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>16.333333333333332</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C96" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D96" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="E96" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F96" s="9">
-        <f t="array" ref="F96">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A96='Feed rations'!$C$4:$C$19)*(C96='Feed rations'!$D$4:$D$19),0),
-MATCH(D96, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.45529134874745014</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A97" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C97" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D97" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="E97" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F97" s="9">
-        <f t="array" ref="F97">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A97='Feed rations'!$C$4:$C$19)*(C97='Feed rations'!$D$4:$D$19),0),
-MATCH(D97, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.15391455397573969</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A98" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C98" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D98" s="37" t="s">
-        <v>90</v>
-      </c>
-      <c r="E98" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F98" s="9">
-        <f t="array" ref="F98">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A98='Feed rations'!$C$4:$C$19)*(C98='Feed rations'!$D$4:$D$19),0),
-MATCH(D98, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.21297114266279207</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A99" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C99" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D99" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="E99" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F99" s="9">
-        <f t="array" ref="F99">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A99='Feed rations'!$C$4:$C$19)*(C99='Feed rations'!$D$4:$D$19),0),
-MATCH(D99, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>5.1260043594831509E-2</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A100" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C100" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D100" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="E100" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F100" s="9">
-        <f t="array" ref="F100">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A100='Feed rations'!$C$4:$C$19)*(C100='Feed rations'!$D$4:$D$19),0),
-MATCH(D100, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.51327255190454091</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A101" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C101" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D101" s="37" t="s">
-        <v>92</v>
-      </c>
-      <c r="E101" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F101" s="9">
-        <f t="array" ref="F101">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A101='Feed rations'!$C$4:$C$19)*(C101='Feed rations'!$D$4:$D$19),0),
-MATCH(D101, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>3.244697719711423E-2</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A102" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C102" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D102" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="E102" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F102" s="9">
-        <f t="array" ref="F102">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A102='Feed rations'!$C$4:$C$19)*(C102='Feed rations'!$D$4:$D$19),0),
-MATCH(D102, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.16237201309158278</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A103" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C103" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D103" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="E103" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F103" s="9">
-        <f t="array" ref="F103">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A103='Feed rations'!$C$4:$C$19)*(C103='Feed rations'!$D$4:$D$19),0),
-MATCH(D103, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.13820674055049387</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C104" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D104" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="E104" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F104" s="9">
-        <f t="array" ref="F104">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A104='Feed rations'!$C$4:$C$19)*(C104='Feed rations'!$D$4:$D$19),0),
-MATCH(D104, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>3.1983448951441167E-2</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C105" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D105" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="E105" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F105" s="9">
-        <f t="array" ref="F105">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A105='Feed rations'!$C$4:$C$19)*(C105='Feed rations'!$D$4:$D$19),0),
-MATCH(D105, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.24828117932401361</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C106" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D106" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="E106" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F106" s="9">
-        <f t="array" ref="F106">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A106='Feed rations'!$C$4:$C$19)*(C106='Feed rations'!$D$4:$D$19),0),
-MATCH(D106, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A107" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C107" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D107" s="37" t="s">
-        <v>50</v>
-      </c>
-      <c r="E107" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F107" s="9">
-        <f t="array" ref="F107">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A107='Feed rations'!$C$4:$C$19)*(C107='Feed rations'!$D$4:$D$19),0),
-MATCH(D107, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>30.999999999999993</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A108" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C108" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D108" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="E108" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F108" s="9">
-        <f t="array" ref="F108">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A108='Feed rations'!$C$4:$C$19)*(C108='Feed rations'!$D$4:$D$19),0),
-MATCH(D108, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>1.5935197206160754</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A109" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C109" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D109" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="E109" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F109" s="9">
-        <f t="array" ref="F109">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A109='Feed rations'!$C$4:$C$19)*(C109='Feed rations'!$D$4:$D$19),0),
-MATCH(D109, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.53870093891508897</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A110" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C110" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D110" s="37" t="s">
-        <v>90</v>
-      </c>
-      <c r="E110" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F110" s="9">
-        <f t="array" ref="F110">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A110='Feed rations'!$C$4:$C$19)*(C110='Feed rations'!$D$4:$D$19),0),
-MATCH(D110, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.74539899931977227</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A111" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C111" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D111" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="E111" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F111" s="9">
-        <f t="array" ref="F111">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A111='Feed rations'!$C$4:$C$19)*(C111='Feed rations'!$D$4:$D$19),0),
-MATCH(D111, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.17941015258191029</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A112" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C112" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D112" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="E112" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F112" s="9">
-        <f t="array" ref="F112">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A112='Feed rations'!$C$4:$C$19)*(C112='Feed rations'!$D$4:$D$19),0),
-MATCH(D112, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>1.7964539316658934</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C113" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D113" s="37" t="s">
-        <v>92</v>
-      </c>
-      <c r="E113" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F113" s="9">
-        <f t="array" ref="F113">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A113='Feed rations'!$C$4:$C$19)*(C113='Feed rations'!$D$4:$D$19),0),
-MATCH(D113, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.1135644201898998</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A114" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C114" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D114" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="E114" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F114" s="9">
-        <f t="array" ref="F114">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A114='Feed rations'!$C$4:$C$19)*(C114='Feed rations'!$D$4:$D$19),0),
-MATCH(D114, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.56830204582053978</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A115" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C115" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D115" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="E115" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F115" s="9">
-        <f t="array" ref="F115">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A115='Feed rations'!$C$4:$C$19)*(C115='Feed rations'!$D$4:$D$19),0),
-MATCH(D115, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.48372359192672859</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A116" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C116" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D116" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="E116" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F116" s="9">
-        <f t="array" ref="F116">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A116='Feed rations'!$C$4:$C$19)*(C116='Feed rations'!$D$4:$D$19),0),
-MATCH(D116, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.11194207133004409</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A117" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C117" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D117" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="E117" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F117" s="9">
-        <f t="array" ref="F117">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A117='Feed rations'!$C$4:$C$19)*(C117='Feed rations'!$D$4:$D$19),0),
-MATCH(D117, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.86898412763404764</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A118" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C118" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D118" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="E118" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F118" s="9">
-        <f t="array" ref="F118">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A118='Feed rations'!$C$4:$C$19)*(C118='Feed rations'!$D$4:$D$19),0),
-MATCH(D118, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>64.666666666666671</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A119" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C119" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D119" s="37" t="s">
-        <v>50</v>
-      </c>
-      <c r="E119" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F119" s="9">
-        <f t="array" ref="F119">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A119='Feed rations'!$C$4:$C$19)*(C119='Feed rations'!$D$4:$D$19),0),
-MATCH(D119, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>32.333333333333329</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A120" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C120" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D120" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="E120" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F120" s="9">
-        <f t="array" ref="F120">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A120='Feed rations'!$C$4:$C$19)*(C120='Feed rations'!$D$4:$D$19),0),
-MATCH(D120, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.6829370231211751</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A121" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C121" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D121" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="E121" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F121" s="9">
-        <f t="array" ref="F121">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A121='Feed rations'!$C$4:$C$19)*(C121='Feed rations'!$D$4:$D$19),0),
-MATCH(D121, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.23087183096360953</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A122" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C122" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D122" s="37" t="s">
-        <v>90</v>
-      </c>
-      <c r="E122" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F122" s="9">
-        <f t="array" ref="F122">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A122='Feed rations'!$C$4:$C$19)*(C122='Feed rations'!$D$4:$D$19),0),
-MATCH(D122, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.31945671399418812</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A123" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C123" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D123" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="E123" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F123" s="9">
-        <f t="array" ref="F123">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A123='Feed rations'!$C$4:$C$19)*(C123='Feed rations'!$D$4:$D$19),0),
-MATCH(D123, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>7.6890065392247256E-2</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A124" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C124" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D124" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="E124" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F124" s="9">
-        <f t="array" ref="F124">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A124='Feed rations'!$C$4:$C$19)*(C124='Feed rations'!$D$4:$D$19),0),
-MATCH(D124, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.76990882785681136</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A125" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C125" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D125" s="37" t="s">
-        <v>92</v>
-      </c>
-      <c r="E125" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F125" s="9">
-        <f t="array" ref="F125">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A125='Feed rations'!$C$4:$C$19)*(C125='Feed rations'!$D$4:$D$19),0),
-MATCH(D125, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>4.8670465795671344E-2</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A126" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C126" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D126" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="E126" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F126" s="9">
-        <f t="array" ref="F126">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A126='Feed rations'!$C$4:$C$19)*(C126='Feed rations'!$D$4:$D$19),0),
-MATCH(D126, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.24355801963737417</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A127" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C127" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D127" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="E127" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F127" s="9">
-        <f t="array" ref="F127">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A127='Feed rations'!$C$4:$C$19)*(C127='Feed rations'!$D$4:$D$19),0),
-MATCH(D127, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.20731011082574077</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A128" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C128" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D128" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="E128" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F128" s="9">
-        <f t="array" ref="F128">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A128='Feed rations'!$C$4:$C$19)*(C128='Feed rations'!$D$4:$D$19),0),
-MATCH(D128, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>4.7975173427161746E-2</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A129" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C129" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D129" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="E129" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F129" s="9">
-        <f t="array" ref="F129">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A129='Feed rations'!$C$4:$C$19)*(C129='Feed rations'!$D$4:$D$19),0),
-MATCH(D129, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.37242176898602036</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A131" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C131" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D131" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="E131" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F131" s="9">
-        <f t="array" ref="F131">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A131='Feed rations'!$C$4:$C$19)*(C131='Feed rations'!$D$4:$D$19),0),
-MATCH(D131, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>66</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A132" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C132" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D132" s="37" t="s">
-        <v>50</v>
-      </c>
-      <c r="E132" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F132" s="9">
-        <f t="array" ref="F132">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A132='Feed rations'!$C$4:$C$19)*(C132='Feed rations'!$D$4:$D$19),0),
-MATCH(D132, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>32.999999999999993</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A133" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C133" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D133" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="E133" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F133" s="9">
-        <f t="array" ref="F133">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A133='Feed rations'!$C$4:$C$19)*(C133='Feed rations'!$D$4:$D$19),0),
-MATCH(D133, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.22764567437372507</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A134" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C134" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D134" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="E134" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F134" s="9">
-        <f t="array" ref="F134">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A134='Feed rations'!$C$4:$C$19)*(C134='Feed rations'!$D$4:$D$19),0),
-MATCH(D134, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>7.6957276987869846E-2</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A135" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C135" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D135" s="37" t="s">
-        <v>90</v>
-      </c>
-      <c r="E135" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F135" s="9">
-        <f t="array" ref="F135">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A135='Feed rations'!$C$4:$C$19)*(C135='Feed rations'!$D$4:$D$19),0),
-MATCH(D135, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.10648557133139604</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A136" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C136" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D136" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="E136" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F136" s="9">
-        <f t="array" ref="F136">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A136='Feed rations'!$C$4:$C$19)*(C136='Feed rations'!$D$4:$D$19),0),
-MATCH(D136, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>2.5630021797415754E-2</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A137" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C137" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D137" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="E137" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F137" s="9">
-        <f t="array" ref="F137">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A137='Feed rations'!$C$4:$C$19)*(C137='Feed rations'!$D$4:$D$19),0),
-MATCH(D137, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.25663627595227045</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A138" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C138" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D138" s="37" t="s">
-        <v>92</v>
-      </c>
-      <c r="E138" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F138" s="9">
-        <f t="array" ref="F138">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A138='Feed rations'!$C$4:$C$19)*(C138='Feed rations'!$D$4:$D$19),0),
-MATCH(D138, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>1.6223488598557115E-2</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A139" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C139" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D139" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="E139" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F139" s="9">
-        <f t="array" ref="F139">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A139='Feed rations'!$C$4:$C$19)*(C139='Feed rations'!$D$4:$D$19),0),
-MATCH(D139, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>8.1186006545791389E-2</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A140" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C140" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D140" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="E140" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F140" s="9">
-        <f t="array" ref="F140">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A140='Feed rations'!$C$4:$C$19)*(C140='Feed rations'!$D$4:$D$19),0),
-MATCH(D140, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>6.9103370275246934E-2</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A141" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C141" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D141" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="E141" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F141" s="9">
-        <f t="array" ref="F141">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A141='Feed rations'!$C$4:$C$19)*(C141='Feed rations'!$D$4:$D$19),0),
-MATCH(D141, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>1.5991724475720583E-2</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A142" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C142" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D142" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="E142" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F142" s="9">
-        <f t="array" ref="F142">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A142='Feed rations'!$C$4:$C$19)*(C142='Feed rations'!$D$4:$D$19),0),
-MATCH(D142, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.12414058966200681</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A143" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C143" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D143" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="E143" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F143" s="9">
-        <f t="array" ref="F143">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A143='Feed rations'!$C$4:$C$19)*(C143='Feed rations'!$D$4:$D$19),0),
-MATCH(D143, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A144" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C144" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D144" s="37" t="s">
-        <v>50</v>
-      </c>
-      <c r="E144" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F144" s="9">
-        <f t="array" ref="F144">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A144='Feed rations'!$C$4:$C$19)*(C144='Feed rations'!$D$4:$D$19),0),
-MATCH(D144, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>15.999999999999998</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A145" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C145" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D145" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="E145" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F145" s="9">
-        <f t="array" ref="F145">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A145='Feed rations'!$C$4:$C$19)*(C145='Feed rations'!$D$4:$D$19),0),
-MATCH(D145, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.91058269749490028</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A146" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C146" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D146" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="E146" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F146" s="9">
-        <f t="array" ref="F146">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A146='Feed rations'!$C$4:$C$19)*(C146='Feed rations'!$D$4:$D$19),0),
-MATCH(D146, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.30782910795147939</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A147" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C147" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D147" s="37" t="s">
-        <v>90</v>
-      </c>
-      <c r="E147" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F147" s="9">
-        <f t="array" ref="F147">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A147='Feed rations'!$C$4:$C$19)*(C147='Feed rations'!$D$4:$D$19),0),
-MATCH(D147, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.42594228532558415</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A148" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C148" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D148" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="E148" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F148" s="9">
-        <f t="array" ref="F148">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A148='Feed rations'!$C$4:$C$19)*(C148='Feed rations'!$D$4:$D$19),0),
-MATCH(D148, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.10252008718966302</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A149" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C149" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D149" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="E149" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F149" s="9">
-        <f t="array" ref="F149">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A149='Feed rations'!$C$4:$C$19)*(C149='Feed rations'!$D$4:$D$19),0),
-MATCH(D149, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>1.0265451038090818</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A150" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C150" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D150" s="37" t="s">
-        <v>92</v>
-      </c>
-      <c r="E150" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F150" s="9">
-        <f t="array" ref="F150">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A150='Feed rations'!$C$4:$C$19)*(C150='Feed rations'!$D$4:$D$19),0),
-MATCH(D150, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>6.4893954394228459E-2</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A151" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C151" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D151" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="E151" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F151" s="9">
-        <f t="array" ref="F151">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A151='Feed rations'!$C$4:$C$19)*(C151='Feed rations'!$D$4:$D$19),0),
-MATCH(D151, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.32474402618316556</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A152" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C152" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D152" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="E152" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F152" s="9">
-        <f t="array" ref="F152">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A152='Feed rations'!$C$4:$C$19)*(C152='Feed rations'!$D$4:$D$19),0),
-MATCH(D152, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.27641348110098773</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A153" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C153" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D153" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="E153" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F153" s="9">
-        <f t="array" ref="F153">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A153='Feed rations'!$C$4:$C$19)*(C153='Feed rations'!$D$4:$D$19),0),
-MATCH(D153, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>6.3966897902882333E-2</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A154" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C154" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D154" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="E154" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F154" s="9">
-        <f t="array" ref="F154">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A154='Feed rations'!$C$4:$C$19)*(C154='Feed rations'!$D$4:$D$19),0),
-MATCH(D154, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.49656235864802722</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A155" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C155" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D155" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="E155" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F155" s="9">
-        <f t="array" ref="F155">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A155='Feed rations'!$C$4:$C$19)*(C155='Feed rations'!$D$4:$D$19),0),
-MATCH(D155, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A156" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C156" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D156" s="37" t="s">
-        <v>50</v>
-      </c>
-      <c r="E156" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F156" s="9">
-        <f t="array" ref="F156">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A156='Feed rations'!$C$4:$C$19)*(C156='Feed rations'!$D$4:$D$19),0),
-MATCH(D156, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>30.999999999999993</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A157" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C157" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D157" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="E157" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F157" s="9">
-        <f t="array" ref="F157">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A157='Feed rations'!$C$4:$C$19)*(C157='Feed rations'!$D$4:$D$19),0),
-MATCH(D157, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>1.5935197206160754</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A158" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C158" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D158" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="E158" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F158" s="9">
-        <f t="array" ref="F158">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A158='Feed rations'!$C$4:$C$19)*(C158='Feed rations'!$D$4:$D$19),0),
-MATCH(D158, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.53870093891508897</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A159" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C159" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D159" s="37" t="s">
-        <v>90</v>
-      </c>
-      <c r="E159" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F159" s="9">
-        <f t="array" ref="F159">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A159='Feed rations'!$C$4:$C$19)*(C159='Feed rations'!$D$4:$D$19),0),
-MATCH(D159, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.74539899931977227</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A160" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C160" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D160" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="E160" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F160" s="9">
-        <f t="array" ref="F160">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A160='Feed rations'!$C$4:$C$19)*(C160='Feed rations'!$D$4:$D$19),0),
-MATCH(D160, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.17941015258191029</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A161" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C161" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D161" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="E161" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F161" s="9">
-        <f t="array" ref="F161">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A161='Feed rations'!$C$4:$C$19)*(C161='Feed rations'!$D$4:$D$19),0),
-MATCH(D161, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>1.7964539316658934</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A162" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C162" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D162" s="37" t="s">
-        <v>92</v>
-      </c>
-      <c r="E162" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F162" s="9">
-        <f t="array" ref="F162">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A162='Feed rations'!$C$4:$C$19)*(C162='Feed rations'!$D$4:$D$19),0),
-MATCH(D162, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.1135644201898998</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A163" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C163" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D163" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="E163" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F163" s="9">
-        <f t="array" ref="F163">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A163='Feed rations'!$C$4:$C$19)*(C163='Feed rations'!$D$4:$D$19),0),
-MATCH(D163, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.56830204582053978</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A164" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C164" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D164" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="E164" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F164" s="9">
-        <f t="array" ref="F164">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A164='Feed rations'!$C$4:$C$19)*(C164='Feed rations'!$D$4:$D$19),0),
-MATCH(D164, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.48372359192672859</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A165" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C165" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D165" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="E165" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F165" s="9">
-        <f t="array" ref="F165">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A165='Feed rations'!$C$4:$C$19)*(C165='Feed rations'!$D$4:$D$19),0),
-MATCH(D165, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.11194207133004409</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A166" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C166" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D166" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="E166" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F166" s="9">
-        <f t="array" ref="F166">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A166='Feed rations'!$C$4:$C$19)*(C166='Feed rations'!$D$4:$D$19),0),
-MATCH(D166, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.86898412763404764</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A167" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C167" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D167" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="E167" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F167" s="9">
-        <f t="array" ref="F167">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A167='Feed rations'!$C$4:$C$19)*(C167='Feed rations'!$D$4:$D$19),0),
-MATCH(D167, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>63.333333333333343</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A168" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C168" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D168" s="37" t="s">
-        <v>50</v>
-      </c>
-      <c r="E168" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F168" s="9">
-        <f t="array" ref="F168">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A168='Feed rations'!$C$4:$C$19)*(C168='Feed rations'!$D$4:$D$19),0),
-MATCH(D168, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>31.666666666666664</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A169" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C169" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D169" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="E169" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F169" s="9">
-        <f t="array" ref="F169">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A169='Feed rations'!$C$4:$C$19)*(C169='Feed rations'!$D$4:$D$19),0),
-MATCH(D169, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>1.1382283718686252</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A170" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C170" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D170" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="E170" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F170" s="9">
-        <f t="array" ref="F170">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A170='Feed rations'!$C$4:$C$19)*(C170='Feed rations'!$D$4:$D$19),0),
-MATCH(D170, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.38478638493934925</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A171" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C171" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D171" s="37" t="s">
-        <v>90</v>
-      </c>
-      <c r="E171" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F171" s="9">
-        <f t="array" ref="F171">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A171='Feed rations'!$C$4:$C$19)*(C171='Feed rations'!$D$4:$D$19),0),
-MATCH(D171, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.53242785665698023</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A172" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C172" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D172" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="E172" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F172" s="9">
-        <f t="array" ref="F172">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A172='Feed rations'!$C$4:$C$19)*(C172='Feed rations'!$D$4:$D$19),0),
-MATCH(D172, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.12815010898707879</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A173" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C173" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D173" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="E173" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F173" s="9">
-        <f t="array" ref="F173">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A173='Feed rations'!$C$4:$C$19)*(C173='Feed rations'!$D$4:$D$19),0),
-MATCH(D173, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>1.2831813797613523</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A174" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C174" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D174" s="37" t="s">
-        <v>92</v>
-      </c>
-      <c r="E174" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F174" s="9">
-        <f t="array" ref="F174">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A174='Feed rations'!$C$4:$C$19)*(C174='Feed rations'!$D$4:$D$19),0),
-MATCH(D174, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>8.1117442992785574E-2</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A175" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C175" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D175" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="E175" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F175" s="9">
-        <f t="array" ref="F175">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A175='Feed rations'!$C$4:$C$19)*(C175='Feed rations'!$D$4:$D$19),0),
-MATCH(D175, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.40593003272895695</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A176" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C176" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D176" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="E176" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F176" s="9">
-        <f t="array" ref="F176">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A176='Feed rations'!$C$4:$C$19)*(C176='Feed rations'!$D$4:$D$19),0),
-MATCH(D176, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.34551685137623467</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A177" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C177" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D177" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="E177" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F177" s="9">
-        <f t="array" ref="F177">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A177='Feed rations'!$C$4:$C$19)*(C177='Feed rations'!$D$4:$D$19),0),
-MATCH(D177, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>7.995862237860292E-2</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A178" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C178" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D178" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="E178" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F178" s="9">
-        <f t="array" ref="F178">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A178='Feed rations'!$C$4:$C$19)*(C178='Feed rations'!$D$4:$D$19),0),
-MATCH(D178, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.62070294831003403</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A180" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C180" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D180" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="E180" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F180" s="9">
-        <f t="array" ref="F180">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A180='Feed rations'!$C$4:$C$19)*(C180='Feed rations'!$D$4:$D$19),0),
-MATCH(D180, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>62.666666666666671</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A181" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C181" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D181" s="37" t="s">
-        <v>50</v>
-      </c>
-      <c r="E181" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F181" s="9">
-        <f t="array" ref="F181">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A181='Feed rations'!$C$4:$C$19)*(C181='Feed rations'!$D$4:$D$19),0),
-MATCH(D181, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>31.333333333333329</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A182" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C182" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D182" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="E182" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F182" s="9">
-        <f t="array" ref="F182">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A182='Feed rations'!$C$4:$C$19)*(C182='Feed rations'!$D$4:$D$19),0),
-MATCH(D182, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>1.3658740462423502</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A183" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C183" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D183" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="E183" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F183" s="9">
-        <f t="array" ref="F183">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A183='Feed rations'!$C$4:$C$19)*(C183='Feed rations'!$D$4:$D$19),0),
-MATCH(D183, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.46174366192721905</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A184" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C184" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D184" s="37" t="s">
-        <v>90</v>
-      </c>
-      <c r="E184" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F184" s="9">
-        <f t="array" ref="F184">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A184='Feed rations'!$C$4:$C$19)*(C184='Feed rations'!$D$4:$D$19),0),
-MATCH(D184, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.63891342798837625</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A185" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C185" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D185" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="E185" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F185" s="9">
-        <f t="array" ref="F185">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A185='Feed rations'!$C$4:$C$19)*(C185='Feed rations'!$D$4:$D$19),0),
-MATCH(D185, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.15378013078449451</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A186" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C186" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D186" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="E186" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F186" s="9">
-        <f t="array" ref="F186">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A186='Feed rations'!$C$4:$C$19)*(C186='Feed rations'!$D$4:$D$19),0),
-MATCH(D186, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>1.5398176557136227</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A187" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C187" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D187" s="37" t="s">
-        <v>92</v>
-      </c>
-      <c r="E187" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F187" s="9">
-        <f t="array" ref="F187">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A187='Feed rations'!$C$4:$C$19)*(C187='Feed rations'!$D$4:$D$19),0),
-MATCH(D187, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>9.7340931591342689E-2</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A188" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C188" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D188" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="E188" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F188" s="9">
-        <f t="array" ref="F188">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A188='Feed rations'!$C$4:$C$19)*(C188='Feed rations'!$D$4:$D$19),0),
-MATCH(D188, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.48711603927474834</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A189" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C189" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D189" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="E189" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F189" s="9">
-        <f t="array" ref="F189">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A189='Feed rations'!$C$4:$C$19)*(C189='Feed rations'!$D$4:$D$19),0),
-MATCH(D189, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.41462022165148155</v>
-      </c>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A190" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C190" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D190" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="E190" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F190" s="9">
-        <f t="array" ref="F190">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A190='Feed rations'!$C$4:$C$19)*(C190='Feed rations'!$D$4:$D$19),0),
-MATCH(D190, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>9.5950346854323493E-2</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A191" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C191" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D191" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="E191" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F191" s="9">
-        <f t="array" ref="F191">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A191='Feed rations'!$C$4:$C$19)*(C191='Feed rations'!$D$4:$D$19),0),
-MATCH(D191, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.74484353797204073</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A192" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C192" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D192" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="E192" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F192" s="9">
-        <f t="array" ref="F192">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A192='Feed rations'!$C$4:$C$19)*(C192='Feed rations'!$D$4:$D$19),0),
-MATCH(D192, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>74.166666666666671</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A193" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C193" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D193" s="37" t="s">
-        <v>50</v>
-      </c>
-      <c r="E193" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F193" s="9">
-        <f t="array" ref="F193">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A193='Feed rations'!$C$4:$C$19)*(C193='Feed rations'!$D$4:$D$19),0),
-MATCH(D193, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>14.833333333333332</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A194" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C194" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D194" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="E194" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F194" s="9">
-        <f t="array" ref="F194">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A194='Feed rations'!$C$4:$C$19)*(C194='Feed rations'!$D$4:$D$19),0),
-MATCH(D194, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>2.5041024181109752</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A195" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C195" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D195" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="E195" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F195" s="9">
-        <f t="array" ref="F195">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A195='Feed rations'!$C$4:$C$19)*(C195='Feed rations'!$D$4:$D$19),0),
-MATCH(D195, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.8465300468665683</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A196" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C196" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D196" s="37" t="s">
-        <v>90</v>
-      </c>
-      <c r="E196" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F196" s="9">
-        <f t="array" ref="F196">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A196='Feed rations'!$C$4:$C$19)*(C196='Feed rations'!$D$4:$D$19),0),
-MATCH(D196, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>1.1713412846453564</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A197" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C197" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D197" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="E197" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F197" s="9">
-        <f t="array" ref="F197">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A197='Feed rations'!$C$4:$C$19)*(C197='Feed rations'!$D$4:$D$19),0),
-MATCH(D197, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.28193023977157328</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A198" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C198" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D198" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="E198" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F198" s="9">
-        <f t="array" ref="F198">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A198='Feed rations'!$C$4:$C$19)*(C198='Feed rations'!$D$4:$D$19),0),
-MATCH(D198, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>2.8229990354749752</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A199" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C199" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D199" s="37" t="s">
-        <v>92</v>
-      </c>
-      <c r="E199" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F199" s="9">
-        <f t="array" ref="F199">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A199='Feed rations'!$C$4:$C$19)*(C199='Feed rations'!$D$4:$D$19),0),
-MATCH(D199, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.17845837458412825</v>
-      </c>
-    </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A200" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C200" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D200" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="E200" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F200" s="9">
-        <f t="array" ref="F200">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A200='Feed rations'!$C$4:$C$19)*(C200='Feed rations'!$D$4:$D$19),0),
-MATCH(D200, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.89304607200370534</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A201" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C201" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D201" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="E201" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F201" s="9">
-        <f t="array" ref="F201">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A201='Feed rations'!$C$4:$C$19)*(C201='Feed rations'!$D$4:$D$19),0),
-MATCH(D201, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.76013707302771627</v>
-      </c>
-    </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A202" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C202" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D202" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="E202" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F202" s="9">
-        <f t="array" ref="F202">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A202='Feed rations'!$C$4:$C$19)*(C202='Feed rations'!$D$4:$D$19),0),
-MATCH(D202, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.17590896923292643</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A203" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C203" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D203" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="E203" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F203" s="9">
-        <f t="array" ref="F203">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A203='Feed rations'!$C$4:$C$19)*(C203='Feed rations'!$D$4:$D$19),0),
-MATCH(D203, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>1.3655464862820748</v>
-      </c>
-    </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A204" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C204" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D204" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="E204" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F204" s="9">
-        <f t="array" ref="F204">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A204='Feed rations'!$C$4:$C$19)*(C204='Feed rations'!$D$4:$D$19),0),
-MATCH(D204, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>60.000000000000007</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A205" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C205" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D205" s="37" t="s">
-        <v>50</v>
-      </c>
-      <c r="E205" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F205" s="9">
-        <f t="array" ref="F205">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A205='Feed rations'!$C$4:$C$19)*(C205='Feed rations'!$D$4:$D$19),0),
-MATCH(D205, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A206" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C206" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D206" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="E206" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F206" s="9">
-        <f t="array" ref="F206">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A206='Feed rations'!$C$4:$C$19)*(C206='Feed rations'!$D$4:$D$19),0),
-MATCH(D206, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>2.2764567437372505</v>
-      </c>
-    </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A207" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C207" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D207" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="E207" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F207" s="9">
-        <f t="array" ref="F207">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A207='Feed rations'!$C$4:$C$19)*(C207='Feed rations'!$D$4:$D$19),0),
-MATCH(D207, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.76957276987869849</v>
-      </c>
-    </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A208" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C208" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D208" s="37" t="s">
-        <v>90</v>
-      </c>
-      <c r="E208" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F208" s="9">
-        <f t="array" ref="F208">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A208='Feed rations'!$C$4:$C$19)*(C208='Feed rations'!$D$4:$D$19),0),
-MATCH(D208, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>1.0648557133139605</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A209" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C209" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D209" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="E209" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F209" s="9">
-        <f t="array" ref="F209">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A209='Feed rations'!$C$4:$C$19)*(C209='Feed rations'!$D$4:$D$19),0),
-MATCH(D209, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.25630021797415758</v>
-      </c>
-    </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A210" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C210" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D210" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="E210" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F210" s="9">
-        <f t="array" ref="F210">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A210='Feed rations'!$C$4:$C$19)*(C210='Feed rations'!$D$4:$D$19),0),
-MATCH(D210, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>2.5663627595227045</v>
-      </c>
-    </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A211" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C211" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D211" s="37" t="s">
-        <v>92</v>
-      </c>
-      <c r="E211" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F211" s="9">
-        <f t="array" ref="F211">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A211='Feed rations'!$C$4:$C$19)*(C211='Feed rations'!$D$4:$D$19),0),
-MATCH(D211, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.16223488598557115</v>
-      </c>
-    </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A212" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C212" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D212" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="E212" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F212" s="9">
-        <f t="array" ref="F212">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A212='Feed rations'!$C$4:$C$19)*(C212='Feed rations'!$D$4:$D$19),0),
-MATCH(D212, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.81186006545791389</v>
-      </c>
-    </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A213" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C213" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D213" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="E213" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F213" s="9">
-        <f t="array" ref="F213">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A213='Feed rations'!$C$4:$C$19)*(C213='Feed rations'!$D$4:$D$19),0),
-MATCH(D213, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.69103370275246934</v>
-      </c>
-    </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A214" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C214" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D214" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="E214" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F214" s="9">
-        <f t="array" ref="F214">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A214='Feed rations'!$C$4:$C$19)*(C214='Feed rations'!$D$4:$D$19),0),
-MATCH(D214, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.15991724475720584</v>
-      </c>
-    </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A215" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C215" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D215" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="E215" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F215" s="9">
-        <f t="array" ref="F215">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A215='Feed rations'!$C$4:$C$19)*(C215='Feed rations'!$D$4:$D$19),0),
-MATCH(D215, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>1.2414058966200681</v>
-      </c>
-    </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A216" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C216" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D216" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="E216" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F216" s="9">
-        <f t="array" ref="F216">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A216='Feed rations'!$C$4:$C$19)*(C216='Feed rations'!$D$4:$D$19),0),
-MATCH(D216, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>58.666666666666679</v>
-      </c>
-    </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A217" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C217" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D217" s="37" t="s">
-        <v>50</v>
-      </c>
-      <c r="E217" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F217" s="9">
-        <f t="array" ref="F217">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A217='Feed rations'!$C$4:$C$19)*(C217='Feed rations'!$D$4:$D$19),0),
-MATCH(D217, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>29.333333333333332</v>
-      </c>
-    </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A218" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C218" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D218" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="E218" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F218" s="9">
-        <f t="array" ref="F218">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A218='Feed rations'!$C$4:$C$19)*(C218='Feed rations'!$D$4:$D$19),0),
-MATCH(D218, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>2.7317480924847004</v>
-      </c>
-    </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A219" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C219" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D219" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="E219" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F219" s="9">
-        <f t="array" ref="F219">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A219='Feed rations'!$C$4:$C$19)*(C219='Feed rations'!$D$4:$D$19),0),
-MATCH(D219, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.9234873238544381</v>
-      </c>
-    </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A220" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C220" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D220" s="37" t="s">
-        <v>90</v>
-      </c>
-      <c r="E220" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F220" s="9">
-        <f t="array" ref="F220">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A220='Feed rations'!$C$4:$C$19)*(C220='Feed rations'!$D$4:$D$19),0),
-MATCH(D220, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>1.2778268559767525</v>
-      </c>
-    </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A221" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C221" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D221" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="E221" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F221" s="9">
-        <f t="array" ref="F221">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A221='Feed rations'!$C$4:$C$19)*(C221='Feed rations'!$D$4:$D$19),0),
-MATCH(D221, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.30756026156898902</v>
-      </c>
-    </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A222" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C222" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D222" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="E222" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F222" s="9">
-        <f t="array" ref="F222">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A222='Feed rations'!$C$4:$C$19)*(C222='Feed rations'!$D$4:$D$19),0),
-MATCH(D222, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>3.0796353114272454</v>
-      </c>
-    </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A223" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C223" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D223" s="37" t="s">
-        <v>92</v>
-      </c>
-      <c r="E223" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F223" s="9">
-        <f t="array" ref="F223">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A223='Feed rations'!$C$4:$C$19)*(C223='Feed rations'!$D$4:$D$19),0),
-MATCH(D223, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.19468186318268538</v>
-      </c>
-    </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A224" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C224" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D224" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="E224" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F224" s="9">
-        <f t="array" ref="F224">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A224='Feed rations'!$C$4:$C$19)*(C224='Feed rations'!$D$4:$D$19),0),
-MATCH(D224, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.97423207854949667</v>
-      </c>
-    </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A225" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C225" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D225" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="E225" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F225" s="9">
-        <f t="array" ref="F225">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A225='Feed rations'!$C$4:$C$19)*(C225='Feed rations'!$D$4:$D$19),0),
-MATCH(D225, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.82924044330296309</v>
-      </c>
-    </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A226" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C226" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D226" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="E226" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F226" s="9">
-        <f t="array" ref="F226">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A226='Feed rations'!$C$4:$C$19)*(C226='Feed rations'!$D$4:$D$19),0),
-MATCH(D226, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>0.19190069370864699</v>
-      </c>
-    </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A227" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C227" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D227" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="E227" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F227" s="9">
-        <f t="array" ref="F227">INDEX('Feed rations'!$J$4:$AA$19,
-MATCH(1, (A227='Feed rations'!$C$4:$C$19)*(C227='Feed rations'!$D$4:$D$19),0),
-MATCH(D227, 'Feed rations'!$J$3:$AA$3, 0))</f>
-        <v>1.4896870759440815</v>
+      <c r="F32" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -7597,22 +3775,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C1:AA62"/>
+  <dimension ref="C1:AC56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="25.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.140625" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.140625" style="37"/>
     <col min="12" max="12" width="8.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="3:28" x14ac:dyDescent="0.25">
       <c r="E1" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="3:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:28" x14ac:dyDescent="0.25">
       <c r="E2" s="1" t="s">
         <v>60</v>
       </c>
@@ -7621,10 +3802,10 @@
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="3" spans="3:25" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="3:28" x14ac:dyDescent="0.25">
       <c r="C3" s="1" t="s">
         <v>58</v>
       </c>
@@ -7635,10 +3816,10 @@
         <v>62</v>
       </c>
       <c r="F3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="G3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="H3" t="s">
         <v>62</v>
@@ -7650,40 +3831,46 @@
         <v>50</v>
       </c>
       <c r="L3" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="M3" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="N3" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="O3" s="46" t="s">
+        <v>97</v>
+      </c>
+      <c r="P3" s="46" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q3" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="R3" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="M3" s="37" t="s">
+      <c r="S3" t="s">
+        <v>87</v>
+      </c>
+      <c r="T3" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="U3" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="N3" s="37" t="s">
-        <v>90</v>
-      </c>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="37" t="s">
+      <c r="W3" s="37" t="s">
         <v>91</v>
       </c>
-      <c r="R3" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="S3" t="s">
+      <c r="X3" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="T3" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="U3" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="W3" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="X3" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="Y3" s="37"/>
-    </row>
-    <row r="4" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="Z3" s="37" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="3:28" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>3</v>
       </c>
@@ -7716,47 +3903,60 @@
       </c>
       <c r="L4" s="9">
         <f>$H4*L$25*100</f>
-        <v>0.22764567437372507</v>
+        <v>0.23222788444440265</v>
       </c>
       <c r="M4" s="9">
-        <f t="shared" ref="M4:N19" si="0">$H4*M$25*100</f>
-        <v>7.6957276987869846E-2</v>
+        <f>$H4*M$25*100</f>
+        <v>2.39611841182896E-2</v>
       </c>
       <c r="N4" s="9">
-        <f t="shared" si="0"/>
-        <v>0.10648557133139604</v>
+        <f>$H4*N$25*100</f>
+        <v>8.3427301057299189E-2</v>
+      </c>
+      <c r="O4" s="9">
+        <f>$H4*O$25*100</f>
+        <v>5.8354448396922961E-3</v>
+      </c>
+      <c r="P4" s="9">
+        <f>$H4*P$25*100</f>
+        <v>0.14563835908849923</v>
       </c>
       <c r="Q4" s="9">
-        <f t="shared" ref="Q4:X19" si="1">$H4*Q$25*100</f>
-        <v>2.5630021797415754E-2</v>
+        <f>$H4*Q$25*100</f>
+        <v>6.5200501002148558E-4</v>
       </c>
       <c r="R4" s="9">
-        <f>$H4*SUM(R$25,O$25:P$25)*100</f>
-        <v>0.25663627595227045</v>
+        <f>$H4*R$25*100</f>
+        <v>0.18662665404349996</v>
       </c>
       <c r="S4" s="9">
-        <f t="shared" si="1"/>
-        <v>1.6223488598557115E-2</v>
+        <f>$H4*S$25*100</f>
+        <v>1.9931118668415414E-2</v>
       </c>
       <c r="T4" s="9">
         <f>$H4*SUM(T$25,V$25*0.5)*100</f>
-        <v>8.1186006545791389E-2</v>
+        <v>0.11736525787182231</v>
       </c>
       <c r="U4" s="9">
         <f>$H4*SUM(U$25,V$25*0.5)*100</f>
-        <v>6.9103370275246934E-2</v>
+        <v>5.1422820134132047E-2</v>
       </c>
       <c r="V4" s="9"/>
       <c r="W4" s="9">
-        <f t="shared" si="1"/>
-        <v>1.5991724475720583E-2</v>
+        <f t="shared" ref="Q4:W19" si="0">$H4*W$25*100</f>
+        <v>5.5308011194926036E-4</v>
       </c>
       <c r="X4" s="9">
         <f>$H4*SUM(X$25,Y$25)*100</f>
-        <v>0.12414058966200681</v>
-      </c>
-    </row>
-    <row r="5" spans="3:25" x14ac:dyDescent="0.25">
+        <v>9.5052213142011593E-2</v>
+      </c>
+      <c r="Z4" s="9">
+        <f>$H4*SUM(Z$25,AA$25)*100</f>
+        <v>3.7306677469965008E-2</v>
+      </c>
+      <c r="AB4" s="9"/>
+    </row>
+    <row r="5" spans="3:28" x14ac:dyDescent="0.25">
       <c r="C5" s="37" t="s">
         <v>3</v>
       </c>
@@ -7764,11 +3964,11 @@
         <v>10</v>
       </c>
       <c r="E5" s="36">
-        <f t="shared" ref="E5:E19" si="2">1-H5</f>
+        <f t="shared" ref="E5:E19" si="1">1-H5</f>
         <v>0.98</v>
       </c>
       <c r="F5" s="40">
-        <f t="shared" ref="F5:F19" si="3">1-G5</f>
+        <f t="shared" ref="F5:F19" si="2">1-G5</f>
         <v>0.83333333333333337</v>
       </c>
       <c r="G5" s="39">
@@ -7780,58 +3980,69 @@
       </c>
       <c r="I5" s="40"/>
       <c r="J5" s="38">
-        <f t="shared" ref="J5:J19" si="4">E5*F5*100</f>
+        <f t="shared" ref="J5:J19" si="3">E5*F5*100</f>
         <v>81.666666666666671</v>
       </c>
       <c r="K5" s="38">
-        <f t="shared" ref="K5:K19" si="5">E5*G5*100</f>
+        <f t="shared" ref="K5:K19" si="4">E5*G5*100</f>
         <v>16.333333333333332</v>
       </c>
       <c r="L5" s="9">
-        <f t="shared" ref="L5:L19" si="6">$H5*L$25*100</f>
-        <v>0.45529134874745014</v>
+        <f t="shared" ref="L5:L19" si="5">$H5*L$25*100</f>
+        <v>0.4644557688888053</v>
       </c>
       <c r="M5" s="9">
+        <f t="shared" ref="M4:N19" si="6">$H5*M$25*100</f>
+        <v>4.7922368236579201E-2</v>
+      </c>
+      <c r="N5" s="9">
+        <f t="shared" si="6"/>
+        <v>0.16685460211459838</v>
+      </c>
+      <c r="O5" s="9">
+        <f t="shared" ref="O4:P19" si="7">$H5*O$25*100</f>
+        <v>1.1670889679384592E-2</v>
+      </c>
+      <c r="P5" s="9">
+        <f t="shared" si="7"/>
+        <v>0.29127671817699846</v>
+      </c>
+      <c r="Q5" s="9">
         <f t="shared" si="0"/>
-        <v>0.15391455397573969</v>
-      </c>
-      <c r="N5" s="9">
+        <v>1.3040100200429712E-3</v>
+      </c>
+      <c r="R5" s="9">
         <f t="shared" si="0"/>
-        <v>0.21297114266279207</v>
-      </c>
-      <c r="O5" s="37"/>
-      <c r="P5" s="37"/>
-      <c r="Q5" s="9">
-        <f t="shared" si="1"/>
-        <v>5.1260043594831509E-2</v>
-      </c>
-      <c r="R5" s="9">
-        <f t="shared" ref="R5:R19" si="7">$H5*SUM(R$25,O$25:P$25)*100</f>
-        <v>0.51327255190454091</v>
+        <v>0.37325330808699991</v>
       </c>
       <c r="S5" s="9">
-        <f t="shared" si="1"/>
-        <v>3.244697719711423E-2</v>
+        <f t="shared" si="0"/>
+        <v>3.9862237336830829E-2</v>
       </c>
       <c r="T5" s="9">
         <f t="shared" ref="T5:T19" si="8">$H5*SUM(T$25,V$25*0.5)*100</f>
-        <v>0.16237201309158278</v>
+        <v>0.23473051574364462</v>
       </c>
       <c r="U5" s="9">
         <f t="shared" ref="U5:U19" si="9">$H5*SUM(U$25,V$25*0.5)*100</f>
-        <v>0.13820674055049387</v>
+        <v>0.10284564026826409</v>
       </c>
       <c r="V5" s="9"/>
       <c r="W5" s="9">
-        <f t="shared" si="1"/>
-        <v>3.1983448951441167E-2</v>
+        <f t="shared" si="0"/>
+        <v>1.1061602238985207E-3</v>
       </c>
       <c r="X5" s="9">
         <f t="shared" ref="X5:X19" si="10">$H5*SUM(X$25,Y$25)*100</f>
-        <v>0.24828117932401361</v>
-      </c>
-    </row>
-    <row r="6" spans="3:25" x14ac:dyDescent="0.25">
+        <v>0.19010442628402319</v>
+      </c>
+      <c r="Z5" s="9">
+        <f>$H5*SUM(Z$25,AA$25)*100</f>
+        <v>7.4613354939930016E-2</v>
+      </c>
+      <c r="AB5" s="9"/>
+    </row>
+    <row r="6" spans="3:28" x14ac:dyDescent="0.25">
       <c r="C6" s="37" t="s">
         <v>3</v>
       </c>
@@ -7839,11 +4050,11 @@
         <v>4</v>
       </c>
       <c r="E6" s="36">
+        <f t="shared" si="1"/>
+        <v>0.92999999999999994</v>
+      </c>
+      <c r="F6" s="40">
         <f t="shared" si="2"/>
-        <v>0.92999999999999994</v>
-      </c>
-      <c r="F6" s="40">
-        <f t="shared" si="3"/>
         <v>0.66666666666666674</v>
       </c>
       <c r="G6" s="39">
@@ -7855,58 +4066,69 @@
       </c>
       <c r="I6" s="40"/>
       <c r="J6" s="38">
+        <f t="shared" si="3"/>
+        <v>62</v>
+      </c>
+      <c r="K6" s="38">
         <f t="shared" si="4"/>
-        <v>62</v>
-      </c>
-      <c r="K6" s="38">
+        <v>30.999999999999993</v>
+      </c>
+      <c r="L6" s="9">
         <f t="shared" si="5"/>
-        <v>30.999999999999993</v>
-      </c>
-      <c r="L6" s="9">
+        <v>1.6255951911108186</v>
+      </c>
+      <c r="M6" s="9">
         <f t="shared" si="6"/>
-        <v>1.5935197206160754</v>
-      </c>
-      <c r="M6" s="9">
+        <v>0.16772828882802723</v>
+      </c>
+      <c r="N6" s="9">
+        <f t="shared" si="6"/>
+        <v>0.58399110740109439</v>
+      </c>
+      <c r="O6" s="9">
+        <f t="shared" si="7"/>
+        <v>4.0848113877846079E-2</v>
+      </c>
+      <c r="P6" s="9">
+        <f t="shared" si="7"/>
+        <v>1.0194685136194948</v>
+      </c>
+      <c r="Q6" s="9">
         <f t="shared" si="0"/>
-        <v>0.53870093891508897</v>
-      </c>
-      <c r="N6" s="9">
+        <v>4.5640350701503995E-3</v>
+      </c>
+      <c r="R6" s="9">
         <f t="shared" si="0"/>
-        <v>0.74539899931977227</v>
-      </c>
-      <c r="O6" s="37"/>
-      <c r="P6" s="37"/>
-      <c r="Q6" s="9">
-        <f t="shared" si="1"/>
-        <v>0.17941015258191029</v>
-      </c>
-      <c r="R6" s="9">
-        <f t="shared" si="7"/>
-        <v>1.7964539316658934</v>
+        <v>1.3063865783044997</v>
       </c>
       <c r="S6" s="9">
-        <f t="shared" si="1"/>
-        <v>0.1135644201898998</v>
+        <f t="shared" si="0"/>
+        <v>0.13951783067890791</v>
       </c>
       <c r="T6" s="9">
         <f t="shared" si="8"/>
-        <v>0.56830204582053978</v>
+        <v>0.82155680510275619</v>
       </c>
       <c r="U6" s="9">
         <f t="shared" si="9"/>
-        <v>0.48372359192672859</v>
+        <v>0.35995974093892436</v>
       </c>
       <c r="V6" s="9"/>
       <c r="W6" s="9">
-        <f t="shared" si="1"/>
-        <v>0.11194207133004409</v>
+        <f t="shared" si="0"/>
+        <v>3.8715607836448231E-3</v>
       </c>
       <c r="X6" s="9">
         <f t="shared" si="10"/>
-        <v>0.86898412763404764</v>
-      </c>
-    </row>
-    <row r="7" spans="3:25" x14ac:dyDescent="0.25">
+        <v>0.66536549199408124</v>
+      </c>
+      <c r="Z6" s="9">
+        <f>$H6*SUM(Z$25,AA$25)*100</f>
+        <v>0.2611467422897551</v>
+      </c>
+      <c r="AB6" s="9"/>
+    </row>
+    <row r="7" spans="3:28" x14ac:dyDescent="0.25">
       <c r="C7" s="37" t="s">
         <v>3</v>
       </c>
@@ -7914,11 +4136,11 @@
         <v>5</v>
       </c>
       <c r="E7" s="36">
+        <f t="shared" si="1"/>
+        <v>0.92</v>
+      </c>
+      <c r="F7" s="40">
         <f t="shared" si="2"/>
-        <v>0.92</v>
-      </c>
-      <c r="F7" s="40">
-        <f t="shared" si="3"/>
         <v>0.66666666666666674</v>
       </c>
       <c r="G7" s="39">
@@ -7930,58 +4152,69 @@
       </c>
       <c r="I7" s="40"/>
       <c r="J7" s="38">
+        <f t="shared" si="3"/>
+        <v>61.333333333333343</v>
+      </c>
+      <c r="K7" s="38">
         <f t="shared" si="4"/>
-        <v>61.333333333333343</v>
-      </c>
-      <c r="K7" s="38">
+        <v>30.666666666666664</v>
+      </c>
+      <c r="L7" s="9">
         <f t="shared" si="5"/>
-        <v>30.666666666666664</v>
-      </c>
-      <c r="L7" s="9">
+        <v>1.8578230755552212</v>
+      </c>
+      <c r="M7" s="9">
         <f t="shared" si="6"/>
-        <v>1.8211653949898006</v>
-      </c>
-      <c r="M7" s="9">
+        <v>0.1916894729463168</v>
+      </c>
+      <c r="N7" s="9">
+        <f t="shared" si="6"/>
+        <v>0.66741840845839351</v>
+      </c>
+      <c r="O7" s="9">
+        <f t="shared" si="7"/>
+        <v>4.6683558717538369E-2</v>
+      </c>
+      <c r="P7" s="9">
+        <f t="shared" si="7"/>
+        <v>1.1651068727079938</v>
+      </c>
+      <c r="Q7" s="9">
         <f t="shared" si="0"/>
-        <v>0.61565821590295877</v>
-      </c>
-      <c r="N7" s="9">
+        <v>5.2160400801718847E-3</v>
+      </c>
+      <c r="R7" s="9">
         <f t="shared" si="0"/>
-        <v>0.85188457065116829</v>
-      </c>
-      <c r="O7" s="37"/>
-      <c r="P7" s="37"/>
-      <c r="Q7" s="9">
-        <f t="shared" si="1"/>
-        <v>0.20504017437932603</v>
-      </c>
-      <c r="R7" s="9">
-        <f t="shared" si="7"/>
-        <v>2.0530902076181636</v>
+        <v>1.4930132323479997</v>
       </c>
       <c r="S7" s="9">
-        <f t="shared" si="1"/>
-        <v>0.12978790878845692</v>
+        <f t="shared" si="0"/>
+        <v>0.15944894934732332</v>
       </c>
       <c r="T7" s="9">
         <f t="shared" si="8"/>
-        <v>0.64948805236633111</v>
+        <v>0.93892206297457848</v>
       </c>
       <c r="U7" s="9">
         <f t="shared" si="9"/>
-        <v>0.55282696220197547</v>
+        <v>0.41138256107305637</v>
       </c>
       <c r="V7" s="9"/>
       <c r="W7" s="9">
-        <f t="shared" si="1"/>
-        <v>0.12793379580576467</v>
+        <f>$H7*W$25*100</f>
+        <v>4.4246408955940829E-3</v>
       </c>
       <c r="X7" s="9">
         <f t="shared" si="10"/>
-        <v>0.99312471729605445</v>
-      </c>
-    </row>
-    <row r="8" spans="3:25" x14ac:dyDescent="0.25">
+        <v>0.76041770513609275</v>
+      </c>
+      <c r="Z7" s="9">
+        <f>$H7*SUM(Z$25,AA$25)*100</f>
+        <v>0.29845341975972006</v>
+      </c>
+      <c r="AB7" s="9"/>
+    </row>
+    <row r="8" spans="3:28" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>6</v>
       </c>
@@ -7989,7 +4222,7 @@
         <v>9</v>
       </c>
       <c r="E8" s="36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.99</v>
       </c>
       <c r="F8" s="40">
@@ -8005,58 +4238,69 @@
       </c>
       <c r="I8" s="40"/>
       <c r="J8" s="38">
+        <f t="shared" si="3"/>
+        <v>66</v>
+      </c>
+      <c r="K8" s="38">
         <f t="shared" si="4"/>
-        <v>66</v>
-      </c>
-      <c r="K8" s="38">
+        <v>32.999999999999993</v>
+      </c>
+      <c r="L8" s="9">
         <f t="shared" si="5"/>
-        <v>32.999999999999993</v>
-      </c>
-      <c r="L8" s="9">
+        <v>0.23222788444440265</v>
+      </c>
+      <c r="M8" s="9">
         <f t="shared" si="6"/>
-        <v>0.22764567437372507</v>
-      </c>
-      <c r="M8" s="9">
+        <v>2.39611841182896E-2</v>
+      </c>
+      <c r="N8" s="9">
+        <f t="shared" si="6"/>
+        <v>8.3427301057299189E-2</v>
+      </c>
+      <c r="O8" s="9">
+        <f t="shared" si="7"/>
+        <v>5.8354448396922961E-3</v>
+      </c>
+      <c r="P8" s="9">
+        <f t="shared" si="7"/>
+        <v>0.14563835908849923</v>
+      </c>
+      <c r="Q8" s="9">
         <f t="shared" si="0"/>
-        <v>7.6957276987869846E-2</v>
-      </c>
-      <c r="N8" s="9">
+        <v>6.5200501002148558E-4</v>
+      </c>
+      <c r="R8" s="9">
         <f t="shared" si="0"/>
-        <v>0.10648557133139604</v>
-      </c>
-      <c r="O8" s="37"/>
-      <c r="P8" s="37"/>
-      <c r="Q8" s="9">
-        <f t="shared" si="1"/>
-        <v>2.5630021797415754E-2</v>
-      </c>
-      <c r="R8" s="9">
-        <f t="shared" si="7"/>
-        <v>0.25663627595227045</v>
+        <v>0.18662665404349996</v>
       </c>
       <c r="S8" s="9">
-        <f t="shared" si="1"/>
-        <v>1.6223488598557115E-2</v>
+        <f t="shared" si="0"/>
+        <v>1.9931118668415414E-2</v>
       </c>
       <c r="T8" s="9">
         <f t="shared" si="8"/>
-        <v>8.1186006545791389E-2</v>
+        <v>0.11736525787182231</v>
       </c>
       <c r="U8" s="9">
         <f t="shared" si="9"/>
-        <v>6.9103370275246934E-2</v>
+        <v>5.1422820134132047E-2</v>
       </c>
       <c r="V8" s="9"/>
       <c r="W8" s="9">
-        <f t="shared" si="1"/>
-        <v>1.5991724475720583E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.5308011194926036E-4</v>
       </c>
       <c r="X8" s="9">
-        <f t="shared" si="10"/>
-        <v>0.12414058966200681</v>
-      </c>
-    </row>
-    <row r="9" spans="3:25" x14ac:dyDescent="0.25">
+        <f>$H8*SUM(X$25,Y$25)*100</f>
+        <v>9.5052213142011593E-2</v>
+      </c>
+      <c r="Z8" s="9">
+        <f>$H8*SUM(Z$25,AA$25)*100</f>
+        <v>3.7306677469965008E-2</v>
+      </c>
+      <c r="AB8" s="9"/>
+    </row>
+    <row r="9" spans="3:28" x14ac:dyDescent="0.25">
       <c r="C9" s="37" t="s">
         <v>6</v>
       </c>
@@ -8064,11 +4308,11 @@
         <v>10</v>
       </c>
       <c r="E9" s="36">
+        <f t="shared" si="1"/>
+        <v>0.98</v>
+      </c>
+      <c r="F9" s="40">
         <f t="shared" si="2"/>
-        <v>0.98</v>
-      </c>
-      <c r="F9" s="40">
-        <f t="shared" si="3"/>
         <v>0.83333333333333337</v>
       </c>
       <c r="G9" s="39">
@@ -8080,58 +4324,69 @@
       </c>
       <c r="I9" s="40"/>
       <c r="J9" s="38">
+        <f t="shared" si="3"/>
+        <v>81.666666666666671</v>
+      </c>
+      <c r="K9" s="38">
         <f t="shared" si="4"/>
-        <v>81.666666666666671</v>
-      </c>
-      <c r="K9" s="38">
+        <v>16.333333333333332</v>
+      </c>
+      <c r="L9" s="9">
         <f t="shared" si="5"/>
-        <v>16.333333333333332</v>
-      </c>
-      <c r="L9" s="9">
+        <v>0.4644557688888053</v>
+      </c>
+      <c r="M9" s="9">
         <f t="shared" si="6"/>
-        <v>0.45529134874745014</v>
-      </c>
-      <c r="M9" s="9">
+        <v>4.7922368236579201E-2</v>
+      </c>
+      <c r="N9" s="9">
+        <f t="shared" si="6"/>
+        <v>0.16685460211459838</v>
+      </c>
+      <c r="O9" s="9">
+        <f t="shared" si="7"/>
+        <v>1.1670889679384592E-2</v>
+      </c>
+      <c r="P9" s="9">
+        <f t="shared" si="7"/>
+        <v>0.29127671817699846</v>
+      </c>
+      <c r="Q9" s="9">
         <f t="shared" si="0"/>
-        <v>0.15391455397573969</v>
-      </c>
-      <c r="N9" s="9">
+        <v>1.3040100200429712E-3</v>
+      </c>
+      <c r="R9" s="9">
         <f t="shared" si="0"/>
-        <v>0.21297114266279207</v>
-      </c>
-      <c r="O9" s="37"/>
-      <c r="P9" s="37"/>
-      <c r="Q9" s="9">
-        <f t="shared" si="1"/>
-        <v>5.1260043594831509E-2</v>
-      </c>
-      <c r="R9" s="9">
-        <f t="shared" si="7"/>
-        <v>0.51327255190454091</v>
+        <v>0.37325330808699991</v>
       </c>
       <c r="S9" s="9">
-        <f t="shared" si="1"/>
-        <v>3.244697719711423E-2</v>
+        <f t="shared" si="0"/>
+        <v>3.9862237336830829E-2</v>
       </c>
       <c r="T9" s="9">
         <f t="shared" si="8"/>
-        <v>0.16237201309158278</v>
+        <v>0.23473051574364462</v>
       </c>
       <c r="U9" s="9">
         <f t="shared" si="9"/>
-        <v>0.13820674055049387</v>
+        <v>0.10284564026826409</v>
       </c>
       <c r="V9" s="9"/>
       <c r="W9" s="9">
-        <f t="shared" si="1"/>
-        <v>3.1983448951441167E-2</v>
+        <f t="shared" si="0"/>
+        <v>1.1061602238985207E-3</v>
       </c>
       <c r="X9" s="9">
         <f t="shared" si="10"/>
-        <v>0.24828117932401361</v>
-      </c>
-    </row>
-    <row r="10" spans="3:25" x14ac:dyDescent="0.25">
+        <v>0.19010442628402319</v>
+      </c>
+      <c r="Z9" s="9">
+        <f>$H9*SUM(Z$25,AA$25)*100</f>
+        <v>7.4613354939930016E-2</v>
+      </c>
+      <c r="AB9" s="9"/>
+    </row>
+    <row r="10" spans="3:28" x14ac:dyDescent="0.25">
       <c r="C10" s="37" t="s">
         <v>6</v>
       </c>
@@ -8139,11 +4394,11 @@
         <v>4</v>
       </c>
       <c r="E10" s="36">
+        <f t="shared" si="1"/>
+        <v>0.92999999999999994</v>
+      </c>
+      <c r="F10" s="40">
         <f t="shared" si="2"/>
-        <v>0.92999999999999994</v>
-      </c>
-      <c r="F10" s="40">
-        <f t="shared" si="3"/>
         <v>0.66666666666666674</v>
       </c>
       <c r="G10" s="39">
@@ -8155,58 +4410,69 @@
       </c>
       <c r="I10" s="40"/>
       <c r="J10" s="38">
+        <f t="shared" si="3"/>
+        <v>62</v>
+      </c>
+      <c r="K10" s="38">
         <f t="shared" si="4"/>
-        <v>62</v>
-      </c>
-      <c r="K10" s="38">
+        <v>30.999999999999993</v>
+      </c>
+      <c r="L10" s="9">
         <f t="shared" si="5"/>
-        <v>30.999999999999993</v>
-      </c>
-      <c r="L10" s="9">
+        <v>1.6255951911108186</v>
+      </c>
+      <c r="M10" s="9">
         <f t="shared" si="6"/>
-        <v>1.5935197206160754</v>
-      </c>
-      <c r="M10" s="9">
+        <v>0.16772828882802723</v>
+      </c>
+      <c r="N10" s="9">
+        <f t="shared" si="6"/>
+        <v>0.58399110740109439</v>
+      </c>
+      <c r="O10" s="9">
+        <f t="shared" si="7"/>
+        <v>4.0848113877846079E-2</v>
+      </c>
+      <c r="P10" s="9">
+        <f t="shared" si="7"/>
+        <v>1.0194685136194948</v>
+      </c>
+      <c r="Q10" s="9">
+        <f>$H10*Q$25*100</f>
+        <v>4.5640350701503995E-3</v>
+      </c>
+      <c r="R10" s="9">
         <f t="shared" si="0"/>
-        <v>0.53870093891508897</v>
-      </c>
-      <c r="N10" s="9">
+        <v>1.3063865783044997</v>
+      </c>
+      <c r="S10" s="9">
         <f t="shared" si="0"/>
-        <v>0.74539899931977227</v>
-      </c>
-      <c r="O10" s="37"/>
-      <c r="P10" s="37"/>
-      <c r="Q10" s="9">
-        <f t="shared" si="1"/>
-        <v>0.17941015258191029</v>
-      </c>
-      <c r="R10" s="9">
-        <f t="shared" si="7"/>
-        <v>1.7964539316658934</v>
-      </c>
-      <c r="S10" s="9">
-        <f t="shared" si="1"/>
-        <v>0.1135644201898998</v>
+        <v>0.13951783067890791</v>
       </c>
       <c r="T10" s="9">
         <f t="shared" si="8"/>
-        <v>0.56830204582053978</v>
+        <v>0.82155680510275619</v>
       </c>
       <c r="U10" s="9">
         <f t="shared" si="9"/>
-        <v>0.48372359192672859</v>
+        <v>0.35995974093892436</v>
       </c>
       <c r="V10" s="9"/>
       <c r="W10" s="9">
-        <f t="shared" si="1"/>
-        <v>0.11194207133004409</v>
+        <f t="shared" si="0"/>
+        <v>3.8715607836448231E-3</v>
       </c>
       <c r="X10" s="9">
         <f t="shared" si="10"/>
-        <v>0.86898412763404764</v>
-      </c>
-    </row>
-    <row r="11" spans="3:25" x14ac:dyDescent="0.25">
+        <v>0.66536549199408124</v>
+      </c>
+      <c r="Z10" s="9">
+        <f>$H10*SUM(Z$25,AA$25)*100</f>
+        <v>0.2611467422897551</v>
+      </c>
+      <c r="AB10" s="9"/>
+    </row>
+    <row r="11" spans="3:28" x14ac:dyDescent="0.25">
       <c r="C11" s="37" t="s">
         <v>6</v>
       </c>
@@ -8214,11 +4480,11 @@
         <v>5</v>
       </c>
       <c r="E11" s="36">
+        <f t="shared" si="1"/>
+        <v>0.97</v>
+      </c>
+      <c r="F11" s="40">
         <f t="shared" si="2"/>
-        <v>0.97</v>
-      </c>
-      <c r="F11" s="40">
-        <f t="shared" si="3"/>
         <v>0.66666666666666674</v>
       </c>
       <c r="G11" s="39">
@@ -8230,58 +4496,69 @@
       </c>
       <c r="I11" s="40"/>
       <c r="J11" s="38">
+        <f t="shared" si="3"/>
+        <v>64.666666666666671</v>
+      </c>
+      <c r="K11" s="38">
         <f t="shared" si="4"/>
-        <v>64.666666666666671</v>
-      </c>
-      <c r="K11" s="38">
+        <v>32.333333333333329</v>
+      </c>
+      <c r="L11" s="9">
         <f t="shared" si="5"/>
-        <v>32.333333333333329</v>
-      </c>
-      <c r="L11" s="9">
+        <v>0.69668365333320792</v>
+      </c>
+      <c r="M11" s="9">
         <f t="shared" si="6"/>
-        <v>0.6829370231211751</v>
-      </c>
-      <c r="M11" s="9">
+        <v>7.188355235486879E-2</v>
+      </c>
+      <c r="N11" s="9">
+        <f t="shared" si="6"/>
+        <v>0.25028190317189752</v>
+      </c>
+      <c r="O11" s="9">
+        <f t="shared" si="7"/>
+        <v>1.7506334519076888E-2</v>
+      </c>
+      <c r="P11" s="9">
+        <f t="shared" si="7"/>
+        <v>0.43691507726549772</v>
+      </c>
+      <c r="Q11" s="9">
+        <f>$H11*Q$25*100</f>
+        <v>1.9560150300644568E-3</v>
+      </c>
+      <c r="R11" s="9">
         <f t="shared" si="0"/>
-        <v>0.23087183096360953</v>
-      </c>
-      <c r="N11" s="9">
+        <v>0.55987996213049984</v>
+      </c>
+      <c r="S11" s="9">
         <f t="shared" si="0"/>
-        <v>0.31945671399418812</v>
-      </c>
-      <c r="O11" s="37"/>
-      <c r="P11" s="37"/>
-      <c r="Q11" s="9">
-        <f t="shared" si="1"/>
-        <v>7.6890065392247256E-2</v>
-      </c>
-      <c r="R11" s="9">
-        <f t="shared" si="7"/>
-        <v>0.76990882785681136</v>
-      </c>
-      <c r="S11" s="9">
-        <f t="shared" si="1"/>
-        <v>4.8670465795671344E-2</v>
+        <v>5.9793356005246247E-2</v>
       </c>
       <c r="T11" s="9">
         <f t="shared" si="8"/>
-        <v>0.24355801963737417</v>
+        <v>0.3520957736154669</v>
       </c>
       <c r="U11" s="9">
         <f t="shared" si="9"/>
-        <v>0.20731011082574077</v>
+        <v>0.15426846040239614</v>
       </c>
       <c r="V11" s="9"/>
       <c r="W11" s="9">
-        <f t="shared" si="1"/>
-        <v>4.7975173427161746E-2</v>
+        <f t="shared" si="0"/>
+        <v>1.659240335847781E-3</v>
       </c>
       <c r="X11" s="9">
         <f t="shared" si="10"/>
-        <v>0.37242176898602036</v>
-      </c>
-    </row>
-    <row r="12" spans="3:25" x14ac:dyDescent="0.25">
+        <v>0.28515663942603475</v>
+      </c>
+      <c r="Z11" s="9">
+        <f>$H11*SUM(Z$25,AA$25)*100</f>
+        <v>0.11192003240989502</v>
+      </c>
+      <c r="AB11" s="9"/>
+    </row>
+    <row r="12" spans="3:28" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
         <v>7</v>
       </c>
@@ -8289,7 +4566,7 @@
         <v>9</v>
       </c>
       <c r="E12" s="36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.99</v>
       </c>
       <c r="F12" s="40">
@@ -8305,58 +4582,69 @@
       </c>
       <c r="I12" s="40"/>
       <c r="J12" s="38">
+        <f t="shared" si="3"/>
+        <v>66</v>
+      </c>
+      <c r="K12" s="38">
         <f t="shared" si="4"/>
-        <v>66</v>
-      </c>
-      <c r="K12" s="38">
+        <v>32.999999999999993</v>
+      </c>
+      <c r="L12" s="9">
         <f t="shared" si="5"/>
-        <v>32.999999999999993</v>
-      </c>
-      <c r="L12" s="9">
+        <v>0.23222788444440265</v>
+      </c>
+      <c r="M12" s="9">
         <f t="shared" si="6"/>
-        <v>0.22764567437372507</v>
-      </c>
-      <c r="M12" s="9">
+        <v>2.39611841182896E-2</v>
+      </c>
+      <c r="N12" s="9">
+        <f t="shared" si="6"/>
+        <v>8.3427301057299189E-2</v>
+      </c>
+      <c r="O12" s="9">
+        <f t="shared" si="7"/>
+        <v>5.8354448396922961E-3</v>
+      </c>
+      <c r="P12" s="9">
+        <f t="shared" si="7"/>
+        <v>0.14563835908849923</v>
+      </c>
+      <c r="Q12" s="9">
         <f t="shared" si="0"/>
-        <v>7.6957276987869846E-2</v>
-      </c>
-      <c r="N12" s="9">
+        <v>6.5200501002148558E-4</v>
+      </c>
+      <c r="R12" s="9">
         <f t="shared" si="0"/>
-        <v>0.10648557133139604</v>
-      </c>
-      <c r="O12" s="37"/>
-      <c r="P12" s="37"/>
-      <c r="Q12" s="9">
-        <f t="shared" si="1"/>
-        <v>2.5630021797415754E-2</v>
-      </c>
-      <c r="R12" s="9">
-        <f t="shared" si="7"/>
-        <v>0.25663627595227045</v>
+        <v>0.18662665404349996</v>
       </c>
       <c r="S12" s="9">
-        <f t="shared" si="1"/>
-        <v>1.6223488598557115E-2</v>
+        <f t="shared" si="0"/>
+        <v>1.9931118668415414E-2</v>
       </c>
       <c r="T12" s="9">
         <f t="shared" si="8"/>
-        <v>8.1186006545791389E-2</v>
+        <v>0.11736525787182231</v>
       </c>
       <c r="U12" s="9">
         <f t="shared" si="9"/>
-        <v>6.9103370275246934E-2</v>
+        <v>5.1422820134132047E-2</v>
       </c>
       <c r="V12" s="9"/>
       <c r="W12" s="9">
-        <f t="shared" si="1"/>
-        <v>1.5991724475720583E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.5308011194926036E-4</v>
       </c>
       <c r="X12" s="9">
         <f t="shared" si="10"/>
-        <v>0.12414058966200681</v>
-      </c>
-    </row>
-    <row r="13" spans="3:25" x14ac:dyDescent="0.25">
+        <v>9.5052213142011593E-2</v>
+      </c>
+      <c r="Z12" s="9">
+        <f>$H12*SUM(Z$25,AA$25)*100</f>
+        <v>3.7306677469965008E-2</v>
+      </c>
+      <c r="AB12" s="9"/>
+    </row>
+    <row r="13" spans="3:28" x14ac:dyDescent="0.25">
       <c r="C13" s="37" t="s">
         <v>7</v>
       </c>
@@ -8364,11 +4652,11 @@
         <v>10</v>
       </c>
       <c r="E13" s="36">
+        <f t="shared" si="1"/>
+        <v>0.96</v>
+      </c>
+      <c r="F13" s="40">
         <f t="shared" si="2"/>
-        <v>0.96</v>
-      </c>
-      <c r="F13" s="40">
-        <f t="shared" si="3"/>
         <v>0.83333333333333337</v>
       </c>
       <c r="G13" s="39">
@@ -8380,58 +4668,69 @@
       </c>
       <c r="I13" s="40"/>
       <c r="J13" s="38">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="K13" s="38">
         <f t="shared" si="4"/>
-        <v>80</v>
-      </c>
-      <c r="K13" s="38">
+        <v>15.999999999999998</v>
+      </c>
+      <c r="L13" s="9">
         <f t="shared" si="5"/>
-        <v>15.999999999999998</v>
-      </c>
-      <c r="L13" s="9">
+        <v>0.9289115377776106</v>
+      </c>
+      <c r="M13" s="9">
         <f t="shared" si="6"/>
-        <v>0.91058269749490028</v>
-      </c>
-      <c r="M13" s="9">
+        <v>9.5844736473158401E-2</v>
+      </c>
+      <c r="N13" s="9">
+        <f t="shared" si="6"/>
+        <v>0.33370920422919675</v>
+      </c>
+      <c r="O13" s="9">
+        <f t="shared" si="7"/>
+        <v>2.3341779358769184E-2</v>
+      </c>
+      <c r="P13" s="9">
+        <f t="shared" si="7"/>
+        <v>0.58255343635399692</v>
+      </c>
+      <c r="Q13" s="9">
         <f t="shared" si="0"/>
-        <v>0.30782910795147939</v>
-      </c>
-      <c r="N13" s="9">
+        <v>2.6080200400859423E-3</v>
+      </c>
+      <c r="R13" s="9">
         <f t="shared" si="0"/>
-        <v>0.42594228532558415</v>
-      </c>
-      <c r="O13" s="37"/>
-      <c r="P13" s="37"/>
-      <c r="Q13" s="9">
-        <f t="shared" si="1"/>
-        <v>0.10252008718966302</v>
-      </c>
-      <c r="R13" s="9">
-        <f t="shared" si="7"/>
-        <v>1.0265451038090818</v>
+        <v>0.74650661617399983</v>
       </c>
       <c r="S13" s="9">
-        <f t="shared" si="1"/>
-        <v>6.4893954394228459E-2</v>
+        <f t="shared" si="0"/>
+        <v>7.9724474673661658E-2</v>
       </c>
       <c r="T13" s="9">
         <f t="shared" si="8"/>
-        <v>0.32474402618316556</v>
+        <v>0.46946103148728924</v>
       </c>
       <c r="U13" s="9">
         <f t="shared" si="9"/>
-        <v>0.27641348110098773</v>
+        <v>0.20569128053652819</v>
       </c>
       <c r="V13" s="9"/>
       <c r="W13" s="9">
-        <f t="shared" si="1"/>
-        <v>6.3966897902882333E-2</v>
+        <f t="shared" si="0"/>
+        <v>2.2123204477970415E-3</v>
       </c>
       <c r="X13" s="9">
         <f t="shared" si="10"/>
-        <v>0.49656235864802722</v>
-      </c>
-    </row>
-    <row r="14" spans="3:25" x14ac:dyDescent="0.25">
+        <v>0.38020885256804637</v>
+      </c>
+      <c r="Z13" s="9">
+        <f>$H13*SUM(Z$25,AA$25)*100</f>
+        <v>0.14922670987986003</v>
+      </c>
+      <c r="AB13" s="9"/>
+    </row>
+    <row r="14" spans="3:28" x14ac:dyDescent="0.25">
       <c r="C14" s="37" t="s">
         <v>7</v>
       </c>
@@ -8439,11 +4738,11 @@
         <v>4</v>
       </c>
       <c r="E14" s="36">
+        <f t="shared" si="1"/>
+        <v>0.92999999999999994</v>
+      </c>
+      <c r="F14" s="40">
         <f t="shared" si="2"/>
-        <v>0.92999999999999994</v>
-      </c>
-      <c r="F14" s="40">
-        <f t="shared" si="3"/>
         <v>0.66666666666666674</v>
       </c>
       <c r="G14" s="39">
@@ -8455,58 +4754,69 @@
       </c>
       <c r="I14" s="40"/>
       <c r="J14" s="38">
+        <f t="shared" si="3"/>
+        <v>62</v>
+      </c>
+      <c r="K14" s="38">
         <f t="shared" si="4"/>
-        <v>62</v>
-      </c>
-      <c r="K14" s="38">
+        <v>30.999999999999993</v>
+      </c>
+      <c r="L14" s="9">
         <f t="shared" si="5"/>
-        <v>30.999999999999993</v>
-      </c>
-      <c r="L14" s="9">
+        <v>1.6255951911108186</v>
+      </c>
+      <c r="M14" s="9">
         <f t="shared" si="6"/>
-        <v>1.5935197206160754</v>
-      </c>
-      <c r="M14" s="9">
+        <v>0.16772828882802723</v>
+      </c>
+      <c r="N14" s="9">
+        <f t="shared" si="6"/>
+        <v>0.58399110740109439</v>
+      </c>
+      <c r="O14" s="9">
+        <f t="shared" si="7"/>
+        <v>4.0848113877846079E-2</v>
+      </c>
+      <c r="P14" s="9">
+        <f t="shared" si="7"/>
+        <v>1.0194685136194948</v>
+      </c>
+      <c r="Q14" s="9">
         <f t="shared" si="0"/>
-        <v>0.53870093891508897</v>
-      </c>
-      <c r="N14" s="9">
+        <v>4.5640350701503995E-3</v>
+      </c>
+      <c r="R14" s="9">
         <f t="shared" si="0"/>
-        <v>0.74539899931977227</v>
-      </c>
-      <c r="O14" s="37"/>
-      <c r="P14" s="37"/>
-      <c r="Q14" s="9">
-        <f t="shared" si="1"/>
-        <v>0.17941015258191029</v>
-      </c>
-      <c r="R14" s="9">
-        <f t="shared" si="7"/>
-        <v>1.7964539316658934</v>
+        <v>1.3063865783044997</v>
       </c>
       <c r="S14" s="9">
-        <f t="shared" si="1"/>
-        <v>0.1135644201898998</v>
+        <f t="shared" si="0"/>
+        <v>0.13951783067890791</v>
       </c>
       <c r="T14" s="9">
         <f t="shared" si="8"/>
-        <v>0.56830204582053978</v>
+        <v>0.82155680510275619</v>
       </c>
       <c r="U14" s="9">
         <f t="shared" si="9"/>
-        <v>0.48372359192672859</v>
+        <v>0.35995974093892436</v>
       </c>
       <c r="V14" s="9"/>
       <c r="W14" s="9">
-        <f t="shared" si="1"/>
-        <v>0.11194207133004409</v>
+        <f t="shared" si="0"/>
+        <v>3.8715607836448231E-3</v>
       </c>
       <c r="X14" s="9">
         <f t="shared" si="10"/>
-        <v>0.86898412763404764</v>
-      </c>
-    </row>
-    <row r="15" spans="3:25" x14ac:dyDescent="0.25">
+        <v>0.66536549199408124</v>
+      </c>
+      <c r="Z14" s="9">
+        <f>$H14*SUM(Z$25,AA$25)*100</f>
+        <v>0.2611467422897551</v>
+      </c>
+      <c r="AB14" s="9"/>
+    </row>
+    <row r="15" spans="3:28" x14ac:dyDescent="0.25">
       <c r="C15" s="37" t="s">
         <v>7</v>
       </c>
@@ -8514,11 +4824,11 @@
         <v>5</v>
       </c>
       <c r="E15" s="36">
+        <f t="shared" si="1"/>
+        <v>0.95</v>
+      </c>
+      <c r="F15" s="40">
         <f t="shared" si="2"/>
-        <v>0.95</v>
-      </c>
-      <c r="F15" s="40">
-        <f t="shared" si="3"/>
         <v>0.66666666666666674</v>
       </c>
       <c r="G15" s="39">
@@ -8530,58 +4840,69 @@
       </c>
       <c r="I15" s="40"/>
       <c r="J15" s="38">
+        <f t="shared" si="3"/>
+        <v>63.333333333333343</v>
+      </c>
+      <c r="K15" s="38">
         <f t="shared" si="4"/>
-        <v>63.333333333333343</v>
-      </c>
-      <c r="K15" s="38">
+        <v>31.666666666666664</v>
+      </c>
+      <c r="L15" s="9">
         <f t="shared" si="5"/>
-        <v>31.666666666666664</v>
-      </c>
-      <c r="L15" s="9">
+        <v>1.1611394222220133</v>
+      </c>
+      <c r="M15" s="9">
         <f t="shared" si="6"/>
-        <v>1.1382283718686252</v>
-      </c>
-      <c r="M15" s="9">
+        <v>0.11980592059144801</v>
+      </c>
+      <c r="N15" s="9">
+        <f t="shared" si="6"/>
+        <v>0.41713650528649598</v>
+      </c>
+      <c r="O15" s="9">
+        <f t="shared" si="7"/>
+        <v>2.9177224198461485E-2</v>
+      </c>
+      <c r="P15" s="9">
+        <f t="shared" si="7"/>
+        <v>0.72819179544249613</v>
+      </c>
+      <c r="Q15" s="9">
         <f t="shared" si="0"/>
-        <v>0.38478638493934925</v>
-      </c>
-      <c r="N15" s="9">
+        <v>3.2600250501074284E-3</v>
+      </c>
+      <c r="R15" s="9">
         <f t="shared" si="0"/>
-        <v>0.53242785665698023</v>
-      </c>
-      <c r="O15" s="37"/>
-      <c r="P15" s="37"/>
-      <c r="Q15" s="9">
-        <f t="shared" si="1"/>
-        <v>0.12815010898707879</v>
-      </c>
-      <c r="R15" s="9">
-        <f t="shared" si="7"/>
-        <v>1.2831813797613523</v>
+        <v>0.93313327021749981</v>
       </c>
       <c r="S15" s="9">
-        <f t="shared" si="1"/>
-        <v>8.1117442992785574E-2</v>
+        <f t="shared" si="0"/>
+        <v>9.9655593342077062E-2</v>
       </c>
       <c r="T15" s="9">
         <f t="shared" si="8"/>
-        <v>0.40593003272895695</v>
+        <v>0.58682628935911163</v>
       </c>
       <c r="U15" s="9">
         <f t="shared" si="9"/>
-        <v>0.34551685137623467</v>
+        <v>0.25711410067066026</v>
       </c>
       <c r="V15" s="9"/>
       <c r="W15" s="9">
-        <f t="shared" si="1"/>
-        <v>7.995862237860292E-2</v>
+        <f t="shared" si="0"/>
+        <v>2.7654005597463021E-3</v>
       </c>
       <c r="X15" s="9">
         <f t="shared" si="10"/>
-        <v>0.62070294831003403</v>
-      </c>
-    </row>
-    <row r="16" spans="3:25" x14ac:dyDescent="0.25">
+        <v>0.47526106571005799</v>
+      </c>
+      <c r="Z15" s="9">
+        <f>$H15*SUM(Z$25,AA$25)*100</f>
+        <v>0.18653338734982505</v>
+      </c>
+      <c r="AB15" s="9"/>
+    </row>
+    <row r="16" spans="3:28" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
         <v>8</v>
       </c>
@@ -8589,7 +4910,7 @@
         <v>9</v>
       </c>
       <c r="E16" s="36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.94</v>
       </c>
       <c r="F16" s="40">
@@ -8605,58 +4926,69 @@
       </c>
       <c r="I16" s="40"/>
       <c r="J16" s="38">
+        <f t="shared" si="3"/>
+        <v>62.666666666666671</v>
+      </c>
+      <c r="K16" s="38">
         <f t="shared" si="4"/>
-        <v>62.666666666666671</v>
-      </c>
-      <c r="K16" s="38">
+        <v>31.333333333333329</v>
+      </c>
+      <c r="L16" s="9">
         <f t="shared" si="5"/>
-        <v>31.333333333333329</v>
-      </c>
-      <c r="L16" s="9">
+        <v>1.3933673066664158</v>
+      </c>
+      <c r="M16" s="9">
         <f t="shared" si="6"/>
-        <v>1.3658740462423502</v>
-      </c>
-      <c r="M16" s="9">
+        <v>0.14376710470973758</v>
+      </c>
+      <c r="N16" s="9">
+        <f t="shared" si="6"/>
+        <v>0.50056380634379505</v>
+      </c>
+      <c r="O16" s="9">
+        <f t="shared" si="7"/>
+        <v>3.5012669038153775E-2</v>
+      </c>
+      <c r="P16" s="9">
+        <f t="shared" si="7"/>
+        <v>0.87383015453099544</v>
+      </c>
+      <c r="Q16" s="9">
         <f t="shared" si="0"/>
-        <v>0.46174366192721905</v>
-      </c>
-      <c r="N16" s="9">
+        <v>3.9120300601289135E-3</v>
+      </c>
+      <c r="R16" s="9">
         <f t="shared" si="0"/>
-        <v>0.63891342798837625</v>
-      </c>
-      <c r="O16" s="37"/>
-      <c r="P16" s="37"/>
-      <c r="Q16" s="9">
-        <f t="shared" si="1"/>
-        <v>0.15378013078449451</v>
-      </c>
-      <c r="R16" s="9">
-        <f t="shared" si="7"/>
-        <v>1.5398176557136227</v>
+        <v>1.1197599242609997</v>
       </c>
       <c r="S16" s="9">
-        <f t="shared" si="1"/>
-        <v>9.7340931591342689E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.11958671201049249</v>
       </c>
       <c r="T16" s="9">
         <f t="shared" si="8"/>
-        <v>0.48711603927474834</v>
+        <v>0.7041915472309338</v>
       </c>
       <c r="U16" s="9">
         <f t="shared" si="9"/>
-        <v>0.41462022165148155</v>
+        <v>0.30853692080479228</v>
       </c>
       <c r="V16" s="9"/>
       <c r="W16" s="9">
-        <f t="shared" si="1"/>
-        <v>9.5950346854323493E-2</v>
+        <f t="shared" si="0"/>
+        <v>3.318480671695562E-3</v>
       </c>
       <c r="X16" s="9">
         <f t="shared" si="10"/>
-        <v>0.74484353797204073</v>
-      </c>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.25">
+        <v>0.57031327885206951</v>
+      </c>
+      <c r="Z16" s="9">
+        <f>$H16*SUM(Z$25,AA$25)*100</f>
+        <v>0.22384006481979005</v>
+      </c>
+      <c r="AB16" s="9"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C17" s="37" t="s">
         <v>8</v>
       </c>
@@ -8664,11 +4996,11 @@
         <v>10</v>
       </c>
       <c r="E17" s="36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.89</v>
       </c>
       <c r="F17" s="40">
-        <f t="shared" si="3"/>
+        <f>1-G17</f>
         <v>0.83333333333333337</v>
       </c>
       <c r="G17" s="39">
@@ -8680,58 +5012,69 @@
       </c>
       <c r="I17" s="40"/>
       <c r="J17" s="38">
-        <f t="shared" si="4"/>
+        <f>E17*F17*100</f>
         <v>74.166666666666671</v>
       </c>
       <c r="K17" s="38">
-        <f t="shared" si="5"/>
+        <f>E17*G17*100</f>
         <v>14.833333333333332</v>
       </c>
       <c r="L17" s="9">
+        <f>$H17*L$25*100</f>
+        <v>2.5545067288884291</v>
+      </c>
+      <c r="M17" s="9">
         <f t="shared" si="6"/>
-        <v>2.5041024181109752</v>
-      </c>
-      <c r="M17" s="9">
+        <v>0.26357302530118559</v>
+      </c>
+      <c r="N17" s="9">
+        <f t="shared" si="6"/>
+        <v>0.91770031163029109</v>
+      </c>
+      <c r="O17" s="9">
+        <f t="shared" si="7"/>
+        <v>6.4189893236615267E-2</v>
+      </c>
+      <c r="P17" s="9">
+        <f t="shared" si="7"/>
+        <v>1.6020219499734916</v>
+      </c>
+      <c r="Q17" s="9">
         <f t="shared" si="0"/>
-        <v>0.8465300468665683</v>
-      </c>
-      <c r="N17" s="9">
+        <v>7.172055110236341E-3</v>
+      </c>
+      <c r="R17" s="9">
         <f t="shared" si="0"/>
-        <v>1.1713412846453564</v>
-      </c>
-      <c r="O17" s="37"/>
-      <c r="P17" s="37"/>
-      <c r="Q17" s="9">
-        <f t="shared" si="1"/>
-        <v>0.28193023977157328</v>
-      </c>
-      <c r="R17" s="9">
-        <f t="shared" si="7"/>
-        <v>2.8229990354749752</v>
+        <v>2.0528931944784996</v>
       </c>
       <c r="S17" s="9">
-        <f t="shared" si="1"/>
-        <v>0.17845837458412825</v>
+        <f t="shared" si="0"/>
+        <v>0.21924230535256958</v>
       </c>
       <c r="T17" s="9">
         <f t="shared" si="8"/>
-        <v>0.89304607200370534</v>
+        <v>1.2910178365900453</v>
       </c>
       <c r="U17" s="9">
         <f t="shared" si="9"/>
-        <v>0.76013707302771627</v>
+        <v>0.56565102147545254</v>
       </c>
       <c r="V17" s="9"/>
       <c r="W17" s="9">
-        <f t="shared" si="1"/>
-        <v>0.17590896923292643</v>
+        <f t="shared" si="0"/>
+        <v>6.0838812314418641E-3</v>
       </c>
       <c r="X17" s="9">
         <f t="shared" si="10"/>
-        <v>1.3655464862820748</v>
-      </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.25">
+        <v>1.0455743445621275</v>
+      </c>
+      <c r="Z17" s="9">
+        <f>$H17*SUM(Z$25,AA$25)*100</f>
+        <v>0.41037345216961513</v>
+      </c>
+      <c r="AB17" s="9"/>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C18" s="37" t="s">
         <v>8</v>
       </c>
@@ -8739,11 +5082,11 @@
         <v>4</v>
       </c>
       <c r="E18" s="36">
+        <f t="shared" si="1"/>
+        <v>0.9</v>
+      </c>
+      <c r="F18" s="40">
         <f t="shared" si="2"/>
-        <v>0.9</v>
-      </c>
-      <c r="F18" s="40">
-        <f t="shared" si="3"/>
         <v>0.66666666666666674</v>
       </c>
       <c r="G18" s="39">
@@ -8755,58 +5098,69 @@
       </c>
       <c r="I18" s="40"/>
       <c r="J18" s="38">
+        <f t="shared" si="3"/>
+        <v>60.000000000000007</v>
+      </c>
+      <c r="K18" s="38">
         <f t="shared" si="4"/>
-        <v>60.000000000000007</v>
-      </c>
-      <c r="K18" s="38">
+        <v>30</v>
+      </c>
+      <c r="L18" s="9">
         <f t="shared" si="5"/>
-        <v>30</v>
-      </c>
-      <c r="L18" s="9">
+        <v>2.3222788444440265</v>
+      </c>
+      <c r="M18" s="9">
         <f t="shared" si="6"/>
-        <v>2.2764567437372505</v>
-      </c>
-      <c r="M18" s="9">
+        <v>0.23961184118289602</v>
+      </c>
+      <c r="N18" s="9">
+        <f t="shared" si="6"/>
+        <v>0.83427301057299197</v>
+      </c>
+      <c r="O18" s="9">
+        <f t="shared" si="7"/>
+        <v>5.835444839692297E-2</v>
+      </c>
+      <c r="P18" s="9">
+        <f t="shared" si="7"/>
+        <v>1.4563835908849923</v>
+      </c>
+      <c r="Q18" s="9">
         <f t="shared" si="0"/>
-        <v>0.76957276987869849</v>
-      </c>
-      <c r="N18" s="9">
+        <v>6.5200501002148567E-3</v>
+      </c>
+      <c r="R18" s="9">
         <f t="shared" si="0"/>
-        <v>1.0648557133139605</v>
-      </c>
-      <c r="O18" s="37"/>
-      <c r="P18" s="37"/>
-      <c r="Q18" s="9">
-        <f t="shared" si="1"/>
-        <v>0.25630021797415758</v>
-      </c>
-      <c r="R18" s="9">
-        <f t="shared" si="7"/>
-        <v>2.5663627595227045</v>
+        <v>1.8662665404349996</v>
       </c>
       <c r="S18" s="9">
-        <f t="shared" si="1"/>
-        <v>0.16223488598557115</v>
+        <f t="shared" si="0"/>
+        <v>0.19931118668415412</v>
       </c>
       <c r="T18" s="9">
         <f t="shared" si="8"/>
-        <v>0.81186006545791389</v>
+        <v>1.1736525787182233</v>
       </c>
       <c r="U18" s="9">
         <f t="shared" si="9"/>
-        <v>0.69103370275246934</v>
+        <v>0.51422820134132052</v>
       </c>
       <c r="V18" s="9"/>
       <c r="W18" s="9">
-        <f t="shared" si="1"/>
-        <v>0.15991724475720584</v>
+        <f t="shared" si="0"/>
+        <v>5.5308011194926043E-3</v>
       </c>
       <c r="X18" s="9">
         <f t="shared" si="10"/>
-        <v>1.2414058966200681</v>
-      </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.25">
+        <v>0.95052213142011599</v>
+      </c>
+      <c r="Z18" s="9">
+        <f>$H18*SUM(Z$25,AA$25)*100</f>
+        <v>0.37306677469965011</v>
+      </c>
+      <c r="AB18" s="9"/>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C19" s="37" t="s">
         <v>8</v>
       </c>
@@ -8814,11 +5168,11 @@
         <v>5</v>
       </c>
       <c r="E19" s="36">
+        <f t="shared" si="1"/>
+        <v>0.88</v>
+      </c>
+      <c r="F19" s="40">
         <f t="shared" si="2"/>
-        <v>0.88</v>
-      </c>
-      <c r="F19" s="40">
-        <f t="shared" si="3"/>
         <v>0.66666666666666674</v>
       </c>
       <c r="G19" s="39">
@@ -8830,188 +5184,202 @@
       </c>
       <c r="I19" s="40"/>
       <c r="J19" s="38">
+        <f t="shared" si="3"/>
+        <v>58.666666666666679</v>
+      </c>
+      <c r="K19" s="38">
         <f t="shared" si="4"/>
-        <v>58.666666666666679</v>
-      </c>
-      <c r="K19" s="38">
+        <v>29.333333333333332</v>
+      </c>
+      <c r="L19" s="9">
         <f t="shared" si="5"/>
-        <v>29.333333333333332</v>
-      </c>
-      <c r="L19" s="9">
+        <v>2.7867346133328317</v>
+      </c>
+      <c r="M19" s="9">
         <f t="shared" si="6"/>
-        <v>2.7317480924847004</v>
-      </c>
-      <c r="M19" s="9">
+        <v>0.28753420941947516</v>
+      </c>
+      <c r="N19" s="9">
+        <f t="shared" si="6"/>
+        <v>1.0011276126875901</v>
+      </c>
+      <c r="O19" s="9">
+        <f t="shared" si="7"/>
+        <v>7.002533807630755E-2</v>
+      </c>
+      <c r="P19" s="9">
+        <f t="shared" si="7"/>
+        <v>1.7476603090619909</v>
+      </c>
+      <c r="Q19" s="9">
         <f t="shared" si="0"/>
-        <v>0.9234873238544381</v>
-      </c>
-      <c r="N19" s="9">
+        <v>7.824060120257827E-3</v>
+      </c>
+      <c r="R19" s="9">
         <f t="shared" si="0"/>
-        <v>1.2778268559767525</v>
-      </c>
-      <c r="O19" s="37"/>
-      <c r="P19" s="37"/>
-      <c r="Q19" s="9">
-        <f t="shared" si="1"/>
-        <v>0.30756026156898902</v>
-      </c>
-      <c r="R19" s="9">
-        <f t="shared" si="7"/>
-        <v>3.0796353114272454</v>
+        <v>2.2395198485219994</v>
       </c>
       <c r="S19" s="9">
-        <f t="shared" si="1"/>
-        <v>0.19468186318268538</v>
+        <f t="shared" si="0"/>
+        <v>0.23917342402098499</v>
       </c>
       <c r="T19" s="9">
         <f t="shared" si="8"/>
-        <v>0.97423207854949667</v>
+        <v>1.4083830944618676</v>
       </c>
       <c r="U19" s="9">
         <f t="shared" si="9"/>
-        <v>0.82924044330296309</v>
+        <v>0.61707384160958456</v>
       </c>
       <c r="V19" s="9"/>
       <c r="W19" s="9">
-        <f t="shared" si="1"/>
-        <v>0.19190069370864699</v>
+        <f t="shared" si="0"/>
+        <v>6.6369613433911239E-3</v>
       </c>
       <c r="X19" s="9">
         <f t="shared" si="10"/>
-        <v>1.4896870759440815</v>
-      </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.25">
+        <v>1.140626557704139</v>
+      </c>
+      <c r="Z19" s="9">
+        <f>$H19*SUM(Z$25,AA$25)*100</f>
+        <v>0.44768012963958009</v>
+      </c>
+      <c r="AB19" s="9"/>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.25">
       <c r="J21" s="34" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.25">
       <c r="K22" t="s">
         <v>62</v>
       </c>
       <c r="L22" t="s">
+        <v>63</v>
+      </c>
+      <c r="M22" t="s">
+        <v>66</v>
+      </c>
+      <c r="N22" t="s">
+        <v>67</v>
+      </c>
+      <c r="O22" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="M22" t="s">
-        <v>67</v>
-      </c>
-      <c r="N22" t="s">
+      <c r="P22" s="46" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>93</v>
+      </c>
+      <c r="R22" t="s">
         <v>68</v>
       </c>
-      <c r="O22" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="P22" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q22" t="s">
+      <c r="S22" t="s">
         <v>69</v>
       </c>
-      <c r="R22" t="s">
+      <c r="T22" t="s">
+        <v>94</v>
+      </c>
+      <c r="U22" t="s">
         <v>70</v>
       </c>
-      <c r="S22" t="s">
+      <c r="V22" s="46" t="s">
+        <v>95</v>
+      </c>
+      <c r="W22" t="s">
         <v>71</v>
       </c>
-      <c r="T22" t="s">
+      <c r="X22" t="s">
         <v>72</v>
       </c>
-      <c r="U22" t="s">
+      <c r="Y22" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="V22" s="4" t="s">
+      <c r="Z22" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="W22" t="s">
+      <c r="AA22" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="X22" t="s">
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="J23" t="s">
         <v>76</v>
       </c>
-      <c r="Y22" s="4" t="s">
+      <c r="K23">
+        <f>SUM(L23:AA23)</f>
+        <v>23690.191499999997</v>
+      </c>
+      <c r="L23">
+        <v>6197.4449999999997</v>
+      </c>
+      <c r="M23">
+        <v>639.45000000000005</v>
+      </c>
+      <c r="N23">
+        <v>2226.4169999999999</v>
+      </c>
+      <c r="O23">
+        <v>155.72999999999999</v>
+      </c>
+      <c r="P23">
+        <v>3886.6379999999995</v>
+      </c>
+      <c r="Q23">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="R23">
+        <v>4980.4890000000005</v>
+      </c>
+      <c r="S23">
+        <v>402.4</v>
+      </c>
+      <c r="T23">
+        <v>118.8</v>
+      </c>
+      <c r="U23">
+        <v>1224.5999999999999</v>
+      </c>
+      <c r="V23">
+        <v>295.43249999999995</v>
+      </c>
+      <c r="W23">
+        <v>13.14</v>
+      </c>
+      <c r="X23">
+        <v>2536.65</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>995.6</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="E24" s="40"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="40"/>
+      <c r="J24" t="s">
         <v>77</v>
       </c>
-      <c r="Z22" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA22" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.25">
-      <c r="J23" t="s">
-        <v>80</v>
-      </c>
-      <c r="K23">
-        <f>SUM(L23:Y23)</f>
-        <v>35183.040000000001</v>
-      </c>
-      <c r="L23">
-        <v>8697.39</v>
-      </c>
-      <c r="M23">
-        <v>2726.58</v>
-      </c>
-      <c r="N23">
-        <v>4044.63</v>
-      </c>
-      <c r="O23">
-        <v>637.71</v>
-      </c>
-      <c r="P23">
-        <v>3923.7</v>
-      </c>
-      <c r="Q23">
-        <v>968.31</v>
-      </c>
-      <c r="R23">
-        <v>5403.57</v>
-      </c>
-      <c r="S23">
-        <v>472</v>
-      </c>
-      <c r="T23">
-        <v>789.30000000000007</v>
-      </c>
-      <c r="U23">
-        <v>1494</v>
-      </c>
-      <c r="V23">
-        <v>1555.9499999999998</v>
-      </c>
-      <c r="W23">
-        <v>607.5</v>
-      </c>
-      <c r="X23">
-        <v>2255.4</v>
-      </c>
-      <c r="Y23">
-        <v>1607</v>
-      </c>
-      <c r="Z23">
-        <v>1251</v>
-      </c>
-      <c r="AA23">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.25">
-      <c r="J24" t="s">
-        <v>81</v>
-      </c>
       <c r="K24" s="37">
-        <f>SUM(L24:Y24)</f>
-        <v>3649.5450000000001</v>
+        <f>SUM(L24:AA24)</f>
+        <v>2996.72</v>
       </c>
       <c r="L24">
-        <v>142.68</v>
+        <v>0</v>
       </c>
       <c r="M24">
-        <v>261.87</v>
+        <v>0</v>
       </c>
       <c r="N24">
-        <v>90.48</v>
+        <v>0</v>
       </c>
       <c r="O24">
         <v>0</v>
@@ -9020,472 +5388,457 @@
         <v>0</v>
       </c>
       <c r="Q24">
-        <v>26.97</v>
+        <v>0</v>
       </c>
       <c r="R24">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="S24">
-        <v>158</v>
+        <v>129.5</v>
       </c>
       <c r="T24">
-        <v>1229.4000000000001</v>
+        <v>2865.6</v>
       </c>
       <c r="U24">
-        <v>55.5</v>
+        <v>0</v>
       </c>
       <c r="V24">
-        <v>711.97499999999991</v>
+        <v>0</v>
       </c>
       <c r="W24">
-        <v>13.5</v>
+        <v>1.62</v>
       </c>
       <c r="X24">
-        <v>591.30000000000007</v>
+        <v>0</v>
       </c>
       <c r="Y24">
-        <v>367</v>
+        <v>0</v>
       </c>
       <c r="Z24">
         <v>0</v>
       </c>
       <c r="AA24">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="E25" s="40"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="40"/>
       <c r="I25" s="39"/>
       <c r="J25" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="K25" s="35">
-        <f>SUM(K23:K24)/SUM($K23:$K24)</f>
+        <f t="shared" ref="K25:AA25" si="11">SUM(K23:K24)/SUM($K23:$K24)</f>
         <v>1</v>
       </c>
       <c r="L25" s="35">
-        <f>SUM(L23:L24)/SUM($K23:$K24)</f>
-        <v>0.22764567437372504</v>
-      </c>
-      <c r="M25" s="35">
-        <f>SUM(M23:M24)/SUM($K23:$K24)</f>
-        <v>7.6957276987869846E-2</v>
-      </c>
-      <c r="N25" s="35">
-        <f>SUM(N23:N24)/SUM($K23:$K24)</f>
-        <v>0.10648557133139604</v>
-      </c>
-      <c r="O25" s="35">
-        <f>SUM(O23:O24)/SUM($K23:$K24)</f>
-        <v>1.6422033197120409E-2</v>
-      </c>
-      <c r="P25" s="35">
-        <f>SUM(P23:P24)/SUM($K23:$K24)</f>
-        <v>0.10104143208596594</v>
-      </c>
-      <c r="Q25" s="35">
-        <f>SUM(Q23:Q24)/SUM($K23:$K24)</f>
-        <v>2.5630021797415754E-2</v>
-      </c>
-      <c r="R25" s="35">
-        <f>SUM(R23:R24)/SUM($K23:$K24)</f>
-        <v>0.13917281066918413</v>
-      </c>
-      <c r="S25" s="35">
-        <f>SUM(S23:S24)/SUM($K23:$K24)</f>
-        <v>1.6223488598557115E-2</v>
-      </c>
-      <c r="T25" s="35">
-        <f>SUM(T23:T24)/SUM($K23:$K24)</f>
-        <v>5.1984692752233733E-2</v>
-      </c>
-      <c r="U25" s="35">
-        <f>SUM(U23:U24)/SUM($K23:$K24)</f>
-        <v>3.9902056481689284E-2</v>
-      </c>
-      <c r="V25" s="35">
-        <f>SUM(V23:V24)/SUM($K23:$K24)</f>
-        <v>5.8402627587115299E-2</v>
-      </c>
-      <c r="W25" s="35">
-        <f>SUM(W23:W24)/SUM($K23:$K24)</f>
-        <v>1.5991724475720583E-2</v>
-      </c>
-      <c r="X25" s="35">
-        <f>SUM(X23:X24)/SUM($K23:$K24)</f>
-        <v>7.3306992053194506E-2</v>
-      </c>
-      <c r="Y25" s="35">
-        <f>SUM(Y23:Y24)/SUM($K23:$K24)</f>
-        <v>5.0833597608812293E-2</v>
-      </c>
-      <c r="Z25" s="35">
-        <f>SUM(Z23:Z24)/SUM($K23:$K24)</f>
-        <v>3.2215213074277702E-2</v>
-      </c>
-      <c r="AA25" s="35">
-        <f>SUM(AA23:AA24)/SUM($K23:$K24)</f>
-        <v>1.9262173764636067E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.25">
+        <f t="shared" si="11"/>
+        <v>0.23222788444440265</v>
+      </c>
+      <c r="M25" s="39">
+        <f t="shared" ref="M25" si="12">SUM(M23:M24)/SUM($K23:$K24)</f>
+        <v>2.39611841182896E-2</v>
+      </c>
+      <c r="N25" s="39">
+        <f t="shared" ref="N25" si="13">SUM(N23:N24)/SUM($K23:$K24)</f>
+        <v>8.3427301057299189E-2</v>
+      </c>
+      <c r="O25" s="39">
+        <f t="shared" ref="O25" si="14">SUM(O23:O24)/SUM($K23:$K24)</f>
+        <v>5.8354448396922961E-3</v>
+      </c>
+      <c r="P25" s="39">
+        <f t="shared" ref="P25" si="15">SUM(P23:P24)/SUM($K23:$K24)</f>
+        <v>0.14563835908849923</v>
+      </c>
+      <c r="Q25" s="39">
+        <f t="shared" ref="Q25" si="16">SUM(Q23:Q24)/SUM($K23:$K24)</f>
+        <v>6.5200501002148558E-4</v>
+      </c>
+      <c r="R25" s="39">
+        <f t="shared" ref="R25" si="17">SUM(R23:R24)/SUM($K23:$K24)</f>
+        <v>0.18662665404349996</v>
+      </c>
+      <c r="S25" s="39">
+        <f t="shared" ref="S25" si="18">SUM(S23:S24)/SUM($K23:$K24)</f>
+        <v>1.9931118668415414E-2</v>
+      </c>
+      <c r="T25" s="39">
+        <f t="shared" ref="T25" si="19">SUM(T23:T24)/SUM($K23:$K24)</f>
+        <v>0.11183010068437482</v>
+      </c>
+      <c r="U25" s="39">
+        <f t="shared" ref="U25" si="20">SUM(U23:U24)/SUM($K23:$K24)</f>
+        <v>4.588766294668456E-2</v>
+      </c>
+      <c r="V25" s="39">
+        <f t="shared" ref="V25" si="21">SUM(V23:V24)/SUM($K23:$K24)</f>
+        <v>1.1070314374894972E-2</v>
+      </c>
+      <c r="W25" s="39">
+        <f t="shared" ref="W25" si="22">SUM(W23:W24)/SUM($K23:$K24)</f>
+        <v>5.5308011194926036E-4</v>
+      </c>
+      <c r="X25" s="39">
+        <f t="shared" ref="X25" si="23">SUM(X23:X24)/SUM($K23:$K24)</f>
+        <v>9.5052213142011593E-2</v>
+      </c>
+      <c r="Y25" s="39">
+        <f t="shared" ref="Y25" si="24">SUM(Y23:Y24)/SUM($K23:$K24)</f>
+        <v>0</v>
+      </c>
+      <c r="Z25" s="39">
+        <f t="shared" ref="Z25" si="25">SUM(Z23:Z24)/SUM($K23:$K24)</f>
+        <v>3.7306677469965008E-2</v>
+      </c>
+      <c r="AA25" s="39">
+        <f t="shared" ref="AA25" si="26">SUM(AA23:AA24)/SUM($K23:$K24)</f>
+        <v>0</v>
+      </c>
+      <c r="AC25" s="40"/>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="E26" s="40"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="40"/>
       <c r="I26" s="39"/>
       <c r="J26" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="K26" s="35">
         <f>K24/SUM(K23:K24)</f>
-        <v>9.3981510630827186E-2</v>
+        <v>0.11229175020871186</v>
       </c>
       <c r="L26" s="35">
         <f>L24/SUM(L23:L24)</f>
-        <v>1.6140143686645018E-2</v>
+        <v>0</v>
       </c>
       <c r="M26" s="35">
         <f>M24/SUM(M23:M24)</f>
-        <v>8.7627365356623008E-2</v>
+        <v>0</v>
       </c>
       <c r="N26" s="35">
         <f>N24/SUM(N23:N24)</f>
-        <v>2.1880917315379764E-2</v>
+        <v>0</v>
       </c>
       <c r="O26" s="35">
-        <f t="shared" ref="O26:P26" si="11">O24/SUM(O23:O24)</f>
+        <f t="shared" ref="O26:P26" si="27">O24/SUM(O23:O24)</f>
         <v>0</v>
       </c>
       <c r="P26" s="35">
-        <f t="shared" si="11"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="Q26" s="35">
-        <f t="shared" ref="Q26:AA26" si="12">Q24/SUM(Q23:Q24)</f>
-        <v>2.7097902097902096E-2</v>
+        <f t="shared" ref="Q26:AA26" si="28">Q24/SUM(Q23:Q24)</f>
+        <v>0</v>
       </c>
       <c r="R26" s="35">
-        <f t="shared" si="12"/>
-        <v>1.6097875080489378E-4</v>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="S26" s="35">
-        <f t="shared" si="12"/>
-        <v>0.25079365079365079</v>
+        <f t="shared" si="28"/>
+        <v>0.243466817070878</v>
       </c>
       <c r="T26" s="35">
-        <f t="shared" si="12"/>
-        <v>0.60900579580918413</v>
+        <f t="shared" si="28"/>
+        <v>0.96019300361881776</v>
       </c>
       <c r="U26" s="35">
-        <f t="shared" si="12"/>
-        <v>3.5818005808325268E-2</v>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="V26" s="35">
-        <f t="shared" si="12"/>
-        <v>0.31393233903237538</v>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="W26" s="35">
-        <f t="shared" si="12"/>
-        <v>2.1739130434782608E-2</v>
+        <f t="shared" si="28"/>
+        <v>0.10975609756097561</v>
       </c>
       <c r="X26" s="35">
-        <f t="shared" si="12"/>
-        <v>0.207714195384129</v>
-      </c>
-      <c r="Y26" s="35">
-        <f t="shared" si="12"/>
-        <v>0.18591691995947315</v>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="35" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="Z26" s="35">
-        <f t="shared" si="12"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="AA26" s="35">
-        <f t="shared" si="12"/>
-        <v>0.12433155080213903</v>
-      </c>
-    </row>
-    <row r="46" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="F46" t="s">
-        <v>80</v>
-      </c>
-      <c r="G46" t="s">
-        <v>81</v>
-      </c>
-      <c r="H46" t="s">
-        <v>82</v>
-      </c>
-      <c r="K46" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="47" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E47" t="s">
-        <v>64</v>
-      </c>
-      <c r="F47">
-        <v>8697.39</v>
-      </c>
-      <c r="G47">
-        <v>142.68</v>
-      </c>
-      <c r="H47">
-        <v>0.21650077997217101</v>
-      </c>
-      <c r="K47">
-        <v>1.6140143686645018E-2</v>
-      </c>
-    </row>
-    <row r="48" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E48" t="s">
-        <v>65</v>
-      </c>
-      <c r="F48">
-        <v>637.71</v>
-      </c>
-      <c r="G48">
-        <v>0</v>
-      </c>
-      <c r="H48">
-        <v>1.5618056462907329E-2</v>
-      </c>
-      <c r="K48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E49" t="s">
-        <v>66</v>
-      </c>
-      <c r="F49">
-        <v>3923.7</v>
-      </c>
-      <c r="G49">
-        <v>0</v>
-      </c>
-      <c r="H49">
-        <v>9.6094726668092836E-2</v>
-      </c>
-      <c r="K49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E50" t="s">
-        <v>67</v>
-      </c>
-      <c r="F50">
-        <v>2726.58</v>
-      </c>
-      <c r="G50">
-        <v>261.87</v>
-      </c>
-      <c r="H50">
-        <v>7.3189664324811277E-2</v>
-      </c>
-      <c r="K50">
-        <v>8.7627365356623008E-2</v>
-      </c>
-    </row>
-    <row r="51" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E51" t="s">
-        <v>68</v>
-      </c>
-      <c r="F51">
-        <v>4044.63</v>
-      </c>
-      <c r="G51">
-        <v>90.48</v>
-      </c>
-      <c r="H51">
-        <v>0.10127233610941136</v>
-      </c>
-      <c r="K51">
-        <v>2.1880917315379764E-2</v>
-      </c>
-    </row>
-    <row r="52" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E52" t="s">
-        <v>69</v>
-      </c>
-      <c r="F52">
-        <v>968.31</v>
-      </c>
-      <c r="G52">
-        <v>26.97</v>
-      </c>
-      <c r="H52">
-        <v>2.4375247740199158E-2</v>
-      </c>
-      <c r="K52">
-        <v>2.7097902097902096E-2</v>
-      </c>
-    </row>
-    <row r="53" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E53" t="s">
-        <v>70</v>
-      </c>
-      <c r="F53">
-        <v>5403.57</v>
-      </c>
-      <c r="G53">
-        <v>0.87</v>
-      </c>
-      <c r="H53">
-        <v>0.13235929979206046</v>
-      </c>
-      <c r="K53">
-        <v>1.6097875080489378E-4</v>
-      </c>
-    </row>
-    <row r="54" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E54" t="s">
-        <v>71</v>
-      </c>
-      <c r="F54">
-        <v>472</v>
-      </c>
-      <c r="G54">
-        <v>158</v>
-      </c>
-      <c r="H54">
-        <v>1.5429232051609065E-2</v>
-      </c>
-      <c r="K54">
-        <v>0.25079365079365079</v>
-      </c>
-    </row>
-    <row r="55" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E55" t="s">
-        <v>72</v>
-      </c>
-      <c r="F55">
-        <v>789.30000000000007</v>
-      </c>
-      <c r="G55">
-        <v>1229.4000000000001</v>
-      </c>
-      <c r="H55">
-        <v>4.9439667845370197E-2</v>
-      </c>
-      <c r="K55">
-        <v>0.60900579580918413</v>
-      </c>
-    </row>
-    <row r="56" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E56" t="s">
-        <v>73</v>
-      </c>
-      <c r="F56">
-        <v>1494</v>
-      </c>
-      <c r="G56">
-        <v>55.5</v>
-      </c>
-      <c r="H56">
-        <v>3.7948563593600389E-2</v>
-      </c>
-      <c r="K56">
-        <v>3.5818005808325268E-2</v>
-      </c>
-    </row>
-    <row r="57" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E57" t="s">
-        <v>74</v>
-      </c>
-      <c r="F57">
-        <v>1555.9499999999998</v>
-      </c>
-      <c r="G57">
-        <v>711.97499999999991</v>
-      </c>
-      <c r="H57">
-        <v>5.5543398572453148E-2</v>
-      </c>
-      <c r="K57">
-        <v>0.31393233903237538</v>
-      </c>
-    </row>
-    <row r="58" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E58" t="s">
-        <v>75</v>
-      </c>
-      <c r="F58">
-        <v>607.5</v>
-      </c>
-      <c r="G58">
-        <v>13.5</v>
-      </c>
-      <c r="H58">
-        <v>1.5208814450871792E-2</v>
-      </c>
-      <c r="K58">
-        <v>2.1739130434782608E-2</v>
-      </c>
-    </row>
-    <row r="59" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E59" t="s">
-        <v>76</v>
-      </c>
-      <c r="F59">
-        <v>2255.4</v>
-      </c>
-      <c r="G59">
-        <v>591.30000000000007</v>
-      </c>
-      <c r="H59">
-        <v>6.9718087113199254E-2</v>
-      </c>
-      <c r="K59">
-        <v>0.207714195384129</v>
-      </c>
-    </row>
-    <row r="60" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E60" t="s">
-        <v>77</v>
-      </c>
-      <c r="F60">
-        <v>1607</v>
-      </c>
-      <c r="G60">
-        <v>367</v>
-      </c>
-      <c r="H60">
-        <v>4.8344927095041734E-2</v>
-      </c>
-      <c r="K60">
-        <v>0.18591691995947315</v>
-      </c>
-    </row>
-    <row r="61" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E61" t="s">
-        <v>78</v>
-      </c>
-      <c r="F61">
-        <v>1251</v>
-      </c>
-      <c r="G61">
-        <v>0</v>
-      </c>
-      <c r="H61">
-        <v>3.0638046502480858E-2</v>
-      </c>
-      <c r="K61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E62" t="s">
-        <v>79</v>
-      </c>
-      <c r="F62">
-        <v>655</v>
-      </c>
-      <c r="G62">
-        <v>93</v>
-      </c>
-      <c r="H62">
-        <v>1.8319151705719967E-2</v>
-      </c>
-      <c r="K62">
-        <v>0.12433155080213903</v>
-      </c>
+      <c r="AA26" s="35" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="40"/>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="E28" s="40"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="40"/>
+      <c r="K28" s="37"/>
+      <c r="L28" s="37"/>
+      <c r="M28" s="37"/>
+      <c r="N28" s="37"/>
+      <c r="O28" s="37"/>
+      <c r="P28" s="37"/>
+      <c r="Q28" s="37"/>
+      <c r="R28" s="37"/>
+      <c r="S28" s="37"/>
+      <c r="T28" s="37"/>
+      <c r="U28" s="37"/>
+      <c r="V28" s="37"/>
+      <c r="W28" s="37"/>
+      <c r="X28" s="37"/>
+      <c r="Y28" s="37"/>
+      <c r="Z28" s="37"/>
+      <c r="AA28" s="37"/>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="E29" s="40"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="40"/>
+      <c r="J29" s="37"/>
+      <c r="K29" s="37"/>
+      <c r="L29" s="37"/>
+      <c r="M29" s="37"/>
+      <c r="N29" s="37"/>
+      <c r="O29" s="37"/>
+      <c r="P29" s="37"/>
+      <c r="Q29" s="37"/>
+      <c r="R29" s="37"/>
+      <c r="S29" s="37"/>
+      <c r="T29" s="37"/>
+      <c r="U29" s="37"/>
+      <c r="V29" s="37"/>
+      <c r="W29" s="37"/>
+      <c r="X29" s="37"/>
+      <c r="Y29" s="37"/>
+      <c r="Z29" s="37"/>
+      <c r="AA29" s="37"/>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="E30" s="40"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="40"/>
+      <c r="H30" s="40"/>
+      <c r="J30" s="37"/>
+      <c r="K30" s="37"/>
+      <c r="L30" s="37"/>
+      <c r="M30" s="37"/>
+      <c r="N30" s="37"/>
+      <c r="O30" s="37"/>
+      <c r="P30" s="37"/>
+      <c r="Q30" s="37"/>
+      <c r="R30" s="37"/>
+      <c r="S30" s="37"/>
+      <c r="T30" s="37"/>
+      <c r="U30" s="37"/>
+      <c r="V30" s="37"/>
+      <c r="W30" s="37"/>
+      <c r="X30" s="37"/>
+      <c r="Y30" s="37"/>
+      <c r="Z30" s="37"/>
+      <c r="AA30" s="37"/>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="E31" s="40"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="40"/>
+      <c r="J31" s="37"/>
+      <c r="K31" s="39"/>
+      <c r="L31" s="39"/>
+      <c r="M31" s="39"/>
+      <c r="N31" s="39"/>
+      <c r="O31" s="39"/>
+      <c r="P31" s="39"/>
+      <c r="Q31" s="39"/>
+      <c r="R31" s="39"/>
+      <c r="S31" s="39"/>
+      <c r="T31" s="39"/>
+      <c r="U31" s="39"/>
+      <c r="V31" s="39"/>
+      <c r="W31" s="39"/>
+      <c r="X31" s="39"/>
+      <c r="Y31" s="39"/>
+      <c r="Z31" s="39"/>
+      <c r="AA31" s="39"/>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="E32" s="40"/>
+      <c r="F32" s="40"/>
+      <c r="G32" s="40"/>
+      <c r="H32" s="40"/>
+      <c r="J32" s="37"/>
+      <c r="K32" s="39"/>
+      <c r="L32" s="39"/>
+      <c r="M32" s="39"/>
+      <c r="N32" s="39"/>
+      <c r="O32" s="39"/>
+      <c r="P32" s="39"/>
+      <c r="Q32" s="39"/>
+      <c r="R32" s="39"/>
+      <c r="S32" s="39"/>
+      <c r="T32" s="39"/>
+      <c r="U32" s="39"/>
+      <c r="V32" s="39"/>
+      <c r="W32" s="39"/>
+      <c r="X32" s="39"/>
+      <c r="Y32" s="39"/>
+      <c r="Z32" s="39"/>
+      <c r="AA32" s="39"/>
+    </row>
+    <row r="33" spans="5:27" x14ac:dyDescent="0.25">
+      <c r="E33" s="40"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="40"/>
+      <c r="H33" s="40"/>
+    </row>
+    <row r="34" spans="5:27" x14ac:dyDescent="0.25">
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="40"/>
+      <c r="H34" s="40"/>
+      <c r="M34" s="37"/>
+      <c r="N34" s="37"/>
+      <c r="O34" s="37"/>
+      <c r="P34" s="37"/>
+      <c r="Q34" s="37"/>
+      <c r="R34" s="37"/>
+      <c r="S34" s="37"/>
+      <c r="T34" s="37"/>
+      <c r="U34" s="37"/>
+      <c r="V34" s="37"/>
+      <c r="W34" s="37"/>
+      <c r="X34" s="37"/>
+      <c r="Y34" s="37"/>
+      <c r="Z34" s="37"/>
+      <c r="AA34" s="37"/>
+    </row>
+    <row r="35" spans="5:27" x14ac:dyDescent="0.25">
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="40"/>
+      <c r="H35" s="40"/>
+    </row>
+    <row r="36" spans="5:27" x14ac:dyDescent="0.25">
+      <c r="E36" s="40"/>
+      <c r="F36" s="40"/>
+      <c r="G36" s="40"/>
+      <c r="H36" s="40"/>
+      <c r="J36" s="34"/>
+    </row>
+    <row r="37" spans="5:27" x14ac:dyDescent="0.25">
+      <c r="E37" s="40"/>
+      <c r="F37" s="40"/>
+      <c r="G37" s="40"/>
+      <c r="H37" s="40"/>
+    </row>
+    <row r="38" spans="5:27" x14ac:dyDescent="0.25">
+      <c r="E38" s="40"/>
+      <c r="F38" s="40"/>
+      <c r="G38" s="40"/>
+      <c r="H38" s="40"/>
+      <c r="O38" s="37"/>
+    </row>
+    <row r="39" spans="5:27" x14ac:dyDescent="0.25">
+      <c r="E39" s="40"/>
+      <c r="F39" s="40"/>
+      <c r="G39" s="40"/>
+      <c r="H39" s="40"/>
+      <c r="O39" s="39"/>
+    </row>
+    <row r="40" spans="5:27" x14ac:dyDescent="0.25">
+      <c r="E40" s="40"/>
+      <c r="F40" s="40"/>
+      <c r="G40" s="40"/>
+      <c r="H40" s="40"/>
+      <c r="M40" s="37"/>
+      <c r="O40" s="39"/>
+    </row>
+    <row r="41" spans="5:27" x14ac:dyDescent="0.25">
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="40"/>
+      <c r="M41" s="37"/>
+      <c r="O41" s="39"/>
+    </row>
+    <row r="42" spans="5:27" x14ac:dyDescent="0.25">
+      <c r="E42" s="40"/>
+      <c r="F42" s="40"/>
+      <c r="G42" s="40"/>
+      <c r="H42" s="40"/>
+      <c r="M42" s="37"/>
+      <c r="O42" s="39"/>
+    </row>
+    <row r="43" spans="5:27" x14ac:dyDescent="0.25">
+      <c r="E43" s="40"/>
+      <c r="F43" s="40"/>
+      <c r="G43" s="40"/>
+      <c r="H43" s="40"/>
+      <c r="M43" s="37"/>
+      <c r="O43" s="39"/>
+    </row>
+    <row r="44" spans="5:27" x14ac:dyDescent="0.25">
+      <c r="H44" s="40"/>
+      <c r="M44" s="37"/>
+      <c r="O44" s="39"/>
+    </row>
+    <row r="45" spans="5:27" x14ac:dyDescent="0.25">
+      <c r="M45" s="37"/>
+      <c r="O45" s="39"/>
+    </row>
+    <row r="46" spans="5:27" x14ac:dyDescent="0.25">
+      <c r="M46" s="37"/>
+      <c r="O46" s="39"/>
+    </row>
+    <row r="47" spans="5:27" x14ac:dyDescent="0.25">
+      <c r="M47" s="37"/>
+      <c r="O47" s="39"/>
+    </row>
+    <row r="48" spans="5:27" x14ac:dyDescent="0.25">
+      <c r="M48" s="37"/>
+      <c r="O48" s="39"/>
+    </row>
+    <row r="49" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="M49" s="37"/>
+      <c r="O49" s="39"/>
+    </row>
+    <row r="50" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="M50" s="37"/>
+      <c r="O50" s="39"/>
+    </row>
+    <row r="51" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="M51" s="37"/>
+      <c r="O51" s="39"/>
+    </row>
+    <row r="52" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="M52" s="37"/>
+      <c r="O52" s="39"/>
+    </row>
+    <row r="53" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="M53" s="37"/>
+      <c r="O53" s="39"/>
+    </row>
+    <row r="54" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="M54" s="37"/>
+      <c r="O54" s="39"/>
+    </row>
+    <row r="56" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="K56" s="38"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9499,22 +5852,22 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="3" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="45" t="s">
+      <c r="B3" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="45"/>
-      <c r="M3" s="45"/>
-      <c r="N3" s="45"/>
-      <c r="O3" s="45"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="41"/>
+      <c r="O3" s="41"/>
     </row>
     <row r="4" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B4" s="42" t="s">
@@ -10191,38 +6544,38 @@
       </c>
     </row>
     <row r="17" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B17" s="41" t="s">
+      <c r="B17" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="41"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="41"/>
-      <c r="I17" s="41"/>
-      <c r="J17" s="41"/>
-      <c r="K17" s="41"/>
-      <c r="L17" s="41"/>
-      <c r="M17" s="41"/>
-      <c r="N17" s="41"/>
-      <c r="O17" s="41"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="45"/>
+      <c r="H17" s="45"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="45"/>
+      <c r="K17" s="45"/>
+      <c r="L17" s="45"/>
+      <c r="M17" s="45"/>
+      <c r="N17" s="45"/>
+      <c r="O17" s="45"/>
     </row>
     <row r="18" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B18" s="41"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="41"/>
-      <c r="J18" s="41"/>
-      <c r="K18" s="41"/>
-      <c r="L18" s="41"/>
-      <c r="M18" s="41"/>
-      <c r="N18" s="41"/>
-      <c r="O18" s="41"/>
+      <c r="B18" s="45"/>
+      <c r="C18" s="45"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="45"/>
+      <c r="J18" s="45"/>
+      <c r="K18" s="45"/>
+      <c r="L18" s="45"/>
+      <c r="M18" s="45"/>
+      <c r="N18" s="45"/>
+      <c r="O18" s="45"/>
     </row>
     <row r="19" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B19" s="42" t="s">
@@ -10900,16 +7253,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B17:O18"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="L19:N19"/>
     <mergeCell ref="B3:O3"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="I4:K4"/>
     <mergeCell ref="L4:N4"/>
-    <mergeCell ref="B17:O18"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="L19:N19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
